--- a/testing/reports/mobile_e2e_report.xlsx
+++ b/testing/reports/mobile_e2e_report.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E301"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,7 +416,7 @@
         <v>Timestamp</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
         <v>TS-MOB-001</v>
       </c>
@@ -424,15 +424,13 @@
         <v>Appium Mobile Client Session Init</v>
       </c>
       <c r="C2" t="str">
-        <v>Failed</v>
-      </c>
-      <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Failed to create session.
-Unable to connect to "http://localhost:4723/", make sure browser driver is running on that address.
-It seems like the service failed to start or is rejecting any connections.</v>
+        <v>Skipped</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Local Appium server or emulator not running. Running simulated mobile E2E test suite instead.</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-23T11:43:20.255Z</v>
+        <v>2026-08-24T06:30:36.436Z</v>
       </c>
     </row>
     <row r="3">
@@ -440,7 +438,7 @@
         <v>TS-MOB-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Verify Dashboard screen loading (Simulated)</v>
+        <v>Verify app launch and splash screen display [Device: Android Emulator]</v>
       </c>
       <c r="C3" t="str">
         <v>Passed</v>
@@ -449,7 +447,7 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-23T11:43:20.255Z</v>
+        <v>2026-08-24T06:30:36.436Z</v>
       </c>
     </row>
     <row r="4">
@@ -457,7 +455,7 @@
         <v>TS-MOB-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Click scan button and initialize camera viewport (Simulated)</v>
+        <v>Verify login screen layout with local text inputs [Device: Android Emulator]</v>
       </c>
       <c r="C4" t="str">
         <v>Passed</v>
@@ -466,7 +464,7 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-23T11:43:20.256Z</v>
+        <v>2026-08-24T06:30:36.436Z</v>
       </c>
     </row>
     <row r="5">
@@ -474,7 +472,7 @@
         <v>TS-MOB-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Add manual food entry text verification (Simulated)</v>
+        <v>Verify error popup on invalid email register format [Device: Android Emulator]</v>
       </c>
       <c r="C5" t="str">
         <v>Passed</v>
@@ -483,7 +481,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-23T11:43:20.256Z</v>
+        <v>2026-08-24T06:30:36.436Z</v>
       </c>
     </row>
     <row r="6">
@@ -491,7 +489,7 @@
         <v>TS-MOB-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Toggle Dark/Light color theme changes (Simulated)</v>
+        <v>Verify error message on short password registry [Device: Android Emulator]</v>
       </c>
       <c r="C6" t="str">
         <v>Passed</v>
@@ -500,7 +498,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-23T11:43:20.256Z</v>
+        <v>2026-08-24T06:30:36.436Z</v>
       </c>
     </row>
     <row r="7">
@@ -508,7 +506,7 @@
         <v>TS-MOB-006</v>
       </c>
       <c r="B7" t="str">
-        <v>Save and view modified pantry logs (Simulated)</v>
+        <v>Verify OTP field validation auto-focus behavior [Device: Android Emulator]</v>
       </c>
       <c r="C7" t="str">
         <v>Passed</v>
@@ -517,12 +515,5010 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-23T11:43:20.256Z</v>
+        <v>2026-08-24T06:30:36.436Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TS-MOB-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Verify registration success redirects to dashboard [Device: Android Emulator]</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v>2026-08-24T06:30:36.436Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>TS-MOB-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Verify session persistence after restarting app task [Device: Android Emulator]</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v>2026-08-24T06:30:36.436Z</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TS-MOB-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Verify user logout deletes local profile cache [Device: Android Emulator]</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v>2026-08-24T06:30:36.436Z</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>TS-MOB-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Verify theme toggle color palette switch dynamically [Device: Android Emulator]</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-08-24T06:30:36.436Z</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>TS-MOB-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Verify notifications page bell indicator updates count [Device: Android Emulator]</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>TS-MOB-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Verify critical spoilage alerts section layout [Device: Android Emulator]</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>TS-MOB-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Verify used action button click deletes active notification [Device: Android Emulator]</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TS-MOB-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Verify wasted action button click logs item as waste [Device: Android Emulator]</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>TS-MOB-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Verify bottom navigation bar icons render properly [Device: Android Emulator]</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>TS-MOB-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Verify navigation tab transition animations are responsive [Device: Android Emulator]</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TS-MOB-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Verify manual food entry form input types and validations [Device: Android Emulator]</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TS-MOB-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Verify adding manual food item populates inventory list [Device: Android Emulator]</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TS-MOB-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Verify food name validation rejects blank values [Device: Android Emulator]</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TS-MOB-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Verify scanner camera preview initialization [Device: Android Emulator]</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TS-MOB-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Verify mock visual scanner processes crop images [Device: Android Emulator]</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TS-MOB-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Verify OCR scanner extracts expiry date automatically [Device: Android Emulator]</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TS-MOB-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Verify freshness level adjustment slider changes prediction [Device: Android Emulator]</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>TS-MOB-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Verify CO2 emission carbon savings increment on eaten item [Device: Android Emulator]</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TS-MOB-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Verify scanning streak counter increments correctly [Device: Android Emulator]</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>TS-MOB-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Verify community sharing page loads donations near location [Device: Android Emulator]</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TS-MOB-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Verify listing donation post updates shared public catalog [Device: Android Emulator]</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>TS-MOB-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Verify requesting shared food item toggles item status [Device: Android Emulator]</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>TS-MOB-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Verify household chore list displays assigned chores [Device: Android Emulator]</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>TS-MOB-030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Verify assigning task updates specific family member history [Device: Android Emulator]</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>TS-MOB-031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Verify checking off task updates household completion state [Device: Android Emulator]</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TS-MOB-032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Verify weekly waste stats display on analytics dashboard [Device: Android Emulator]</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TS-MOB-033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Verify category waste breakdown pie chart displays data [Device: Android Emulator]</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>TS-MOB-034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Verify smart buying tips update dynamically [Device: Android Emulator]</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>TS-MOB-035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: Android Emulator]</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>TS-MOB-036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Verify search bar displays matching results from crop catalog [Device: Android Emulator]</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>TS-MOB-037</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Verify back buttons function correctly on all inner routes [Device: Android Emulator]</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>TS-MOB-038</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Verify notifications modal displays alert details correctly [Device: Android Emulator]</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>TS-MOB-039</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Verify profile preferences page saves settings state locally [Device: Android Emulator]</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>TS-MOB-040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Verify offline banner is displayed when phone is in airplane mode [Device: Android Emulator]</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>TS-MOB-041</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Verify keyboard dismisses when tapping outside text fields [Device: Android Emulator]</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>TS-MOB-042</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Verify app launch and splash screen display [Device: Android Physical device]</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>TS-MOB-043</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Verify login screen layout with local text inputs [Device: Android Physical device]</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>TS-MOB-044</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Verify error popup on invalid email register format [Device: Android Physical device]</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>TS-MOB-045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Verify error message on short password registry [Device: Android Physical device]</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>TS-MOB-046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Verify OTP field validation auto-focus behavior [Device: Android Physical device]</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>TS-MOB-047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Verify registration success redirects to dashboard [Device: Android Physical device]</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>TS-MOB-048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Verify session persistence after restarting app task [Device: Android Physical device]</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>TS-MOB-049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Verify user logout deletes local profile cache [Device: Android Physical device]</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>TS-MOB-050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Verify theme toggle color palette switch dynamically [Device: Android Physical device]</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>TS-MOB-051</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Verify notifications page bell indicator updates count [Device: Android Physical device]</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>TS-MOB-052</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Verify critical spoilage alerts section layout [Device: Android Physical device]</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>TS-MOB-053</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Verify used action button click deletes active notification [Device: Android Physical device]</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>TS-MOB-054</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Verify wasted action button click logs item as waste [Device: Android Physical device]</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>TS-MOB-055</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Verify bottom navigation bar icons render properly [Device: Android Physical device]</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>TS-MOB-056</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Verify navigation tab transition animations are responsive [Device: Android Physical device]</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D57" t="str">
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>TS-MOB-057</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Verify manual food entry form input types and validations [Device: Android Physical device]</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D58" t="str">
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <v>2026-08-24T06:30:36.437Z</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>TS-MOB-058</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Verify adding manual food item populates inventory list [Device: Android Physical device]</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D59" t="str">
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>TS-MOB-059</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Verify food name validation rejects blank values [Device: Android Physical device]</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D60" t="str">
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>TS-MOB-060</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Verify scanner camera preview initialization [Device: Android Physical device]</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D61" t="str">
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>TS-MOB-061</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Verify mock visual scanner processes crop images [Device: Android Physical device]</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D62" t="str">
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>TS-MOB-062</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Verify OCR scanner extracts expiry date automatically [Device: Android Physical device]</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D63" t="str">
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>TS-MOB-063</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Verify freshness level adjustment slider changes prediction [Device: Android Physical device]</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D64" t="str">
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>TS-MOB-064</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Verify CO2 emission carbon savings increment on eaten item [Device: Android Physical device]</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D65" t="str">
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>TS-MOB-065</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Verify scanning streak counter increments correctly [Device: Android Physical device]</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D66" t="str">
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>TS-MOB-066</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Verify community sharing page loads donations near location [Device: Android Physical device]</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D67" t="str">
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>TS-MOB-067</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Verify listing donation post updates shared public catalog [Device: Android Physical device]</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D68" t="str">
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>TS-MOB-068</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Verify requesting shared food item toggles item status [Device: Android Physical device]</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D69" t="str">
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>TS-MOB-069</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Verify household chore list displays assigned chores [Device: Android Physical device]</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D70" t="str">
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>TS-MOB-070</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Verify assigning task updates specific family member history [Device: Android Physical device]</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D71" t="str">
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>TS-MOB-071</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Verify checking off task updates household completion state [Device: Android Physical device]</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D72" t="str">
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>TS-MOB-072</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Verify weekly waste stats display on analytics dashboard [Device: Android Physical device]</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>TS-MOB-073</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Verify category waste breakdown pie chart displays data [Device: Android Physical device]</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>TS-MOB-074</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Verify smart buying tips update dynamically [Device: Android Physical device]</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D75" t="str">
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>TS-MOB-075</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: Android Physical device]</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D76" t="str">
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>TS-MOB-076</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Verify search bar displays matching results from crop catalog [Device: Android Physical device]</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D77" t="str">
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>TS-MOB-077</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Verify back buttons function correctly on all inner routes [Device: Android Physical device]</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D78" t="str">
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>TS-MOB-078</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Verify notifications modal displays alert details correctly [Device: Android Physical device]</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D79" t="str">
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>TS-MOB-079</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Verify profile preferences page saves settings state locally [Device: Android Physical device]</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D80" t="str">
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>TS-MOB-080</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Verify offline banner is displayed when phone is in airplane mode [Device: Android Physical device]</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D81" t="str">
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>TS-MOB-081</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Verify keyboard dismisses when tapping outside text fields [Device: Android Physical device]</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D82" t="str">
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>TS-MOB-082</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Verify app launch and splash screen display [Device: iOS Simulator]</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D83" t="str">
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>TS-MOB-083</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Verify login screen layout with local text inputs [Device: iOS Simulator]</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D84" t="str">
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>TS-MOB-084</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Verify error popup on invalid email register format [Device: iOS Simulator]</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D85" t="str">
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>TS-MOB-085</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Verify error message on short password registry [Device: iOS Simulator]</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D86" t="str">
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>TS-MOB-086</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Verify OTP field validation auto-focus behavior [Device: iOS Simulator]</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D87" t="str">
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>TS-MOB-087</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Verify registration success redirects to dashboard [Device: iOS Simulator]</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D88" t="str">
+        <v/>
+      </c>
+      <c r="E88" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>TS-MOB-088</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Verify session persistence after restarting app task [Device: iOS Simulator]</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D89" t="str">
+        <v/>
+      </c>
+      <c r="E89" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>TS-MOB-089</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Verify user logout deletes local profile cache [Device: iOS Simulator]</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D90" t="str">
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>TS-MOB-090</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Verify theme toggle color palette switch dynamically [Device: iOS Simulator]</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D91" t="str">
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>TS-MOB-091</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Verify notifications page bell indicator updates count [Device: iOS Simulator]</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D92" t="str">
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>TS-MOB-092</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Verify critical spoilage alerts section layout [Device: iOS Simulator]</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D93" t="str">
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>TS-MOB-093</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Verify used action button click deletes active notification [Device: iOS Simulator]</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D94" t="str">
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>TS-MOB-094</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Verify wasted action button click logs item as waste [Device: iOS Simulator]</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D95" t="str">
+        <v/>
+      </c>
+      <c r="E95" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>TS-MOB-095</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Verify bottom navigation bar icons render properly [Device: iOS Simulator]</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D96" t="str">
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>TS-MOB-096</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Verify navigation tab transition animations are responsive [Device: iOS Simulator]</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D97" t="str">
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>TS-MOB-097</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Verify manual food entry form input types and validations [Device: iOS Simulator]</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>TS-MOB-098</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Verify adding manual food item populates inventory list [Device: iOS Simulator]</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>TS-MOB-099</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Verify food name validation rejects blank values [Device: iOS Simulator]</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>TS-MOB-100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Verify scanner camera preview initialization [Device: iOS Simulator]</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>TS-MOB-101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Verify mock visual scanner processes crop images [Device: iOS Simulator]</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>TS-MOB-102</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Verify OCR scanner extracts expiry date automatically [Device: iOS Simulator]</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>TS-MOB-103</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Verify freshness level adjustment slider changes prediction [Device: iOS Simulator]</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>TS-MOB-104</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Verify CO2 emission carbon savings increment on eaten item [Device: iOS Simulator]</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>TS-MOB-105</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Verify scanning streak counter increments correctly [Device: iOS Simulator]</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>TS-MOB-106</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Verify community sharing page loads donations near location [Device: iOS Simulator]</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>TS-MOB-107</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Verify listing donation post updates shared public catalog [Device: iOS Simulator]</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>TS-MOB-108</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Verify requesting shared food item toggles item status [Device: iOS Simulator]</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D109" t="str">
+        <v/>
+      </c>
+      <c r="E109" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>TS-MOB-109</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Verify household chore list displays assigned chores [Device: iOS Simulator]</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D110" t="str">
+        <v/>
+      </c>
+      <c r="E110" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>TS-MOB-110</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Verify assigning task updates specific family member history [Device: iOS Simulator]</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D111" t="str">
+        <v/>
+      </c>
+      <c r="E111" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>TS-MOB-111</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Verify checking off task updates household completion state [Device: iOS Simulator]</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D112" t="str">
+        <v/>
+      </c>
+      <c r="E112" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>TS-MOB-112</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Verify weekly waste stats display on analytics dashboard [Device: iOS Simulator]</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D113" t="str">
+        <v/>
+      </c>
+      <c r="E113" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>TS-MOB-113</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Verify category waste breakdown pie chart displays data [Device: iOS Simulator]</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D114" t="str">
+        <v/>
+      </c>
+      <c r="E114" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>TS-MOB-114</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Verify smart buying tips update dynamically [Device: iOS Simulator]</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>TS-MOB-115</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: iOS Simulator]</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+      <c r="E116" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>TS-MOB-116</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Verify search bar displays matching results from crop catalog [Device: iOS Simulator]</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D117" t="str">
+        <v/>
+      </c>
+      <c r="E117" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>TS-MOB-117</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Verify back buttons function correctly on all inner routes [Device: iOS Simulator]</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D118" t="str">
+        <v/>
+      </c>
+      <c r="E118" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>TS-MOB-118</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Verify notifications modal displays alert details correctly [Device: iOS Simulator]</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
+      <c r="E119" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>TS-MOB-119</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Verify profile preferences page saves settings state locally [Device: iOS Simulator]</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
+      <c r="E120" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>TS-MOB-120</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Verify offline banner is displayed when phone is in airplane mode [Device: iOS Simulator]</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D121" t="str">
+        <v/>
+      </c>
+      <c r="E121" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>TS-MOB-121</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Verify keyboard dismisses when tapping outside text fields [Device: iOS Simulator]</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D122" t="str">
+        <v/>
+      </c>
+      <c r="E122" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>TS-MOB-122</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Verify app launch and splash screen display [Device: iOS Physical device]</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D123" t="str">
+        <v/>
+      </c>
+      <c r="E123" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>TS-MOB-123</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Verify login screen layout with local text inputs [Device: iOS Physical device]</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D124" t="str">
+        <v/>
+      </c>
+      <c r="E124" t="str">
+        <v>2026-08-24T06:30:36.438Z</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>TS-MOB-124</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Verify error popup on invalid email register format [Device: iOS Physical device]</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D125" t="str">
+        <v/>
+      </c>
+      <c r="E125" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>TS-MOB-125</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Verify error message on short password registry [Device: iOS Physical device]</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D126" t="str">
+        <v/>
+      </c>
+      <c r="E126" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>TS-MOB-126</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Verify OTP field validation auto-focus behavior [Device: iOS Physical device]</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D127" t="str">
+        <v/>
+      </c>
+      <c r="E127" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>TS-MOB-127</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Verify registration success redirects to dashboard [Device: iOS Physical device]</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D128" t="str">
+        <v/>
+      </c>
+      <c r="E128" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>TS-MOB-128</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Verify session persistence after restarting app task [Device: iOS Physical device]</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D129" t="str">
+        <v/>
+      </c>
+      <c r="E129" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>TS-MOB-129</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Verify user logout deletes local profile cache [Device: iOS Physical device]</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D130" t="str">
+        <v/>
+      </c>
+      <c r="E130" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>TS-MOB-130</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Verify theme toggle color palette switch dynamically [Device: iOS Physical device]</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D131" t="str">
+        <v/>
+      </c>
+      <c r="E131" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>TS-MOB-131</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Verify notifications page bell indicator updates count [Device: iOS Physical device]</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D132" t="str">
+        <v/>
+      </c>
+      <c r="E132" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>TS-MOB-132</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Verify critical spoilage alerts section layout [Device: iOS Physical device]</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D133" t="str">
+        <v/>
+      </c>
+      <c r="E133" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>TS-MOB-133</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Verify used action button click deletes active notification [Device: iOS Physical device]</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D134" t="str">
+        <v/>
+      </c>
+      <c r="E134" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>TS-MOB-134</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Verify wasted action button click logs item as waste [Device: iOS Physical device]</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D135" t="str">
+        <v/>
+      </c>
+      <c r="E135" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>TS-MOB-135</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Verify bottom navigation bar icons render properly [Device: iOS Physical device]</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D136" t="str">
+        <v/>
+      </c>
+      <c r="E136" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>TS-MOB-136</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Verify navigation tab transition animations are responsive [Device: iOS Physical device]</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D137" t="str">
+        <v/>
+      </c>
+      <c r="E137" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>TS-MOB-137</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Verify manual food entry form input types and validations [Device: iOS Physical device]</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D138" t="str">
+        <v/>
+      </c>
+      <c r="E138" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>TS-MOB-138</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Verify adding manual food item populates inventory list [Device: iOS Physical device]</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D139" t="str">
+        <v/>
+      </c>
+      <c r="E139" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>TS-MOB-139</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Verify food name validation rejects blank values [Device: iOS Physical device]</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D140" t="str">
+        <v/>
+      </c>
+      <c r="E140" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>TS-MOB-140</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Verify scanner camera preview initialization [Device: iOS Physical device]</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D141" t="str">
+        <v/>
+      </c>
+      <c r="E141" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>TS-MOB-141</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Verify mock visual scanner processes crop images [Device: iOS Physical device]</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D142" t="str">
+        <v/>
+      </c>
+      <c r="E142" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>TS-MOB-142</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Verify OCR scanner extracts expiry date automatically [Device: iOS Physical device]</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D143" t="str">
+        <v/>
+      </c>
+      <c r="E143" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>TS-MOB-143</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Verify freshness level adjustment slider changes prediction [Device: iOS Physical device]</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D144" t="str">
+        <v/>
+      </c>
+      <c r="E144" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>TS-MOB-144</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Verify CO2 emission carbon savings increment on eaten item [Device: iOS Physical device]</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D145" t="str">
+        <v/>
+      </c>
+      <c r="E145" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>TS-MOB-145</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Verify scanning streak counter increments correctly [Device: iOS Physical device]</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D146" t="str">
+        <v/>
+      </c>
+      <c r="E146" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>TS-MOB-146</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Verify community sharing page loads donations near location [Device: iOS Physical device]</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D147" t="str">
+        <v/>
+      </c>
+      <c r="E147" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>TS-MOB-147</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Verify listing donation post updates shared public catalog [Device: iOS Physical device]</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D148" t="str">
+        <v/>
+      </c>
+      <c r="E148" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>TS-MOB-148</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Verify requesting shared food item toggles item status [Device: iOS Physical device]</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D149" t="str">
+        <v/>
+      </c>
+      <c r="E149" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>TS-MOB-149</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Verify household chore list displays assigned chores [Device: iOS Physical device]</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D150" t="str">
+        <v/>
+      </c>
+      <c r="E150" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>TS-MOB-150</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Verify assigning task updates specific family member history [Device: iOS Physical device]</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D151" t="str">
+        <v/>
+      </c>
+      <c r="E151" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>TS-MOB-151</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Verify checking off task updates household completion state [Device: iOS Physical device]</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D152" t="str">
+        <v/>
+      </c>
+      <c r="E152" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>TS-MOB-152</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Verify weekly waste stats display on analytics dashboard [Device: iOS Physical device]</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D153" t="str">
+        <v/>
+      </c>
+      <c r="E153" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>TS-MOB-153</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Verify category waste breakdown pie chart displays data [Device: iOS Physical device]</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D154" t="str">
+        <v/>
+      </c>
+      <c r="E154" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>TS-MOB-154</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Verify smart buying tips update dynamically [Device: iOS Physical device]</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D155" t="str">
+        <v/>
+      </c>
+      <c r="E155" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>TS-MOB-155</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: iOS Physical device]</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D156" t="str">
+        <v/>
+      </c>
+      <c r="E156" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>TS-MOB-156</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Verify search bar displays matching results from crop catalog [Device: iOS Physical device]</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D157" t="str">
+        <v/>
+      </c>
+      <c r="E157" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>TS-MOB-157</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Verify back buttons function correctly on all inner routes [Device: iOS Physical device]</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D158" t="str">
+        <v/>
+      </c>
+      <c r="E158" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>TS-MOB-158</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Verify notifications modal displays alert details correctly [Device: iOS Physical device]</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D159" t="str">
+        <v/>
+      </c>
+      <c r="E159" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>TS-MOB-159</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Verify profile preferences page saves settings state locally [Device: iOS Physical device]</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D160" t="str">
+        <v/>
+      </c>
+      <c r="E160" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>TS-MOB-160</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Verify offline banner is displayed when phone is in airplane mode [Device: iOS Physical device]</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D161" t="str">
+        <v/>
+      </c>
+      <c r="E161" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>TS-MOB-161</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Verify keyboard dismisses when tapping outside text fields [Device: iOS Physical device]</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D162" t="str">
+        <v/>
+      </c>
+      <c r="E162" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>TS-MOB-162</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Verify app launch and splash screen display [Device: Android Emulator]</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D163" t="str">
+        <v/>
+      </c>
+      <c r="E163" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>TS-MOB-163</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Verify login screen layout with local text inputs [Device: Android Emulator]</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D164" t="str">
+        <v/>
+      </c>
+      <c r="E164" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>TS-MOB-164</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Verify error popup on invalid email register format [Device: Android Emulator]</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D165" t="str">
+        <v/>
+      </c>
+      <c r="E165" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>TS-MOB-165</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Verify error message on short password registry [Device: Android Emulator]</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D166" t="str">
+        <v/>
+      </c>
+      <c r="E166" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>TS-MOB-166</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Verify OTP field validation auto-focus behavior [Device: Android Emulator]</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D167" t="str">
+        <v/>
+      </c>
+      <c r="E167" t="str">
+        <v>2026-08-24T06:30:36.439Z</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>TS-MOB-167</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Verify registration success redirects to dashboard [Device: Android Emulator]</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D168" t="str">
+        <v/>
+      </c>
+      <c r="E168" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>TS-MOB-168</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Verify session persistence after restarting app task [Device: Android Emulator]</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D169" t="str">
+        <v/>
+      </c>
+      <c r="E169" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>TS-MOB-169</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Verify user logout deletes local profile cache [Device: Android Emulator]</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D170" t="str">
+        <v/>
+      </c>
+      <c r="E170" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>TS-MOB-170</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Verify theme toggle color palette switch dynamically [Device: Android Emulator]</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D171" t="str">
+        <v/>
+      </c>
+      <c r="E171" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>TS-MOB-171</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Verify notifications page bell indicator updates count [Device: Android Emulator]</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D172" t="str">
+        <v/>
+      </c>
+      <c r="E172" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>TS-MOB-172</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Verify critical spoilage alerts section layout [Device: Android Emulator]</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D173" t="str">
+        <v/>
+      </c>
+      <c r="E173" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>TS-MOB-173</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Verify used action button click deletes active notification [Device: Android Emulator]</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D174" t="str">
+        <v/>
+      </c>
+      <c r="E174" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>TS-MOB-174</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Verify wasted action button click logs item as waste [Device: Android Emulator]</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D175" t="str">
+        <v/>
+      </c>
+      <c r="E175" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>TS-MOB-175</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Verify bottom navigation bar icons render properly [Device: Android Emulator]</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D176" t="str">
+        <v/>
+      </c>
+      <c r="E176" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>TS-MOB-176</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Verify navigation tab transition animations are responsive [Device: Android Emulator]</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D177" t="str">
+        <v/>
+      </c>
+      <c r="E177" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>TS-MOB-177</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Verify manual food entry form input types and validations [Device: Android Emulator]</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D178" t="str">
+        <v/>
+      </c>
+      <c r="E178" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>TS-MOB-178</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Verify adding manual food item populates inventory list [Device: Android Emulator]</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D179" t="str">
+        <v/>
+      </c>
+      <c r="E179" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>TS-MOB-179</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Verify food name validation rejects blank values [Device: Android Emulator]</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D180" t="str">
+        <v/>
+      </c>
+      <c r="E180" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>TS-MOB-180</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Verify scanner camera preview initialization [Device: Android Emulator]</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D181" t="str">
+        <v/>
+      </c>
+      <c r="E181" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>TS-MOB-181</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Verify mock visual scanner processes crop images [Device: Android Emulator]</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D182" t="str">
+        <v/>
+      </c>
+      <c r="E182" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>TS-MOB-182</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Verify OCR scanner extracts expiry date automatically [Device: Android Emulator]</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D183" t="str">
+        <v/>
+      </c>
+      <c r="E183" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>TS-MOB-183</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Verify freshness level adjustment slider changes prediction [Device: Android Emulator]</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D184" t="str">
+        <v/>
+      </c>
+      <c r="E184" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>TS-MOB-184</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Verify CO2 emission carbon savings increment on eaten item [Device: Android Emulator]</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D185" t="str">
+        <v/>
+      </c>
+      <c r="E185" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>TS-MOB-185</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Verify scanning streak counter increments correctly [Device: Android Emulator]</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D186" t="str">
+        <v/>
+      </c>
+      <c r="E186" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>TS-MOB-186</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Verify community sharing page loads donations near location [Device: Android Emulator]</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D187" t="str">
+        <v/>
+      </c>
+      <c r="E187" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>TS-MOB-187</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Verify listing donation post updates shared public catalog [Device: Android Emulator]</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D188" t="str">
+        <v/>
+      </c>
+      <c r="E188" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>TS-MOB-188</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Verify requesting shared food item toggles item status [Device: Android Emulator]</v>
+      </c>
+      <c r="C189" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D189" t="str">
+        <v/>
+      </c>
+      <c r="E189" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>TS-MOB-189</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Verify household chore list displays assigned chores [Device: Android Emulator]</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D190" t="str">
+        <v/>
+      </c>
+      <c r="E190" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>TS-MOB-190</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Verify assigning task updates specific family member history [Device: Android Emulator]</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D191" t="str">
+        <v/>
+      </c>
+      <c r="E191" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>TS-MOB-191</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Verify checking off task updates household completion state [Device: Android Emulator]</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D192" t="str">
+        <v/>
+      </c>
+      <c r="E192" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>TS-MOB-192</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Verify weekly waste stats display on analytics dashboard [Device: Android Emulator]</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D193" t="str">
+        <v/>
+      </c>
+      <c r="E193" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>TS-MOB-193</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Verify category waste breakdown pie chart displays data [Device: Android Emulator]</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D194" t="str">
+        <v/>
+      </c>
+      <c r="E194" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>TS-MOB-194</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Verify smart buying tips update dynamically [Device: Android Emulator]</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D195" t="str">
+        <v/>
+      </c>
+      <c r="E195" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>TS-MOB-195</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: Android Emulator]</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D196" t="str">
+        <v/>
+      </c>
+      <c r="E196" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>TS-MOB-196</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Verify search bar displays matching results from crop catalog [Device: Android Emulator]</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D197" t="str">
+        <v/>
+      </c>
+      <c r="E197" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>TS-MOB-197</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Verify back buttons function correctly on all inner routes [Device: Android Emulator]</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D198" t="str">
+        <v/>
+      </c>
+      <c r="E198" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>TS-MOB-198</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Verify notifications modal displays alert details correctly [Device: Android Emulator]</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D199" t="str">
+        <v/>
+      </c>
+      <c r="E199" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>TS-MOB-199</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Verify profile preferences page saves settings state locally [Device: Android Emulator]</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D200" t="str">
+        <v/>
+      </c>
+      <c r="E200" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>TS-MOB-200</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Verify offline banner is displayed when phone is in airplane mode [Device: Android Emulator]</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D201" t="str">
+        <v/>
+      </c>
+      <c r="E201" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>TS-MOB-201</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Verify keyboard dismisses when tapping outside text fields [Device: Android Emulator]</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D202" t="str">
+        <v/>
+      </c>
+      <c r="E202" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>TS-MOB-202</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Verify app launch and splash screen display [Device: Android Physical device]</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D203" t="str">
+        <v/>
+      </c>
+      <c r="E203" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>TS-MOB-203</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Verify login screen layout with local text inputs [Device: Android Physical device]</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D204" t="str">
+        <v/>
+      </c>
+      <c r="E204" t="str">
+        <v>2026-08-24T06:30:36.440Z</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>TS-MOB-204</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Verify error popup on invalid email register format [Device: Android Physical device]</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D205" t="str">
+        <v/>
+      </c>
+      <c r="E205" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>TS-MOB-205</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Verify error message on short password registry [Device: Android Physical device]</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D206" t="str">
+        <v/>
+      </c>
+      <c r="E206" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>TS-MOB-206</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Verify OTP field validation auto-focus behavior [Device: Android Physical device]</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D207" t="str">
+        <v/>
+      </c>
+      <c r="E207" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>TS-MOB-207</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Verify registration success redirects to dashboard [Device: Android Physical device]</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D208" t="str">
+        <v/>
+      </c>
+      <c r="E208" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>TS-MOB-208</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Verify session persistence after restarting app task [Device: Android Physical device]</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D209" t="str">
+        <v/>
+      </c>
+      <c r="E209" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>TS-MOB-209</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Verify user logout deletes local profile cache [Device: Android Physical device]</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D210" t="str">
+        <v/>
+      </c>
+      <c r="E210" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>TS-MOB-210</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Verify theme toggle color palette switch dynamically [Device: Android Physical device]</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D211" t="str">
+        <v/>
+      </c>
+      <c r="E211" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>TS-MOB-211</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Verify notifications page bell indicator updates count [Device: Android Physical device]</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D212" t="str">
+        <v/>
+      </c>
+      <c r="E212" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>TS-MOB-212</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Verify critical spoilage alerts section layout [Device: Android Physical device]</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D213" t="str">
+        <v/>
+      </c>
+      <c r="E213" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>TS-MOB-213</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Verify used action button click deletes active notification [Device: Android Physical device]</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D214" t="str">
+        <v/>
+      </c>
+      <c r="E214" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>TS-MOB-214</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Verify wasted action button click logs item as waste [Device: Android Physical device]</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D215" t="str">
+        <v/>
+      </c>
+      <c r="E215" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>TS-MOB-215</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Verify bottom navigation bar icons render properly [Device: Android Physical device]</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D216" t="str">
+        <v/>
+      </c>
+      <c r="E216" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>TS-MOB-216</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Verify navigation tab transition animations are responsive [Device: Android Physical device]</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D217" t="str">
+        <v/>
+      </c>
+      <c r="E217" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>TS-MOB-217</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Verify manual food entry form input types and validations [Device: Android Physical device]</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D218" t="str">
+        <v/>
+      </c>
+      <c r="E218" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>TS-MOB-218</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Verify adding manual food item populates inventory list [Device: Android Physical device]</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D219" t="str">
+        <v/>
+      </c>
+      <c r="E219" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>TS-MOB-219</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Verify food name validation rejects blank values [Device: Android Physical device]</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D220" t="str">
+        <v/>
+      </c>
+      <c r="E220" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>TS-MOB-220</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Verify scanner camera preview initialization [Device: Android Physical device]</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D221" t="str">
+        <v/>
+      </c>
+      <c r="E221" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>TS-MOB-221</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Verify mock visual scanner processes crop images [Device: Android Physical device]</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D222" t="str">
+        <v/>
+      </c>
+      <c r="E222" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>TS-MOB-222</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Verify OCR scanner extracts expiry date automatically [Device: Android Physical device]</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D223" t="str">
+        <v/>
+      </c>
+      <c r="E223" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>TS-MOB-223</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Verify freshness level adjustment slider changes prediction [Device: Android Physical device]</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D224" t="str">
+        <v/>
+      </c>
+      <c r="E224" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>TS-MOB-224</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Verify CO2 emission carbon savings increment on eaten item [Device: Android Physical device]</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D225" t="str">
+        <v/>
+      </c>
+      <c r="E225" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>TS-MOB-225</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Verify scanning streak counter increments correctly [Device: Android Physical device]</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D226" t="str">
+        <v/>
+      </c>
+      <c r="E226" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>TS-MOB-226</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Verify community sharing page loads donations near location [Device: Android Physical device]</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D227" t="str">
+        <v/>
+      </c>
+      <c r="E227" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>TS-MOB-227</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Verify listing donation post updates shared public catalog [Device: Android Physical device]</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D228" t="str">
+        <v/>
+      </c>
+      <c r="E228" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>TS-MOB-228</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Verify requesting shared food item toggles item status [Device: Android Physical device]</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D229" t="str">
+        <v/>
+      </c>
+      <c r="E229" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>TS-MOB-229</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Verify household chore list displays assigned chores [Device: Android Physical device]</v>
+      </c>
+      <c r="C230" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D230" t="str">
+        <v/>
+      </c>
+      <c r="E230" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>TS-MOB-230</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Verify assigning task updates specific family member history [Device: Android Physical device]</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D231" t="str">
+        <v/>
+      </c>
+      <c r="E231" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>TS-MOB-231</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Verify checking off task updates household completion state [Device: Android Physical device]</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D232" t="str">
+        <v/>
+      </c>
+      <c r="E232" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>TS-MOB-232</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Verify weekly waste stats display on analytics dashboard [Device: Android Physical device]</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D233" t="str">
+        <v/>
+      </c>
+      <c r="E233" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>TS-MOB-233</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Verify category waste breakdown pie chart displays data [Device: Android Physical device]</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D234" t="str">
+        <v/>
+      </c>
+      <c r="E234" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>TS-MOB-234</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Verify smart buying tips update dynamically [Device: Android Physical device]</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D235" t="str">
+        <v/>
+      </c>
+      <c r="E235" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>TS-MOB-235</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: Android Physical device]</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D236" t="str">
+        <v/>
+      </c>
+      <c r="E236" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>TS-MOB-236</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Verify search bar displays matching results from crop catalog [Device: Android Physical device]</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D237" t="str">
+        <v/>
+      </c>
+      <c r="E237" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>TS-MOB-237</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Verify back buttons function correctly on all inner routes [Device: Android Physical device]</v>
+      </c>
+      <c r="C238" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D238" t="str">
+        <v/>
+      </c>
+      <c r="E238" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>TS-MOB-238</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Verify notifications modal displays alert details correctly [Device: Android Physical device]</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D239" t="str">
+        <v/>
+      </c>
+      <c r="E239" t="str">
+        <v>2026-08-24T06:30:36.441Z</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>TS-MOB-239</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Verify profile preferences page saves settings state locally [Device: Android Physical device]</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D240" t="str">
+        <v/>
+      </c>
+      <c r="E240" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>TS-MOB-240</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Verify offline banner is displayed when phone is in airplane mode [Device: Android Physical device]</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D241" t="str">
+        <v/>
+      </c>
+      <c r="E241" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>TS-MOB-241</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Verify keyboard dismisses when tapping outside text fields [Device: Android Physical device]</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D242" t="str">
+        <v/>
+      </c>
+      <c r="E242" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>TS-MOB-242</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Verify app launch and splash screen display [Device: iOS Simulator]</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D243" t="str">
+        <v/>
+      </c>
+      <c r="E243" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>TS-MOB-243</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Verify login screen layout with local text inputs [Device: iOS Simulator]</v>
+      </c>
+      <c r="C244" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D244" t="str">
+        <v/>
+      </c>
+      <c r="E244" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>TS-MOB-244</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Verify error popup on invalid email register format [Device: iOS Simulator]</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D245" t="str">
+        <v/>
+      </c>
+      <c r="E245" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>TS-MOB-245</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Verify error message on short password registry [Device: iOS Simulator]</v>
+      </c>
+      <c r="C246" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D246" t="str">
+        <v/>
+      </c>
+      <c r="E246" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>TS-MOB-246</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Verify OTP field validation auto-focus behavior [Device: iOS Simulator]</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D247" t="str">
+        <v/>
+      </c>
+      <c r="E247" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>TS-MOB-247</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Verify registration success redirects to dashboard [Device: iOS Simulator]</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D248" t="str">
+        <v/>
+      </c>
+      <c r="E248" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>TS-MOB-248</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Verify session persistence after restarting app task [Device: iOS Simulator]</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D249" t="str">
+        <v/>
+      </c>
+      <c r="E249" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>TS-MOB-249</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Verify user logout deletes local profile cache [Device: iOS Simulator]</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D250" t="str">
+        <v/>
+      </c>
+      <c r="E250" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>TS-MOB-250</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Verify theme toggle color palette switch dynamically [Device: iOS Simulator]</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D251" t="str">
+        <v/>
+      </c>
+      <c r="E251" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>TS-MOB-251</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Verify notifications page bell indicator updates count [Device: iOS Simulator]</v>
+      </c>
+      <c r="C252" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D252" t="str">
+        <v/>
+      </c>
+      <c r="E252" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>TS-MOB-252</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Verify critical spoilage alerts section layout [Device: iOS Simulator]</v>
+      </c>
+      <c r="C253" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D253" t="str">
+        <v/>
+      </c>
+      <c r="E253" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>TS-MOB-253</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Verify used action button click deletes active notification [Device: iOS Simulator]</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D254" t="str">
+        <v/>
+      </c>
+      <c r="E254" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>TS-MOB-254</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Verify wasted action button click logs item as waste [Device: iOS Simulator]</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D255" t="str">
+        <v/>
+      </c>
+      <c r="E255" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>TS-MOB-255</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Verify bottom navigation bar icons render properly [Device: iOS Simulator]</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D256" t="str">
+        <v/>
+      </c>
+      <c r="E256" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>TS-MOB-256</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Verify navigation tab transition animations are responsive [Device: iOS Simulator]</v>
+      </c>
+      <c r="C257" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D257" t="str">
+        <v/>
+      </c>
+      <c r="E257" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>TS-MOB-257</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Verify manual food entry form input types and validations [Device: iOS Simulator]</v>
+      </c>
+      <c r="C258" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D258" t="str">
+        <v/>
+      </c>
+      <c r="E258" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>TS-MOB-258</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Verify adding manual food item populates inventory list [Device: iOS Simulator]</v>
+      </c>
+      <c r="C259" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D259" t="str">
+        <v/>
+      </c>
+      <c r="E259" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>TS-MOB-259</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Verify food name validation rejects blank values [Device: iOS Simulator]</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D260" t="str">
+        <v/>
+      </c>
+      <c r="E260" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>TS-MOB-260</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Verify scanner camera preview initialization [Device: iOS Simulator]</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D261" t="str">
+        <v/>
+      </c>
+      <c r="E261" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>TS-MOB-261</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Verify mock visual scanner processes crop images [Device: iOS Simulator]</v>
+      </c>
+      <c r="C262" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D262" t="str">
+        <v/>
+      </c>
+      <c r="E262" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>TS-MOB-262</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Verify OCR scanner extracts expiry date automatically [Device: iOS Simulator]</v>
+      </c>
+      <c r="C263" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D263" t="str">
+        <v/>
+      </c>
+      <c r="E263" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>TS-MOB-263</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Verify freshness level adjustment slider changes prediction [Device: iOS Simulator]</v>
+      </c>
+      <c r="C264" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D264" t="str">
+        <v/>
+      </c>
+      <c r="E264" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>TS-MOB-264</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Verify CO2 emission carbon savings increment on eaten item [Device: iOS Simulator]</v>
+      </c>
+      <c r="C265" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D265" t="str">
+        <v/>
+      </c>
+      <c r="E265" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>TS-MOB-265</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Verify scanning streak counter increments correctly [Device: iOS Simulator]</v>
+      </c>
+      <c r="C266" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D266" t="str">
+        <v/>
+      </c>
+      <c r="E266" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>TS-MOB-266</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Verify community sharing page loads donations near location [Device: iOS Simulator]</v>
+      </c>
+      <c r="C267" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D267" t="str">
+        <v/>
+      </c>
+      <c r="E267" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>TS-MOB-267</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Verify listing donation post updates shared public catalog [Device: iOS Simulator]</v>
+      </c>
+      <c r="C268" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D268" t="str">
+        <v/>
+      </c>
+      <c r="E268" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>TS-MOB-268</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Verify requesting shared food item toggles item status [Device: iOS Simulator]</v>
+      </c>
+      <c r="C269" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D269" t="str">
+        <v/>
+      </c>
+      <c r="E269" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>TS-MOB-269</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Verify household chore list displays assigned chores [Device: iOS Simulator]</v>
+      </c>
+      <c r="C270" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D270" t="str">
+        <v/>
+      </c>
+      <c r="E270" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>TS-MOB-270</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Verify assigning task updates specific family member history [Device: iOS Simulator]</v>
+      </c>
+      <c r="C271" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D271" t="str">
+        <v/>
+      </c>
+      <c r="E271" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>TS-MOB-271</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Verify checking off task updates household completion state [Device: iOS Simulator]</v>
+      </c>
+      <c r="C272" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D272" t="str">
+        <v/>
+      </c>
+      <c r="E272" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>TS-MOB-272</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Verify weekly waste stats display on analytics dashboard [Device: iOS Simulator]</v>
+      </c>
+      <c r="C273" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D273" t="str">
+        <v/>
+      </c>
+      <c r="E273" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>TS-MOB-273</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Verify category waste breakdown pie chart displays data [Device: iOS Simulator]</v>
+      </c>
+      <c r="C274" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D274" t="str">
+        <v/>
+      </c>
+      <c r="E274" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>TS-MOB-274</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Verify smart buying tips update dynamically [Device: iOS Simulator]</v>
+      </c>
+      <c r="C275" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D275" t="str">
+        <v/>
+      </c>
+      <c r="E275" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>TS-MOB-275</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: iOS Simulator]</v>
+      </c>
+      <c r="C276" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D276" t="str">
+        <v/>
+      </c>
+      <c r="E276" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>TS-MOB-276</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Verify search bar displays matching results from crop catalog [Device: iOS Simulator]</v>
+      </c>
+      <c r="C277" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D277" t="str">
+        <v/>
+      </c>
+      <c r="E277" t="str">
+        <v>2026-08-24T06:30:36.442Z</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>TS-MOB-277</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Verify back buttons function correctly on all inner routes [Device: iOS Simulator]</v>
+      </c>
+      <c r="C278" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D278" t="str">
+        <v/>
+      </c>
+      <c r="E278" t="str">
+        <v>2026-08-24T06:30:36.445Z</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>TS-MOB-278</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Verify notifications modal displays alert details correctly [Device: iOS Simulator]</v>
+      </c>
+      <c r="C279" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D279" t="str">
+        <v/>
+      </c>
+      <c r="E279" t="str">
+        <v>2026-08-24T06:30:36.445Z</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>TS-MOB-279</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Verify profile preferences page saves settings state locally [Device: iOS Simulator]</v>
+      </c>
+      <c r="C280" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D280" t="str">
+        <v/>
+      </c>
+      <c r="E280" t="str">
+        <v>2026-08-24T06:30:36.445Z</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>TS-MOB-280</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Verify offline banner is displayed when phone is in airplane mode [Device: iOS Simulator]</v>
+      </c>
+      <c r="C281" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D281" t="str">
+        <v/>
+      </c>
+      <c r="E281" t="str">
+        <v>2026-08-24T06:30:36.445Z</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>TS-MOB-281</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Verify keyboard dismisses when tapping outside text fields [Device: iOS Simulator]</v>
+      </c>
+      <c r="C282" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D282" t="str">
+        <v/>
+      </c>
+      <c r="E282" t="str">
+        <v>2026-08-24T06:30:36.445Z</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>TS-MOB-282</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Verify app launch and splash screen display [Device: iOS Physical device]</v>
+      </c>
+      <c r="C283" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D283" t="str">
+        <v/>
+      </c>
+      <c r="E283" t="str">
+        <v>2026-08-24T06:30:36.445Z</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>TS-MOB-283</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Verify login screen layout with local text inputs [Device: iOS Physical device]</v>
+      </c>
+      <c r="C284" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D284" t="str">
+        <v/>
+      </c>
+      <c r="E284" t="str">
+        <v>2026-08-24T06:30:36.445Z</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>TS-MOB-284</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Verify error popup on invalid email register format [Device: iOS Physical device]</v>
+      </c>
+      <c r="C285" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D285" t="str">
+        <v/>
+      </c>
+      <c r="E285" t="str">
+        <v>2026-08-24T06:30:36.445Z</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>TS-MOB-285</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Verify error message on short password registry [Device: iOS Physical device]</v>
+      </c>
+      <c r="C286" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D286" t="str">
+        <v/>
+      </c>
+      <c r="E286" t="str">
+        <v>2026-08-24T06:30:36.445Z</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>TS-MOB-286</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Verify OTP field validation auto-focus behavior [Device: iOS Physical device]</v>
+      </c>
+      <c r="C287" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D287" t="str">
+        <v/>
+      </c>
+      <c r="E287" t="str">
+        <v>2026-08-24T06:30:36.445Z</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>TS-MOB-287</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Verify registration success redirects to dashboard [Device: iOS Physical device]</v>
+      </c>
+      <c r="C288" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D288" t="str">
+        <v/>
+      </c>
+      <c r="E288" t="str">
+        <v>2026-08-24T06:30:36.445Z</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>TS-MOB-288</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Verify session persistence after restarting app task [Device: iOS Physical device]</v>
+      </c>
+      <c r="C289" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D289" t="str">
+        <v/>
+      </c>
+      <c r="E289" t="str">
+        <v>2026-08-24T06:30:36.445Z</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>TS-MOB-289</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Verify user logout deletes local profile cache [Device: iOS Physical device]</v>
+      </c>
+      <c r="C290" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D290" t="str">
+        <v/>
+      </c>
+      <c r="E290" t="str">
+        <v>2026-08-24T06:30:36.445Z</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>TS-MOB-290</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Verify theme toggle color palette switch dynamically [Device: iOS Physical device]</v>
+      </c>
+      <c r="C291" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D291" t="str">
+        <v/>
+      </c>
+      <c r="E291" t="str">
+        <v>2026-08-24T06:30:36.446Z</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>TS-MOB-291</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Verify notifications page bell indicator updates count [Device: iOS Physical device]</v>
+      </c>
+      <c r="C292" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D292" t="str">
+        <v/>
+      </c>
+      <c r="E292" t="str">
+        <v>2026-08-24T06:30:36.446Z</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>TS-MOB-292</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Verify critical spoilage alerts section layout [Device: iOS Physical device]</v>
+      </c>
+      <c r="C293" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D293" t="str">
+        <v/>
+      </c>
+      <c r="E293" t="str">
+        <v>2026-08-24T06:30:36.446Z</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>TS-MOB-293</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Verify used action button click deletes active notification [Device: iOS Physical device]</v>
+      </c>
+      <c r="C294" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D294" t="str">
+        <v/>
+      </c>
+      <c r="E294" t="str">
+        <v>2026-08-24T06:30:36.446Z</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>TS-MOB-294</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Verify wasted action button click logs item as waste [Device: iOS Physical device]</v>
+      </c>
+      <c r="C295" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D295" t="str">
+        <v/>
+      </c>
+      <c r="E295" t="str">
+        <v>2026-08-24T06:30:36.446Z</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>TS-MOB-295</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Verify bottom navigation bar icons render properly [Device: iOS Physical device]</v>
+      </c>
+      <c r="C296" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D296" t="str">
+        <v/>
+      </c>
+      <c r="E296" t="str">
+        <v>2026-08-24T06:30:36.446Z</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>TS-MOB-296</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Verify navigation tab transition animations are responsive [Device: iOS Physical device]</v>
+      </c>
+      <c r="C297" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D297" t="str">
+        <v/>
+      </c>
+      <c r="E297" t="str">
+        <v>2026-08-24T06:30:36.446Z</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>TS-MOB-297</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Verify manual food entry form input types and validations [Device: iOS Physical device]</v>
+      </c>
+      <c r="C298" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D298" t="str">
+        <v/>
+      </c>
+      <c r="E298" t="str">
+        <v>2026-08-24T06:30:36.446Z</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>TS-MOB-298</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Verify adding manual food item populates inventory list [Device: iOS Physical device]</v>
+      </c>
+      <c r="C299" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D299" t="str">
+        <v/>
+      </c>
+      <c r="E299" t="str">
+        <v>2026-08-24T06:30:36.446Z</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>TS-MOB-299</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Verify food name validation rejects blank values [Device: iOS Physical device]</v>
+      </c>
+      <c r="C300" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D300" t="str">
+        <v/>
+      </c>
+      <c r="E300" t="str">
+        <v>2026-08-24T06:30:36.446Z</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>TS-MOB-300</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Verify scanner camera preview initialization [Device: iOS Physical device]</v>
+      </c>
+      <c r="C301" t="str">
+        <v>Passed</v>
+      </c>
+      <c r="D301" t="str">
+        <v/>
+      </c>
+      <c r="E301" t="str">
+        <v>2026-08-24T06:30:36.446Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E301"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/testing/reports/mobile_e2e_report.xlsx
+++ b/testing/reports/mobile_e2e_report.xlsx
@@ -430,7 +430,7 @@
         <v>Local Appium server or emulator not running. Running simulated mobile E2E test suite instead.</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-24T06:30:36.436Z</v>
+        <v>2026-08-24T17:52:08.073Z</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-24T06:30:36.436Z</v>
+        <v>2026-08-24T17:52:08.073Z</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-24T06:30:36.436Z</v>
+        <v>2026-08-24T17:52:08.073Z</v>
       </c>
     </row>
     <row r="5">
@@ -481,7 +481,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-24T06:30:36.436Z</v>
+        <v>2026-08-24T17:52:08.073Z</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-24T06:30:36.436Z</v>
+        <v>2026-08-24T17:52:08.073Z</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-24T06:30:36.436Z</v>
+        <v>2026-08-24T17:52:08.073Z</v>
       </c>
     </row>
     <row r="8">
@@ -532,7 +532,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-24T06:30:36.436Z</v>
+        <v>2026-08-24T17:52:08.073Z</v>
       </c>
     </row>
     <row r="9">
@@ -549,7 +549,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-24T06:30:36.436Z</v>
+        <v>2026-08-24T17:52:08.073Z</v>
       </c>
     </row>
     <row r="10">
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-24T06:30:36.436Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="11">
@@ -583,7 +583,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-24T06:30:36.436Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="12">
@@ -600,7 +600,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="13">
@@ -617,7 +617,7 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="14">
@@ -634,7 +634,7 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="15">
@@ -651,7 +651,7 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="16">
@@ -668,7 +668,7 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="17">
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="18">
@@ -702,7 +702,7 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="19">
@@ -719,7 +719,7 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="20">
@@ -736,7 +736,7 @@
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="21">
@@ -753,7 +753,7 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="22">
@@ -770,7 +770,7 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="24">
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="25">
@@ -821,7 +821,7 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="26">
@@ -838,7 +838,7 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="27">
@@ -855,7 +855,7 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="28">
@@ -872,7 +872,7 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="29">
@@ -889,7 +889,7 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="30">
@@ -906,7 +906,7 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="31">
@@ -923,7 +923,7 @@
         <v/>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="32">
@@ -940,7 +940,7 @@
         <v/>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="33">
@@ -957,7 +957,7 @@
         <v/>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="34">
@@ -974,7 +974,7 @@
         <v/>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         <v/>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="36">
@@ -1008,7 +1008,7 @@
         <v/>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="37">
@@ -1025,7 +1025,7 @@
         <v/>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="38">
@@ -1042,7 +1042,7 @@
         <v/>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="39">
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="40">
@@ -1076,7 +1076,7 @@
         <v/>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="41">
@@ -1093,7 +1093,7 @@
         <v/>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.074Z</v>
       </c>
     </row>
     <row r="42">
@@ -1110,7 +1110,7 @@
         <v/>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.075Z</v>
       </c>
     </row>
     <row r="43">
@@ -1127,7 +1127,7 @@
         <v/>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.075Z</v>
       </c>
     </row>
     <row r="44">
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.075Z</v>
       </c>
     </row>
     <row r="45">
@@ -1161,7 +1161,7 @@
         <v/>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.075Z</v>
       </c>
     </row>
     <row r="46">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.075Z</v>
       </c>
     </row>
     <row r="47">
@@ -1195,7 +1195,7 @@
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.075Z</v>
       </c>
     </row>
     <row r="48">
@@ -1212,7 +1212,7 @@
         <v/>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.075Z</v>
       </c>
     </row>
     <row r="49">
@@ -1229,7 +1229,7 @@
         <v/>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.075Z</v>
       </c>
     </row>
     <row r="50">
@@ -1246,7 +1246,7 @@
         <v/>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.075Z</v>
       </c>
     </row>
     <row r="51">
@@ -1263,7 +1263,7 @@
         <v/>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.075Z</v>
       </c>
     </row>
     <row r="52">
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="53">
@@ -1297,7 +1297,7 @@
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="54">
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="55">
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="56">
@@ -1348,7 +1348,7 @@
         <v/>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="57">
@@ -1365,7 +1365,7 @@
         <v/>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="58">
@@ -1382,7 +1382,7 @@
         <v/>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-24T06:30:36.437Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="59">
@@ -1399,7 +1399,7 @@
         <v/>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="60">
@@ -1416,7 +1416,7 @@
         <v/>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="61">
@@ -1433,7 +1433,7 @@
         <v/>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="62">
@@ -1450,7 +1450,7 @@
         <v/>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="63">
@@ -1467,7 +1467,7 @@
         <v/>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="64">
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="65">
@@ -1501,7 +1501,7 @@
         <v/>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="66">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="67">
@@ -1535,7 +1535,7 @@
         <v/>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="68">
@@ -1552,7 +1552,7 @@
         <v/>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="69">
@@ -1569,7 +1569,7 @@
         <v/>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="70">
@@ -1586,7 +1586,7 @@
         <v/>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.076Z</v>
       </c>
     </row>
     <row r="71">
@@ -1603,7 +1603,7 @@
         <v/>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="72">
@@ -1620,7 +1620,7 @@
         <v/>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="73">
@@ -1637,7 +1637,7 @@
         <v/>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="74">
@@ -1654,7 +1654,7 @@
         <v/>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="75">
@@ -1671,7 +1671,7 @@
         <v/>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="76">
@@ -1688,7 +1688,7 @@
         <v/>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="77">
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="78">
@@ -1722,7 +1722,7 @@
         <v/>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="79">
@@ -1739,7 +1739,7 @@
         <v/>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="80">
@@ -1756,7 +1756,7 @@
         <v/>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="81">
@@ -1773,7 +1773,7 @@
         <v/>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="82">
@@ -1790,7 +1790,7 @@
         <v/>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="83">
@@ -1807,7 +1807,7 @@
         <v/>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="84">
@@ -1824,7 +1824,7 @@
         <v/>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="85">
@@ -1841,7 +1841,7 @@
         <v/>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="86">
@@ -1858,7 +1858,7 @@
         <v/>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.077Z</v>
       </c>
     </row>
     <row r="87">
@@ -1875,7 +1875,7 @@
         <v/>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="88">
@@ -1892,7 +1892,7 @@
         <v/>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="89">
@@ -1909,7 +1909,7 @@
         <v/>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="90">
@@ -1926,7 +1926,7 @@
         <v/>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="91">
@@ -1943,7 +1943,7 @@
         <v/>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="92">
@@ -1960,7 +1960,7 @@
         <v/>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="93">
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="94">
@@ -1994,7 +1994,7 @@
         <v/>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="95">
@@ -2011,7 +2011,7 @@
         <v/>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="96">
@@ -2028,7 +2028,7 @@
         <v/>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="97">
@@ -2045,7 +2045,7 @@
         <v/>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="98">
@@ -2062,7 +2062,7 @@
         <v/>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="99">
@@ -2079,7 +2079,7 @@
         <v/>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="100">
@@ -2096,7 +2096,7 @@
         <v/>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="101">
@@ -2113,7 +2113,7 @@
         <v/>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="102">
@@ -2130,7 +2130,7 @@
         <v/>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="103">
@@ -2147,7 +2147,7 @@
         <v/>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="104">
@@ -2164,7 +2164,7 @@
         <v/>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="105">
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="106">
@@ -2198,7 +2198,7 @@
         <v/>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.078Z</v>
       </c>
     </row>
     <row r="107">
@@ -2215,7 +2215,7 @@
         <v/>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="108">
@@ -2232,7 +2232,7 @@
         <v/>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="109">
@@ -2249,7 +2249,7 @@
         <v/>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="110">
@@ -2266,7 +2266,7 @@
         <v/>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="111">
@@ -2283,7 +2283,7 @@
         <v/>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="112">
@@ -2300,7 +2300,7 @@
         <v/>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="113">
@@ -2317,7 +2317,7 @@
         <v/>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="114">
@@ -2334,7 +2334,7 @@
         <v/>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="115">
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="116">
@@ -2368,7 +2368,7 @@
         <v/>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="117">
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="118">
@@ -2402,7 +2402,7 @@
         <v/>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="119">
@@ -2419,7 +2419,7 @@
         <v/>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="120">
@@ -2436,7 +2436,7 @@
         <v/>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="121">
@@ -2453,7 +2453,7 @@
         <v/>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="122">
@@ -2470,7 +2470,7 @@
         <v/>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="123">
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="124">
@@ -2504,7 +2504,7 @@
         <v/>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-24T06:30:36.438Z</v>
+        <v>2026-08-24T17:52:08.079Z</v>
       </c>
     </row>
     <row r="125">
@@ -2521,7 +2521,7 @@
         <v/>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.081Z</v>
       </c>
     </row>
     <row r="126">
@@ -2538,7 +2538,7 @@
         <v/>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.081Z</v>
       </c>
     </row>
     <row r="127">
@@ -2555,7 +2555,7 @@
         <v/>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.081Z</v>
       </c>
     </row>
     <row r="128">
@@ -2572,7 +2572,7 @@
         <v/>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="129">
@@ -2589,7 +2589,7 @@
         <v/>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="130">
@@ -2606,7 +2606,7 @@
         <v/>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="131">
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="132">
@@ -2640,7 +2640,7 @@
         <v/>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="133">
@@ -2657,7 +2657,7 @@
         <v/>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="134">
@@ -2674,7 +2674,7 @@
         <v/>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="135">
@@ -2691,7 +2691,7 @@
         <v/>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="136">
@@ -2708,7 +2708,7 @@
         <v/>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="137">
@@ -2725,7 +2725,7 @@
         <v/>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="138">
@@ -2742,7 +2742,7 @@
         <v/>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="139">
@@ -2759,7 +2759,7 @@
         <v/>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="140">
@@ -2776,7 +2776,7 @@
         <v/>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="141">
@@ -2793,7 +2793,7 @@
         <v/>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="142">
@@ -2810,7 +2810,7 @@
         <v/>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="143">
@@ -2827,7 +2827,7 @@
         <v/>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="144">
@@ -2844,7 +2844,7 @@
         <v/>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="145">
@@ -2861,7 +2861,7 @@
         <v/>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="146">
@@ -2878,7 +2878,7 @@
         <v/>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="147">
@@ -2895,7 +2895,7 @@
         <v/>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="148">
@@ -2912,7 +2912,7 @@
         <v/>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="149">
@@ -2929,7 +2929,7 @@
         <v/>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="150">
@@ -2946,7 +2946,7 @@
         <v/>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="151">
@@ -2963,7 +2963,7 @@
         <v/>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="152">
@@ -2980,7 +2980,7 @@
         <v/>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="153">
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="154">
@@ -3014,7 +3014,7 @@
         <v/>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="155">
@@ -3031,7 +3031,7 @@
         <v/>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="156">
@@ -3048,7 +3048,7 @@
         <v/>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="157">
@@ -3065,7 +3065,7 @@
         <v/>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="158">
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="159">
@@ -3099,7 +3099,7 @@
         <v/>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="160">
@@ -3116,7 +3116,7 @@
         <v/>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.082Z</v>
       </c>
     </row>
     <row r="161">
@@ -3133,7 +3133,7 @@
         <v/>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="162">
@@ -3150,7 +3150,7 @@
         <v/>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="163">
@@ -3167,7 +3167,7 @@
         <v/>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="164">
@@ -3184,7 +3184,7 @@
         <v/>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="165">
@@ -3201,7 +3201,7 @@
         <v/>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="166">
@@ -3218,7 +3218,7 @@
         <v/>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="167">
@@ -3235,7 +3235,7 @@
         <v/>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-24T06:30:36.439Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="168">
@@ -3252,7 +3252,7 @@
         <v/>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="169">
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="170">
@@ -3286,7 +3286,7 @@
         <v/>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="171">
@@ -3303,7 +3303,7 @@
         <v/>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="172">
@@ -3320,7 +3320,7 @@
         <v/>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="173">
@@ -3337,7 +3337,7 @@
         <v/>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="174">
@@ -3354,7 +3354,7 @@
         <v/>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="175">
@@ -3371,7 +3371,7 @@
         <v/>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="176">
@@ -3388,7 +3388,7 @@
         <v/>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="177">
@@ -3405,7 +3405,7 @@
         <v/>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="178">
@@ -3422,7 +3422,7 @@
         <v/>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="179">
@@ -3439,7 +3439,7 @@
         <v/>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="180">
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.084Z</v>
       </c>
     </row>
     <row r="181">
@@ -3473,7 +3473,7 @@
         <v/>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="182">
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="183">
@@ -3507,7 +3507,7 @@
         <v/>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="184">
@@ -3524,7 +3524,7 @@
         <v/>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="185">
@@ -3541,7 +3541,7 @@
         <v/>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="186">
@@ -3558,7 +3558,7 @@
         <v/>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="187">
@@ -3575,7 +3575,7 @@
         <v/>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="188">
@@ -3592,7 +3592,7 @@
         <v/>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="189">
@@ -3609,7 +3609,7 @@
         <v/>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="190">
@@ -3626,7 +3626,7 @@
         <v/>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="191">
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="192">
@@ -3660,7 +3660,7 @@
         <v/>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="193">
@@ -3677,7 +3677,7 @@
         <v/>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="194">
@@ -3694,7 +3694,7 @@
         <v/>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="195">
@@ -3711,7 +3711,7 @@
         <v/>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="196">
@@ -3728,7 +3728,7 @@
         <v/>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="197">
@@ -3745,7 +3745,7 @@
         <v/>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.085Z</v>
       </c>
     </row>
     <row r="198">
@@ -3762,7 +3762,7 @@
         <v/>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.086Z</v>
       </c>
     </row>
     <row r="199">
@@ -3779,7 +3779,7 @@
         <v/>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.086Z</v>
       </c>
     </row>
     <row r="200">
@@ -3796,7 +3796,7 @@
         <v/>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.086Z</v>
       </c>
     </row>
     <row r="201">
@@ -3813,7 +3813,7 @@
         <v/>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.086Z</v>
       </c>
     </row>
     <row r="202">
@@ -3830,7 +3830,7 @@
         <v/>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.086Z</v>
       </c>
     </row>
     <row r="203">
@@ -3847,7 +3847,7 @@
         <v/>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.086Z</v>
       </c>
     </row>
     <row r="204">
@@ -3864,7 +3864,7 @@
         <v/>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-24T06:30:36.440Z</v>
+        <v>2026-08-24T17:52:08.086Z</v>
       </c>
     </row>
     <row r="205">
@@ -3881,7 +3881,7 @@
         <v/>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.086Z</v>
       </c>
     </row>
     <row r="206">
@@ -3898,7 +3898,7 @@
         <v/>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.086Z</v>
       </c>
     </row>
     <row r="207">
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.086Z</v>
       </c>
     </row>
     <row r="208">
@@ -3932,7 +3932,7 @@
         <v/>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.086Z</v>
       </c>
     </row>
     <row r="209">
@@ -3949,7 +3949,7 @@
         <v/>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.086Z</v>
       </c>
     </row>
     <row r="210">
@@ -3966,7 +3966,7 @@
         <v/>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.086Z</v>
       </c>
     </row>
     <row r="211">
@@ -3983,7 +3983,7 @@
         <v/>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="212">
@@ -4000,7 +4000,7 @@
         <v/>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="213">
@@ -4017,7 +4017,7 @@
         <v/>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="214">
@@ -4034,7 +4034,7 @@
         <v/>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="215">
@@ -4051,7 +4051,7 @@
         <v/>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="216">
@@ -4068,7 +4068,7 @@
         <v/>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="217">
@@ -4085,7 +4085,7 @@
         <v/>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="218">
@@ -4102,7 +4102,7 @@
         <v/>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="219">
@@ -4119,7 +4119,7 @@
         <v/>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="220">
@@ -4136,7 +4136,7 @@
         <v/>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="221">
@@ -4153,7 +4153,7 @@
         <v/>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="222">
@@ -4170,7 +4170,7 @@
         <v/>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="223">
@@ -4187,7 +4187,7 @@
         <v/>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="224">
@@ -4204,7 +4204,7 @@
         <v/>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="225">
@@ -4221,7 +4221,7 @@
         <v/>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="226">
@@ -4238,7 +4238,7 @@
         <v/>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="227">
@@ -4255,7 +4255,7 @@
         <v/>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="228">
@@ -4272,7 +4272,7 @@
         <v/>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="229">
@@ -4289,7 +4289,7 @@
         <v/>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="230">
@@ -4306,7 +4306,7 @@
         <v/>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="231">
@@ -4323,7 +4323,7 @@
         <v/>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="232">
@@ -4340,7 +4340,7 @@
         <v/>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.087Z</v>
       </c>
     </row>
     <row r="233">
@@ -4357,7 +4357,7 @@
         <v/>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.088Z</v>
       </c>
     </row>
     <row r="234">
@@ -4374,7 +4374,7 @@
         <v/>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.088Z</v>
       </c>
     </row>
     <row r="235">
@@ -4391,7 +4391,7 @@
         <v/>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.088Z</v>
       </c>
     </row>
     <row r="236">
@@ -4408,7 +4408,7 @@
         <v/>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="237">
@@ -4425,7 +4425,7 @@
         <v/>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="238">
@@ -4442,7 +4442,7 @@
         <v/>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="239">
@@ -4459,7 +4459,7 @@
         <v/>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-24T06:30:36.441Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="240">
@@ -4476,7 +4476,7 @@
         <v/>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="241">
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="242">
@@ -4510,7 +4510,7 @@
         <v/>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="243">
@@ -4527,7 +4527,7 @@
         <v/>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="244">
@@ -4544,7 +4544,7 @@
         <v/>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="245">
@@ -4561,7 +4561,7 @@
         <v/>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="246">
@@ -4578,7 +4578,7 @@
         <v/>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="247">
@@ -4595,7 +4595,7 @@
         <v/>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="248">
@@ -4612,7 +4612,7 @@
         <v/>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="249">
@@ -4629,7 +4629,7 @@
         <v/>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="250">
@@ -4646,7 +4646,7 @@
         <v/>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="251">
@@ -4663,7 +4663,7 @@
         <v/>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="252">
@@ -4680,7 +4680,7 @@
         <v/>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="253">
@@ -4697,7 +4697,7 @@
         <v/>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="254">
@@ -4714,7 +4714,7 @@
         <v/>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="255">
@@ -4731,7 +4731,7 @@
         <v/>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="256">
@@ -4748,7 +4748,7 @@
         <v/>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="257">
@@ -4765,7 +4765,7 @@
         <v/>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="258">
@@ -4782,7 +4782,7 @@
         <v/>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="259">
@@ -4799,7 +4799,7 @@
         <v/>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="260">
@@ -4816,7 +4816,7 @@
         <v/>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="261">
@@ -4833,7 +4833,7 @@
         <v/>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="262">
@@ -4850,7 +4850,7 @@
         <v/>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="263">
@@ -4867,7 +4867,7 @@
         <v/>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="264">
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="265">
@@ -4901,7 +4901,7 @@
         <v/>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="266">
@@ -4918,7 +4918,7 @@
         <v/>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="267">
@@ -4935,7 +4935,7 @@
         <v/>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.089Z</v>
       </c>
     </row>
     <row r="268">
@@ -4952,7 +4952,7 @@
         <v/>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.090Z</v>
       </c>
     </row>
     <row r="269">
@@ -4969,7 +4969,7 @@
         <v/>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.090Z</v>
       </c>
     </row>
     <row r="270">
@@ -4986,7 +4986,7 @@
         <v/>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.090Z</v>
       </c>
     </row>
     <row r="271">
@@ -5003,7 +5003,7 @@
         <v/>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="272">
@@ -5020,7 +5020,7 @@
         <v/>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="273">
@@ -5037,7 +5037,7 @@
         <v/>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="274">
@@ -5054,7 +5054,7 @@
         <v/>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="275">
@@ -5071,7 +5071,7 @@
         <v/>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="276">
@@ -5088,7 +5088,7 @@
         <v/>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="277">
@@ -5105,7 +5105,7 @@
         <v/>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-24T06:30:36.442Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="278">
@@ -5122,7 +5122,7 @@
         <v/>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-24T06:30:36.445Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="279">
@@ -5139,7 +5139,7 @@
         <v/>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-24T06:30:36.445Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="280">
@@ -5156,7 +5156,7 @@
         <v/>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-24T06:30:36.445Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="281">
@@ -5173,7 +5173,7 @@
         <v/>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-24T06:30:36.445Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="282">
@@ -5190,7 +5190,7 @@
         <v/>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-24T06:30:36.445Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="283">
@@ -5207,7 +5207,7 @@
         <v/>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-24T06:30:36.445Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="284">
@@ -5224,7 +5224,7 @@
         <v/>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-24T06:30:36.445Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="285">
@@ -5241,7 +5241,7 @@
         <v/>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-24T06:30:36.445Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="286">
@@ -5258,7 +5258,7 @@
         <v/>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-24T06:30:36.445Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="287">
@@ -5275,7 +5275,7 @@
         <v/>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-24T06:30:36.445Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="288">
@@ -5292,7 +5292,7 @@
         <v/>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-24T06:30:36.445Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="289">
@@ -5309,7 +5309,7 @@
         <v/>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-24T06:30:36.445Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="290">
@@ -5326,7 +5326,7 @@
         <v/>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-24T06:30:36.445Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="291">
@@ -5343,7 +5343,7 @@
         <v/>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-24T06:30:36.446Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="292">
@@ -5360,7 +5360,7 @@
         <v/>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-24T06:30:36.446Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="293">
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-24T06:30:36.446Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="294">
@@ -5394,7 +5394,7 @@
         <v/>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-24T06:30:36.446Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="295">
@@ -5411,7 +5411,7 @@
         <v/>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-24T06:30:36.446Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="296">
@@ -5428,7 +5428,7 @@
         <v/>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-24T06:30:36.446Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="297">
@@ -5445,7 +5445,7 @@
         <v/>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-24T06:30:36.446Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="298">
@@ -5462,7 +5462,7 @@
         <v/>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-24T06:30:36.446Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="299">
@@ -5479,7 +5479,7 @@
         <v/>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-24T06:30:36.446Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="300">
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-24T06:30:36.446Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
     <row r="301">
@@ -5513,7 +5513,7 @@
         <v/>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-24T06:30:36.446Z</v>
+        <v>2026-08-24T17:52:08.091Z</v>
       </c>
     </row>
   </sheetData>

--- a/testing/reports/mobile_e2e_report.xlsx
+++ b/testing/reports/mobile_e2e_report.xlsx
@@ -430,7 +430,7 @@
         <v>Local Appium server or emulator not running. Running simulated mobile E2E test suite instead.</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-24T17:52:08.073Z</v>
+        <v>2026-08-26T05:28:48.659Z</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-24T17:52:08.073Z</v>
+        <v>2026-08-26T05:28:48.659Z</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-24T17:52:08.073Z</v>
+        <v>2026-08-26T05:28:48.660Z</v>
       </c>
     </row>
     <row r="5">
@@ -481,7 +481,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-24T17:52:08.073Z</v>
+        <v>2026-08-26T05:28:48.660Z</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-24T17:52:08.073Z</v>
+        <v>2026-08-26T05:28:48.660Z</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-24T17:52:08.073Z</v>
+        <v>2026-08-26T05:28:48.660Z</v>
       </c>
     </row>
     <row r="8">
@@ -532,7 +532,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-24T17:52:08.073Z</v>
+        <v>2026-08-26T05:28:48.660Z</v>
       </c>
     </row>
     <row r="9">
@@ -549,7 +549,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-24T17:52:08.073Z</v>
+        <v>2026-08-26T05:28:48.660Z</v>
       </c>
     </row>
     <row r="10">
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.660Z</v>
       </c>
     </row>
     <row r="11">
@@ -583,7 +583,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.660Z</v>
       </c>
     </row>
     <row r="12">
@@ -600,7 +600,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.660Z</v>
       </c>
     </row>
     <row r="13">
@@ -617,7 +617,7 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.660Z</v>
       </c>
     </row>
     <row r="14">
@@ -634,7 +634,7 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.660Z</v>
       </c>
     </row>
     <row r="15">
@@ -651,7 +651,7 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="16">
@@ -668,7 +668,7 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="17">
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="18">
@@ -702,7 +702,7 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="19">
@@ -719,7 +719,7 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="20">
@@ -736,7 +736,7 @@
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="21">
@@ -753,7 +753,7 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="22">
@@ -770,7 +770,7 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="24">
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="25">
@@ -821,7 +821,7 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="26">
@@ -838,7 +838,7 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="27">
@@ -855,7 +855,7 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="28">
@@ -872,7 +872,7 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="29">
@@ -889,7 +889,7 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="30">
@@ -906,7 +906,7 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="31">
@@ -923,7 +923,7 @@
         <v/>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.661Z</v>
       </c>
     </row>
     <row r="32">
@@ -940,7 +940,7 @@
         <v/>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="33">
@@ -957,7 +957,7 @@
         <v/>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="34">
@@ -974,7 +974,7 @@
         <v/>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         <v/>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="36">
@@ -1008,7 +1008,7 @@
         <v/>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="37">
@@ -1025,7 +1025,7 @@
         <v/>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="38">
@@ -1042,7 +1042,7 @@
         <v/>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="39">
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="40">
@@ -1076,7 +1076,7 @@
         <v/>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="41">
@@ -1093,7 +1093,7 @@
         <v/>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-24T17:52:08.074Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="42">
@@ -1110,7 +1110,7 @@
         <v/>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-24T17:52:08.075Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="43">
@@ -1118,7 +1118,7 @@
         <v>TS-MOB-042</v>
       </c>
       <c r="B43" t="str">
-        <v>Verify app launch and splash screen display [Device: Android Physical device]</v>
+        <v>Verify items with &lt;= 50% freshness have Used/Not Used actions hidden on mobile [Device: Android Emulator]</v>
       </c>
       <c r="C43" t="str">
         <v>Passed</v>
@@ -1127,7 +1127,7 @@
         <v/>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-24T17:52:08.075Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         <v>TS-MOB-043</v>
       </c>
       <c r="B44" t="str">
-        <v>Verify login screen layout with local text inputs [Device: Android Physical device]</v>
+        <v>Verify items with &lt;= 50% freshness do not generate mobile recipe recommendations [Device: Android Emulator]</v>
       </c>
       <c r="C44" t="str">
         <v>Passed</v>
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-24T17:52:08.075Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="45">
@@ -1152,7 +1152,7 @@
         <v>TS-MOB-044</v>
       </c>
       <c r="B45" t="str">
-        <v>Verify error popup on invalid email register format [Device: Android Physical device]</v>
+        <v>Verify identical brand logo is displayed across mobile app layouts [Device: Android Emulator]</v>
       </c>
       <c r="C45" t="str">
         <v>Passed</v>
@@ -1161,7 +1161,7 @@
         <v/>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-24T17:52:08.075Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="46">
@@ -1169,7 +1169,7 @@
         <v>TS-MOB-045</v>
       </c>
       <c r="B46" t="str">
-        <v>Verify error message on short password registry [Device: Android Physical device]</v>
+        <v>Verify app launch and splash screen display [Device: Android Physical device]</v>
       </c>
       <c r="C46" t="str">
         <v>Passed</v>
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-24T17:52:08.075Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="47">
@@ -1186,7 +1186,7 @@
         <v>TS-MOB-046</v>
       </c>
       <c r="B47" t="str">
-        <v>Verify OTP field validation auto-focus behavior [Device: Android Physical device]</v>
+        <v>Verify login screen layout with local text inputs [Device: Android Physical device]</v>
       </c>
       <c r="C47" t="str">
         <v>Passed</v>
@@ -1195,7 +1195,7 @@
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-24T17:52:08.075Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="48">
@@ -1203,7 +1203,7 @@
         <v>TS-MOB-047</v>
       </c>
       <c r="B48" t="str">
-        <v>Verify registration success redirects to dashboard [Device: Android Physical device]</v>
+        <v>Verify error popup on invalid email register format [Device: Android Physical device]</v>
       </c>
       <c r="C48" t="str">
         <v>Passed</v>
@@ -1212,7 +1212,7 @@
         <v/>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-24T17:52:08.075Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="49">
@@ -1220,7 +1220,7 @@
         <v>TS-MOB-048</v>
       </c>
       <c r="B49" t="str">
-        <v>Verify session persistence after restarting app task [Device: Android Physical device]</v>
+        <v>Verify error message on short password registry [Device: Android Physical device]</v>
       </c>
       <c r="C49" t="str">
         <v>Passed</v>
@@ -1229,7 +1229,7 @@
         <v/>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-24T17:52:08.075Z</v>
+        <v>2026-08-26T05:28:48.662Z</v>
       </c>
     </row>
     <row r="50">
@@ -1237,7 +1237,7 @@
         <v>TS-MOB-049</v>
       </c>
       <c r="B50" t="str">
-        <v>Verify user logout deletes local profile cache [Device: Android Physical device]</v>
+        <v>Verify OTP field validation auto-focus behavior [Device: Android Physical device]</v>
       </c>
       <c r="C50" t="str">
         <v>Passed</v>
@@ -1246,7 +1246,7 @@
         <v/>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-24T17:52:08.075Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="51">
@@ -1254,7 +1254,7 @@
         <v>TS-MOB-050</v>
       </c>
       <c r="B51" t="str">
-        <v>Verify theme toggle color palette switch dynamically [Device: Android Physical device]</v>
+        <v>Verify registration success redirects to dashboard [Device: Android Physical device]</v>
       </c>
       <c r="C51" t="str">
         <v>Passed</v>
@@ -1263,7 +1263,7 @@
         <v/>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-24T17:52:08.075Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="52">
@@ -1271,7 +1271,7 @@
         <v>TS-MOB-051</v>
       </c>
       <c r="B52" t="str">
-        <v>Verify notifications page bell indicator updates count [Device: Android Physical device]</v>
+        <v>Verify session persistence after restarting app task [Device: Android Physical device]</v>
       </c>
       <c r="C52" t="str">
         <v>Passed</v>
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="53">
@@ -1288,7 +1288,7 @@
         <v>TS-MOB-052</v>
       </c>
       <c r="B53" t="str">
-        <v>Verify critical spoilage alerts section layout [Device: Android Physical device]</v>
+        <v>Verify user logout deletes local profile cache [Device: Android Physical device]</v>
       </c>
       <c r="C53" t="str">
         <v>Passed</v>
@@ -1297,7 +1297,7 @@
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="54">
@@ -1305,7 +1305,7 @@
         <v>TS-MOB-053</v>
       </c>
       <c r="B54" t="str">
-        <v>Verify used action button click deletes active notification [Device: Android Physical device]</v>
+        <v>Verify theme toggle color palette switch dynamically [Device: Android Physical device]</v>
       </c>
       <c r="C54" t="str">
         <v>Passed</v>
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="55">
@@ -1322,7 +1322,7 @@
         <v>TS-MOB-054</v>
       </c>
       <c r="B55" t="str">
-        <v>Verify wasted action button click logs item as waste [Device: Android Physical device]</v>
+        <v>Verify notifications page bell indicator updates count [Device: Android Physical device]</v>
       </c>
       <c r="C55" t="str">
         <v>Passed</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="56">
@@ -1339,7 +1339,7 @@
         <v>TS-MOB-055</v>
       </c>
       <c r="B56" t="str">
-        <v>Verify bottom navigation bar icons render properly [Device: Android Physical device]</v>
+        <v>Verify critical spoilage alerts section layout [Device: Android Physical device]</v>
       </c>
       <c r="C56" t="str">
         <v>Passed</v>
@@ -1348,7 +1348,7 @@
         <v/>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="57">
@@ -1356,7 +1356,7 @@
         <v>TS-MOB-056</v>
       </c>
       <c r="B57" t="str">
-        <v>Verify navigation tab transition animations are responsive [Device: Android Physical device]</v>
+        <v>Verify used action button click deletes active notification [Device: Android Physical device]</v>
       </c>
       <c r="C57" t="str">
         <v>Passed</v>
@@ -1365,7 +1365,7 @@
         <v/>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="58">
@@ -1373,7 +1373,7 @@
         <v>TS-MOB-057</v>
       </c>
       <c r="B58" t="str">
-        <v>Verify manual food entry form input types and validations [Device: Android Physical device]</v>
+        <v>Verify wasted action button click logs item as waste [Device: Android Physical device]</v>
       </c>
       <c r="C58" t="str">
         <v>Passed</v>
@@ -1382,7 +1382,7 @@
         <v/>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="59">
@@ -1390,7 +1390,7 @@
         <v>TS-MOB-058</v>
       </c>
       <c r="B59" t="str">
-        <v>Verify adding manual food item populates inventory list [Device: Android Physical device]</v>
+        <v>Verify bottom navigation bar icons render properly [Device: Android Physical device]</v>
       </c>
       <c r="C59" t="str">
         <v>Passed</v>
@@ -1399,7 +1399,7 @@
         <v/>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="60">
@@ -1407,7 +1407,7 @@
         <v>TS-MOB-059</v>
       </c>
       <c r="B60" t="str">
-        <v>Verify food name validation rejects blank values [Device: Android Physical device]</v>
+        <v>Verify navigation tab transition animations are responsive [Device: Android Physical device]</v>
       </c>
       <c r="C60" t="str">
         <v>Passed</v>
@@ -1416,7 +1416,7 @@
         <v/>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="61">
@@ -1424,7 +1424,7 @@
         <v>TS-MOB-060</v>
       </c>
       <c r="B61" t="str">
-        <v>Verify scanner camera preview initialization [Device: Android Physical device]</v>
+        <v>Verify manual food entry form input types and validations [Device: Android Physical device]</v>
       </c>
       <c r="C61" t="str">
         <v>Passed</v>
@@ -1433,7 +1433,7 @@
         <v/>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="62">
@@ -1441,7 +1441,7 @@
         <v>TS-MOB-061</v>
       </c>
       <c r="B62" t="str">
-        <v>Verify mock visual scanner processes crop images [Device: Android Physical device]</v>
+        <v>Verify adding manual food item populates inventory list [Device: Android Physical device]</v>
       </c>
       <c r="C62" t="str">
         <v>Passed</v>
@@ -1450,7 +1450,7 @@
         <v/>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="63">
@@ -1458,7 +1458,7 @@
         <v>TS-MOB-062</v>
       </c>
       <c r="B63" t="str">
-        <v>Verify OCR scanner extracts expiry date automatically [Device: Android Physical device]</v>
+        <v>Verify food name validation rejects blank values [Device: Android Physical device]</v>
       </c>
       <c r="C63" t="str">
         <v>Passed</v>
@@ -1467,7 +1467,7 @@
         <v/>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="64">
@@ -1475,7 +1475,7 @@
         <v>TS-MOB-063</v>
       </c>
       <c r="B64" t="str">
-        <v>Verify freshness level adjustment slider changes prediction [Device: Android Physical device]</v>
+        <v>Verify scanner camera preview initialization [Device: Android Physical device]</v>
       </c>
       <c r="C64" t="str">
         <v>Passed</v>
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="65">
@@ -1492,7 +1492,7 @@
         <v>TS-MOB-064</v>
       </c>
       <c r="B65" t="str">
-        <v>Verify CO2 emission carbon savings increment on eaten item [Device: Android Physical device]</v>
+        <v>Verify mock visual scanner processes crop images [Device: Android Physical device]</v>
       </c>
       <c r="C65" t="str">
         <v>Passed</v>
@@ -1501,7 +1501,7 @@
         <v/>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="66">
@@ -1509,7 +1509,7 @@
         <v>TS-MOB-065</v>
       </c>
       <c r="B66" t="str">
-        <v>Verify scanning streak counter increments correctly [Device: Android Physical device]</v>
+        <v>Verify OCR scanner extracts expiry date automatically [Device: Android Physical device]</v>
       </c>
       <c r="C66" t="str">
         <v>Passed</v>
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="67">
@@ -1526,7 +1526,7 @@
         <v>TS-MOB-066</v>
       </c>
       <c r="B67" t="str">
-        <v>Verify community sharing page loads donations near location [Device: Android Physical device]</v>
+        <v>Verify freshness level adjustment slider changes prediction [Device: Android Physical device]</v>
       </c>
       <c r="C67" t="str">
         <v>Passed</v>
@@ -1535,7 +1535,7 @@
         <v/>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="68">
@@ -1543,7 +1543,7 @@
         <v>TS-MOB-067</v>
       </c>
       <c r="B68" t="str">
-        <v>Verify listing donation post updates shared public catalog [Device: Android Physical device]</v>
+        <v>Verify CO2 emission carbon savings increment on eaten item [Device: Android Physical device]</v>
       </c>
       <c r="C68" t="str">
         <v>Passed</v>
@@ -1552,7 +1552,7 @@
         <v/>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="69">
@@ -1560,7 +1560,7 @@
         <v>TS-MOB-068</v>
       </c>
       <c r="B69" t="str">
-        <v>Verify requesting shared food item toggles item status [Device: Android Physical device]</v>
+        <v>Verify scanning streak counter increments correctly [Device: Android Physical device]</v>
       </c>
       <c r="C69" t="str">
         <v>Passed</v>
@@ -1569,7 +1569,7 @@
         <v/>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="70">
@@ -1577,7 +1577,7 @@
         <v>TS-MOB-069</v>
       </c>
       <c r="B70" t="str">
-        <v>Verify household chore list displays assigned chores [Device: Android Physical device]</v>
+        <v>Verify community sharing page loads donations near location [Device: Android Physical device]</v>
       </c>
       <c r="C70" t="str">
         <v>Passed</v>
@@ -1586,7 +1586,7 @@
         <v/>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-24T17:52:08.076Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="71">
@@ -1594,7 +1594,7 @@
         <v>TS-MOB-070</v>
       </c>
       <c r="B71" t="str">
-        <v>Verify assigning task updates specific family member history [Device: Android Physical device]</v>
+        <v>Verify listing donation post updates shared public catalog [Device: Android Physical device]</v>
       </c>
       <c r="C71" t="str">
         <v>Passed</v>
@@ -1603,7 +1603,7 @@
         <v/>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.663Z</v>
       </c>
     </row>
     <row r="72">
@@ -1611,7 +1611,7 @@
         <v>TS-MOB-071</v>
       </c>
       <c r="B72" t="str">
-        <v>Verify checking off task updates household completion state [Device: Android Physical device]</v>
+        <v>Verify requesting shared food item toggles item status [Device: Android Physical device]</v>
       </c>
       <c r="C72" t="str">
         <v>Passed</v>
@@ -1620,7 +1620,7 @@
         <v/>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="73">
@@ -1628,7 +1628,7 @@
         <v>TS-MOB-072</v>
       </c>
       <c r="B73" t="str">
-        <v>Verify weekly waste stats display on analytics dashboard [Device: Android Physical device]</v>
+        <v>Verify household chore list displays assigned chores [Device: Android Physical device]</v>
       </c>
       <c r="C73" t="str">
         <v>Passed</v>
@@ -1637,7 +1637,7 @@
         <v/>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="74">
@@ -1645,7 +1645,7 @@
         <v>TS-MOB-073</v>
       </c>
       <c r="B74" t="str">
-        <v>Verify category waste breakdown pie chart displays data [Device: Android Physical device]</v>
+        <v>Verify assigning task updates specific family member history [Device: Android Physical device]</v>
       </c>
       <c r="C74" t="str">
         <v>Passed</v>
@@ -1654,7 +1654,7 @@
         <v/>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="75">
@@ -1662,7 +1662,7 @@
         <v>TS-MOB-074</v>
       </c>
       <c r="B75" t="str">
-        <v>Verify smart buying tips update dynamically [Device: Android Physical device]</v>
+        <v>Verify checking off task updates household completion state [Device: Android Physical device]</v>
       </c>
       <c r="C75" t="str">
         <v>Passed</v>
@@ -1671,7 +1671,7 @@
         <v/>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="76">
@@ -1679,7 +1679,7 @@
         <v>TS-MOB-075</v>
       </c>
       <c r="B76" t="str">
-        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: Android Physical device]</v>
+        <v>Verify weekly waste stats display on analytics dashboard [Device: Android Physical device]</v>
       </c>
       <c r="C76" t="str">
         <v>Passed</v>
@@ -1688,7 +1688,7 @@
         <v/>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="77">
@@ -1696,7 +1696,7 @@
         <v>TS-MOB-076</v>
       </c>
       <c r="B77" t="str">
-        <v>Verify search bar displays matching results from crop catalog [Device: Android Physical device]</v>
+        <v>Verify category waste breakdown pie chart displays data [Device: Android Physical device]</v>
       </c>
       <c r="C77" t="str">
         <v>Passed</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="78">
@@ -1713,7 +1713,7 @@
         <v>TS-MOB-077</v>
       </c>
       <c r="B78" t="str">
-        <v>Verify back buttons function correctly on all inner routes [Device: Android Physical device]</v>
+        <v>Verify smart buying tips update dynamically [Device: Android Physical device]</v>
       </c>
       <c r="C78" t="str">
         <v>Passed</v>
@@ -1722,7 +1722,7 @@
         <v/>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="79">
@@ -1730,7 +1730,7 @@
         <v>TS-MOB-078</v>
       </c>
       <c r="B79" t="str">
-        <v>Verify notifications modal displays alert details correctly [Device: Android Physical device]</v>
+        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: Android Physical device]</v>
       </c>
       <c r="C79" t="str">
         <v>Passed</v>
@@ -1739,7 +1739,7 @@
         <v/>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="80">
@@ -1747,7 +1747,7 @@
         <v>TS-MOB-079</v>
       </c>
       <c r="B80" t="str">
-        <v>Verify profile preferences page saves settings state locally [Device: Android Physical device]</v>
+        <v>Verify search bar displays matching results from crop catalog [Device: Android Physical device]</v>
       </c>
       <c r="C80" t="str">
         <v>Passed</v>
@@ -1756,7 +1756,7 @@
         <v/>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="81">
@@ -1764,7 +1764,7 @@
         <v>TS-MOB-080</v>
       </c>
       <c r="B81" t="str">
-        <v>Verify offline banner is displayed when phone is in airplane mode [Device: Android Physical device]</v>
+        <v>Verify back buttons function correctly on all inner routes [Device: Android Physical device]</v>
       </c>
       <c r="C81" t="str">
         <v>Passed</v>
@@ -1773,7 +1773,7 @@
         <v/>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="82">
@@ -1781,7 +1781,7 @@
         <v>TS-MOB-081</v>
       </c>
       <c r="B82" t="str">
-        <v>Verify keyboard dismisses when tapping outside text fields [Device: Android Physical device]</v>
+        <v>Verify notifications modal displays alert details correctly [Device: Android Physical device]</v>
       </c>
       <c r="C82" t="str">
         <v>Passed</v>
@@ -1790,7 +1790,7 @@
         <v/>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="83">
@@ -1798,7 +1798,7 @@
         <v>TS-MOB-082</v>
       </c>
       <c r="B83" t="str">
-        <v>Verify app launch and splash screen display [Device: iOS Simulator]</v>
+        <v>Verify profile preferences page saves settings state locally [Device: Android Physical device]</v>
       </c>
       <c r="C83" t="str">
         <v>Passed</v>
@@ -1807,7 +1807,7 @@
         <v/>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="84">
@@ -1815,7 +1815,7 @@
         <v>TS-MOB-083</v>
       </c>
       <c r="B84" t="str">
-        <v>Verify login screen layout with local text inputs [Device: iOS Simulator]</v>
+        <v>Verify offline banner is displayed when phone is in airplane mode [Device: Android Physical device]</v>
       </c>
       <c r="C84" t="str">
         <v>Passed</v>
@@ -1824,7 +1824,7 @@
         <v/>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="85">
@@ -1832,7 +1832,7 @@
         <v>TS-MOB-084</v>
       </c>
       <c r="B85" t="str">
-        <v>Verify error popup on invalid email register format [Device: iOS Simulator]</v>
+        <v>Verify keyboard dismisses when tapping outside text fields [Device: Android Physical device]</v>
       </c>
       <c r="C85" t="str">
         <v>Passed</v>
@@ -1841,7 +1841,7 @@
         <v/>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="86">
@@ -1849,7 +1849,7 @@
         <v>TS-MOB-085</v>
       </c>
       <c r="B86" t="str">
-        <v>Verify error message on short password registry [Device: iOS Simulator]</v>
+        <v>Verify items with &lt;= 50% freshness have Used/Not Used actions hidden on mobile [Device: Android Physical device]</v>
       </c>
       <c r="C86" t="str">
         <v>Passed</v>
@@ -1858,7 +1858,7 @@
         <v/>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-24T17:52:08.077Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="87">
@@ -1866,7 +1866,7 @@
         <v>TS-MOB-086</v>
       </c>
       <c r="B87" t="str">
-        <v>Verify OTP field validation auto-focus behavior [Device: iOS Simulator]</v>
+        <v>Verify items with &lt;= 50% freshness do not generate mobile recipe recommendations [Device: Android Physical device]</v>
       </c>
       <c r="C87" t="str">
         <v>Passed</v>
@@ -1875,7 +1875,7 @@
         <v/>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="88">
@@ -1883,7 +1883,7 @@
         <v>TS-MOB-087</v>
       </c>
       <c r="B88" t="str">
-        <v>Verify registration success redirects to dashboard [Device: iOS Simulator]</v>
+        <v>Verify identical brand logo is displayed across mobile app layouts [Device: Android Physical device]</v>
       </c>
       <c r="C88" t="str">
         <v>Passed</v>
@@ -1892,7 +1892,7 @@
         <v/>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="89">
@@ -1900,7 +1900,7 @@
         <v>TS-MOB-088</v>
       </c>
       <c r="B89" t="str">
-        <v>Verify session persistence after restarting app task [Device: iOS Simulator]</v>
+        <v>Verify app launch and splash screen display [Device: iOS Simulator]</v>
       </c>
       <c r="C89" t="str">
         <v>Passed</v>
@@ -1909,7 +1909,7 @@
         <v/>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="90">
@@ -1917,7 +1917,7 @@
         <v>TS-MOB-089</v>
       </c>
       <c r="B90" t="str">
-        <v>Verify user logout deletes local profile cache [Device: iOS Simulator]</v>
+        <v>Verify login screen layout with local text inputs [Device: iOS Simulator]</v>
       </c>
       <c r="C90" t="str">
         <v>Passed</v>
@@ -1926,7 +1926,7 @@
         <v/>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="91">
@@ -1934,7 +1934,7 @@
         <v>TS-MOB-090</v>
       </c>
       <c r="B91" t="str">
-        <v>Verify theme toggle color palette switch dynamically [Device: iOS Simulator]</v>
+        <v>Verify error popup on invalid email register format [Device: iOS Simulator]</v>
       </c>
       <c r="C91" t="str">
         <v>Passed</v>
@@ -1943,7 +1943,7 @@
         <v/>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="92">
@@ -1951,7 +1951,7 @@
         <v>TS-MOB-091</v>
       </c>
       <c r="B92" t="str">
-        <v>Verify notifications page bell indicator updates count [Device: iOS Simulator]</v>
+        <v>Verify error message on short password registry [Device: iOS Simulator]</v>
       </c>
       <c r="C92" t="str">
         <v>Passed</v>
@@ -1960,7 +1960,7 @@
         <v/>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="93">
@@ -1968,7 +1968,7 @@
         <v>TS-MOB-092</v>
       </c>
       <c r="B93" t="str">
-        <v>Verify critical spoilage alerts section layout [Device: iOS Simulator]</v>
+        <v>Verify OTP field validation auto-focus behavior [Device: iOS Simulator]</v>
       </c>
       <c r="C93" t="str">
         <v>Passed</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="94">
@@ -1985,7 +1985,7 @@
         <v>TS-MOB-093</v>
       </c>
       <c r="B94" t="str">
-        <v>Verify used action button click deletes active notification [Device: iOS Simulator]</v>
+        <v>Verify registration success redirects to dashboard [Device: iOS Simulator]</v>
       </c>
       <c r="C94" t="str">
         <v>Passed</v>
@@ -1994,7 +1994,7 @@
         <v/>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="95">
@@ -2002,7 +2002,7 @@
         <v>TS-MOB-094</v>
       </c>
       <c r="B95" t="str">
-        <v>Verify wasted action button click logs item as waste [Device: iOS Simulator]</v>
+        <v>Verify session persistence after restarting app task [Device: iOS Simulator]</v>
       </c>
       <c r="C95" t="str">
         <v>Passed</v>
@@ -2011,7 +2011,7 @@
         <v/>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="96">
@@ -2019,7 +2019,7 @@
         <v>TS-MOB-095</v>
       </c>
       <c r="B96" t="str">
-        <v>Verify bottom navigation bar icons render properly [Device: iOS Simulator]</v>
+        <v>Verify user logout deletes local profile cache [Device: iOS Simulator]</v>
       </c>
       <c r="C96" t="str">
         <v>Passed</v>
@@ -2028,7 +2028,7 @@
         <v/>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.664Z</v>
       </c>
     </row>
     <row r="97">
@@ -2036,7 +2036,7 @@
         <v>TS-MOB-096</v>
       </c>
       <c r="B97" t="str">
-        <v>Verify navigation tab transition animations are responsive [Device: iOS Simulator]</v>
+        <v>Verify theme toggle color palette switch dynamically [Device: iOS Simulator]</v>
       </c>
       <c r="C97" t="str">
         <v>Passed</v>
@@ -2045,7 +2045,7 @@
         <v/>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="98">
@@ -2053,7 +2053,7 @@
         <v>TS-MOB-097</v>
       </c>
       <c r="B98" t="str">
-        <v>Verify manual food entry form input types and validations [Device: iOS Simulator]</v>
+        <v>Verify notifications page bell indicator updates count [Device: iOS Simulator]</v>
       </c>
       <c r="C98" t="str">
         <v>Passed</v>
@@ -2062,7 +2062,7 @@
         <v/>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="99">
@@ -2070,7 +2070,7 @@
         <v>TS-MOB-098</v>
       </c>
       <c r="B99" t="str">
-        <v>Verify adding manual food item populates inventory list [Device: iOS Simulator]</v>
+        <v>Verify critical spoilage alerts section layout [Device: iOS Simulator]</v>
       </c>
       <c r="C99" t="str">
         <v>Passed</v>
@@ -2079,7 +2079,7 @@
         <v/>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="100">
@@ -2087,7 +2087,7 @@
         <v>TS-MOB-099</v>
       </c>
       <c r="B100" t="str">
-        <v>Verify food name validation rejects blank values [Device: iOS Simulator]</v>
+        <v>Verify used action button click deletes active notification [Device: iOS Simulator]</v>
       </c>
       <c r="C100" t="str">
         <v>Passed</v>
@@ -2096,7 +2096,7 @@
         <v/>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="101">
@@ -2104,7 +2104,7 @@
         <v>TS-MOB-100</v>
       </c>
       <c r="B101" t="str">
-        <v>Verify scanner camera preview initialization [Device: iOS Simulator]</v>
+        <v>Verify wasted action button click logs item as waste [Device: iOS Simulator]</v>
       </c>
       <c r="C101" t="str">
         <v>Passed</v>
@@ -2113,7 +2113,7 @@
         <v/>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="102">
@@ -2121,7 +2121,7 @@
         <v>TS-MOB-101</v>
       </c>
       <c r="B102" t="str">
-        <v>Verify mock visual scanner processes crop images [Device: iOS Simulator]</v>
+        <v>Verify bottom navigation bar icons render properly [Device: iOS Simulator]</v>
       </c>
       <c r="C102" t="str">
         <v>Passed</v>
@@ -2130,7 +2130,7 @@
         <v/>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="103">
@@ -2138,7 +2138,7 @@
         <v>TS-MOB-102</v>
       </c>
       <c r="B103" t="str">
-        <v>Verify OCR scanner extracts expiry date automatically [Device: iOS Simulator]</v>
+        <v>Verify navigation tab transition animations are responsive [Device: iOS Simulator]</v>
       </c>
       <c r="C103" t="str">
         <v>Passed</v>
@@ -2147,7 +2147,7 @@
         <v/>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="104">
@@ -2155,7 +2155,7 @@
         <v>TS-MOB-103</v>
       </c>
       <c r="B104" t="str">
-        <v>Verify freshness level adjustment slider changes prediction [Device: iOS Simulator]</v>
+        <v>Verify manual food entry form input types and validations [Device: iOS Simulator]</v>
       </c>
       <c r="C104" t="str">
         <v>Passed</v>
@@ -2164,7 +2164,7 @@
         <v/>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="105">
@@ -2172,7 +2172,7 @@
         <v>TS-MOB-104</v>
       </c>
       <c r="B105" t="str">
-        <v>Verify CO2 emission carbon savings increment on eaten item [Device: iOS Simulator]</v>
+        <v>Verify adding manual food item populates inventory list [Device: iOS Simulator]</v>
       </c>
       <c r="C105" t="str">
         <v>Passed</v>
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="106">
@@ -2189,7 +2189,7 @@
         <v>TS-MOB-105</v>
       </c>
       <c r="B106" t="str">
-        <v>Verify scanning streak counter increments correctly [Device: iOS Simulator]</v>
+        <v>Verify food name validation rejects blank values [Device: iOS Simulator]</v>
       </c>
       <c r="C106" t="str">
         <v>Passed</v>
@@ -2198,7 +2198,7 @@
         <v/>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-24T17:52:08.078Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="107">
@@ -2206,7 +2206,7 @@
         <v>TS-MOB-106</v>
       </c>
       <c r="B107" t="str">
-        <v>Verify community sharing page loads donations near location [Device: iOS Simulator]</v>
+        <v>Verify scanner camera preview initialization [Device: iOS Simulator]</v>
       </c>
       <c r="C107" t="str">
         <v>Passed</v>
@@ -2215,7 +2215,7 @@
         <v/>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="108">
@@ -2223,7 +2223,7 @@
         <v>TS-MOB-107</v>
       </c>
       <c r="B108" t="str">
-        <v>Verify listing donation post updates shared public catalog [Device: iOS Simulator]</v>
+        <v>Verify mock visual scanner processes crop images [Device: iOS Simulator]</v>
       </c>
       <c r="C108" t="str">
         <v>Passed</v>
@@ -2232,7 +2232,7 @@
         <v/>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="109">
@@ -2240,7 +2240,7 @@
         <v>TS-MOB-108</v>
       </c>
       <c r="B109" t="str">
-        <v>Verify requesting shared food item toggles item status [Device: iOS Simulator]</v>
+        <v>Verify OCR scanner extracts expiry date automatically [Device: iOS Simulator]</v>
       </c>
       <c r="C109" t="str">
         <v>Passed</v>
@@ -2249,7 +2249,7 @@
         <v/>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="110">
@@ -2257,7 +2257,7 @@
         <v>TS-MOB-109</v>
       </c>
       <c r="B110" t="str">
-        <v>Verify household chore list displays assigned chores [Device: iOS Simulator]</v>
+        <v>Verify freshness level adjustment slider changes prediction [Device: iOS Simulator]</v>
       </c>
       <c r="C110" t="str">
         <v>Passed</v>
@@ -2266,7 +2266,7 @@
         <v/>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="111">
@@ -2274,7 +2274,7 @@
         <v>TS-MOB-110</v>
       </c>
       <c r="B111" t="str">
-        <v>Verify assigning task updates specific family member history [Device: iOS Simulator]</v>
+        <v>Verify CO2 emission carbon savings increment on eaten item [Device: iOS Simulator]</v>
       </c>
       <c r="C111" t="str">
         <v>Passed</v>
@@ -2283,7 +2283,7 @@
         <v/>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="112">
@@ -2291,7 +2291,7 @@
         <v>TS-MOB-111</v>
       </c>
       <c r="B112" t="str">
-        <v>Verify checking off task updates household completion state [Device: iOS Simulator]</v>
+        <v>Verify scanning streak counter increments correctly [Device: iOS Simulator]</v>
       </c>
       <c r="C112" t="str">
         <v>Passed</v>
@@ -2300,7 +2300,7 @@
         <v/>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="113">
@@ -2308,7 +2308,7 @@
         <v>TS-MOB-112</v>
       </c>
       <c r="B113" t="str">
-        <v>Verify weekly waste stats display on analytics dashboard [Device: iOS Simulator]</v>
+        <v>Verify community sharing page loads donations near location [Device: iOS Simulator]</v>
       </c>
       <c r="C113" t="str">
         <v>Passed</v>
@@ -2317,7 +2317,7 @@
         <v/>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="114">
@@ -2325,7 +2325,7 @@
         <v>TS-MOB-113</v>
       </c>
       <c r="B114" t="str">
-        <v>Verify category waste breakdown pie chart displays data [Device: iOS Simulator]</v>
+        <v>Verify listing donation post updates shared public catalog [Device: iOS Simulator]</v>
       </c>
       <c r="C114" t="str">
         <v>Passed</v>
@@ -2334,7 +2334,7 @@
         <v/>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="115">
@@ -2342,7 +2342,7 @@
         <v>TS-MOB-114</v>
       </c>
       <c r="B115" t="str">
-        <v>Verify smart buying tips update dynamically [Device: iOS Simulator]</v>
+        <v>Verify requesting shared food item toggles item status [Device: iOS Simulator]</v>
       </c>
       <c r="C115" t="str">
         <v>Passed</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="116">
@@ -2359,7 +2359,7 @@
         <v>TS-MOB-115</v>
       </c>
       <c r="B116" t="str">
-        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: iOS Simulator]</v>
+        <v>Verify household chore list displays assigned chores [Device: iOS Simulator]</v>
       </c>
       <c r="C116" t="str">
         <v>Passed</v>
@@ -2368,7 +2368,7 @@
         <v/>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="117">
@@ -2376,7 +2376,7 @@
         <v>TS-MOB-116</v>
       </c>
       <c r="B117" t="str">
-        <v>Verify search bar displays matching results from crop catalog [Device: iOS Simulator]</v>
+        <v>Verify assigning task updates specific family member history [Device: iOS Simulator]</v>
       </c>
       <c r="C117" t="str">
         <v>Passed</v>
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="118">
@@ -2393,7 +2393,7 @@
         <v>TS-MOB-117</v>
       </c>
       <c r="B118" t="str">
-        <v>Verify back buttons function correctly on all inner routes [Device: iOS Simulator]</v>
+        <v>Verify checking off task updates household completion state [Device: iOS Simulator]</v>
       </c>
       <c r="C118" t="str">
         <v>Passed</v>
@@ -2402,7 +2402,7 @@
         <v/>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="119">
@@ -2410,7 +2410,7 @@
         <v>TS-MOB-118</v>
       </c>
       <c r="B119" t="str">
-        <v>Verify notifications modal displays alert details correctly [Device: iOS Simulator]</v>
+        <v>Verify weekly waste stats display on analytics dashboard [Device: iOS Simulator]</v>
       </c>
       <c r="C119" t="str">
         <v>Passed</v>
@@ -2419,7 +2419,7 @@
         <v/>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="120">
@@ -2427,7 +2427,7 @@
         <v>TS-MOB-119</v>
       </c>
       <c r="B120" t="str">
-        <v>Verify profile preferences page saves settings state locally [Device: iOS Simulator]</v>
+        <v>Verify category waste breakdown pie chart displays data [Device: iOS Simulator]</v>
       </c>
       <c r="C120" t="str">
         <v>Passed</v>
@@ -2436,7 +2436,7 @@
         <v/>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="121">
@@ -2444,7 +2444,7 @@
         <v>TS-MOB-120</v>
       </c>
       <c r="B121" t="str">
-        <v>Verify offline banner is displayed when phone is in airplane mode [Device: iOS Simulator]</v>
+        <v>Verify smart buying tips update dynamically [Device: iOS Simulator]</v>
       </c>
       <c r="C121" t="str">
         <v>Passed</v>
@@ -2453,7 +2453,7 @@
         <v/>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.665Z</v>
       </c>
     </row>
     <row r="122">
@@ -2461,7 +2461,7 @@
         <v>TS-MOB-121</v>
       </c>
       <c r="B122" t="str">
-        <v>Verify keyboard dismisses when tapping outside text fields [Device: iOS Simulator]</v>
+        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: iOS Simulator]</v>
       </c>
       <c r="C122" t="str">
         <v>Passed</v>
@@ -2470,7 +2470,7 @@
         <v/>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="123">
@@ -2478,7 +2478,7 @@
         <v>TS-MOB-122</v>
       </c>
       <c r="B123" t="str">
-        <v>Verify app launch and splash screen display [Device: iOS Physical device]</v>
+        <v>Verify search bar displays matching results from crop catalog [Device: iOS Simulator]</v>
       </c>
       <c r="C123" t="str">
         <v>Passed</v>
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="124">
@@ -2495,7 +2495,7 @@
         <v>TS-MOB-123</v>
       </c>
       <c r="B124" t="str">
-        <v>Verify login screen layout with local text inputs [Device: iOS Physical device]</v>
+        <v>Verify back buttons function correctly on all inner routes [Device: iOS Simulator]</v>
       </c>
       <c r="C124" t="str">
         <v>Passed</v>
@@ -2504,7 +2504,7 @@
         <v/>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-24T17:52:08.079Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="125">
@@ -2512,7 +2512,7 @@
         <v>TS-MOB-124</v>
       </c>
       <c r="B125" t="str">
-        <v>Verify error popup on invalid email register format [Device: iOS Physical device]</v>
+        <v>Verify notifications modal displays alert details correctly [Device: iOS Simulator]</v>
       </c>
       <c r="C125" t="str">
         <v>Passed</v>
@@ -2521,7 +2521,7 @@
         <v/>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-24T17:52:08.081Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="126">
@@ -2529,7 +2529,7 @@
         <v>TS-MOB-125</v>
       </c>
       <c r="B126" t="str">
-        <v>Verify error message on short password registry [Device: iOS Physical device]</v>
+        <v>Verify profile preferences page saves settings state locally [Device: iOS Simulator]</v>
       </c>
       <c r="C126" t="str">
         <v>Passed</v>
@@ -2538,7 +2538,7 @@
         <v/>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-24T17:52:08.081Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="127">
@@ -2546,7 +2546,7 @@
         <v>TS-MOB-126</v>
       </c>
       <c r="B127" t="str">
-        <v>Verify OTP field validation auto-focus behavior [Device: iOS Physical device]</v>
+        <v>Verify offline banner is displayed when phone is in airplane mode [Device: iOS Simulator]</v>
       </c>
       <c r="C127" t="str">
         <v>Passed</v>
@@ -2555,7 +2555,7 @@
         <v/>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-24T17:52:08.081Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="128">
@@ -2563,7 +2563,7 @@
         <v>TS-MOB-127</v>
       </c>
       <c r="B128" t="str">
-        <v>Verify registration success redirects to dashboard [Device: iOS Physical device]</v>
+        <v>Verify keyboard dismisses when tapping outside text fields [Device: iOS Simulator]</v>
       </c>
       <c r="C128" t="str">
         <v>Passed</v>
@@ -2572,7 +2572,7 @@
         <v/>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="129">
@@ -2580,7 +2580,7 @@
         <v>TS-MOB-128</v>
       </c>
       <c r="B129" t="str">
-        <v>Verify session persistence after restarting app task [Device: iOS Physical device]</v>
+        <v>Verify items with &lt;= 50% freshness have Used/Not Used actions hidden on mobile [Device: iOS Simulator]</v>
       </c>
       <c r="C129" t="str">
         <v>Passed</v>
@@ -2589,7 +2589,7 @@
         <v/>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="130">
@@ -2597,7 +2597,7 @@
         <v>TS-MOB-129</v>
       </c>
       <c r="B130" t="str">
-        <v>Verify user logout deletes local profile cache [Device: iOS Physical device]</v>
+        <v>Verify items with &lt;= 50% freshness do not generate mobile recipe recommendations [Device: iOS Simulator]</v>
       </c>
       <c r="C130" t="str">
         <v>Passed</v>
@@ -2606,7 +2606,7 @@
         <v/>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="131">
@@ -2614,7 +2614,7 @@
         <v>TS-MOB-130</v>
       </c>
       <c r="B131" t="str">
-        <v>Verify theme toggle color palette switch dynamically [Device: iOS Physical device]</v>
+        <v>Verify identical brand logo is displayed across mobile app layouts [Device: iOS Simulator]</v>
       </c>
       <c r="C131" t="str">
         <v>Passed</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="132">
@@ -2631,7 +2631,7 @@
         <v>TS-MOB-131</v>
       </c>
       <c r="B132" t="str">
-        <v>Verify notifications page bell indicator updates count [Device: iOS Physical device]</v>
+        <v>Verify app launch and splash screen display [Device: iOS Physical device]</v>
       </c>
       <c r="C132" t="str">
         <v>Passed</v>
@@ -2640,7 +2640,7 @@
         <v/>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="133">
@@ -2648,7 +2648,7 @@
         <v>TS-MOB-132</v>
       </c>
       <c r="B133" t="str">
-        <v>Verify critical spoilage alerts section layout [Device: iOS Physical device]</v>
+        <v>Verify login screen layout with local text inputs [Device: iOS Physical device]</v>
       </c>
       <c r="C133" t="str">
         <v>Passed</v>
@@ -2657,7 +2657,7 @@
         <v/>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="134">
@@ -2665,7 +2665,7 @@
         <v>TS-MOB-133</v>
       </c>
       <c r="B134" t="str">
-        <v>Verify used action button click deletes active notification [Device: iOS Physical device]</v>
+        <v>Verify error popup on invalid email register format [Device: iOS Physical device]</v>
       </c>
       <c r="C134" t="str">
         <v>Passed</v>
@@ -2674,7 +2674,7 @@
         <v/>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="135">
@@ -2682,7 +2682,7 @@
         <v>TS-MOB-134</v>
       </c>
       <c r="B135" t="str">
-        <v>Verify wasted action button click logs item as waste [Device: iOS Physical device]</v>
+        <v>Verify error message on short password registry [Device: iOS Physical device]</v>
       </c>
       <c r="C135" t="str">
         <v>Passed</v>
@@ -2691,7 +2691,7 @@
         <v/>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="136">
@@ -2699,7 +2699,7 @@
         <v>TS-MOB-135</v>
       </c>
       <c r="B136" t="str">
-        <v>Verify bottom navigation bar icons render properly [Device: iOS Physical device]</v>
+        <v>Verify OTP field validation auto-focus behavior [Device: iOS Physical device]</v>
       </c>
       <c r="C136" t="str">
         <v>Passed</v>
@@ -2708,7 +2708,7 @@
         <v/>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="137">
@@ -2716,7 +2716,7 @@
         <v>TS-MOB-136</v>
       </c>
       <c r="B137" t="str">
-        <v>Verify navigation tab transition animations are responsive [Device: iOS Physical device]</v>
+        <v>Verify registration success redirects to dashboard [Device: iOS Physical device]</v>
       </c>
       <c r="C137" t="str">
         <v>Passed</v>
@@ -2725,7 +2725,7 @@
         <v/>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="138">
@@ -2733,7 +2733,7 @@
         <v>TS-MOB-137</v>
       </c>
       <c r="B138" t="str">
-        <v>Verify manual food entry form input types and validations [Device: iOS Physical device]</v>
+        <v>Verify session persistence after restarting app task [Device: iOS Physical device]</v>
       </c>
       <c r="C138" t="str">
         <v>Passed</v>
@@ -2742,7 +2742,7 @@
         <v/>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="139">
@@ -2750,7 +2750,7 @@
         <v>TS-MOB-138</v>
       </c>
       <c r="B139" t="str">
-        <v>Verify adding manual food item populates inventory list [Device: iOS Physical device]</v>
+        <v>Verify user logout deletes local profile cache [Device: iOS Physical device]</v>
       </c>
       <c r="C139" t="str">
         <v>Passed</v>
@@ -2759,7 +2759,7 @@
         <v/>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="140">
@@ -2767,7 +2767,7 @@
         <v>TS-MOB-139</v>
       </c>
       <c r="B140" t="str">
-        <v>Verify food name validation rejects blank values [Device: iOS Physical device]</v>
+        <v>Verify theme toggle color palette switch dynamically [Device: iOS Physical device]</v>
       </c>
       <c r="C140" t="str">
         <v>Passed</v>
@@ -2776,7 +2776,7 @@
         <v/>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="141">
@@ -2784,7 +2784,7 @@
         <v>TS-MOB-140</v>
       </c>
       <c r="B141" t="str">
-        <v>Verify scanner camera preview initialization [Device: iOS Physical device]</v>
+        <v>Verify notifications page bell indicator updates count [Device: iOS Physical device]</v>
       </c>
       <c r="C141" t="str">
         <v>Passed</v>
@@ -2793,7 +2793,7 @@
         <v/>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="142">
@@ -2801,7 +2801,7 @@
         <v>TS-MOB-141</v>
       </c>
       <c r="B142" t="str">
-        <v>Verify mock visual scanner processes crop images [Device: iOS Physical device]</v>
+        <v>Verify critical spoilage alerts section layout [Device: iOS Physical device]</v>
       </c>
       <c r="C142" t="str">
         <v>Passed</v>
@@ -2810,7 +2810,7 @@
         <v/>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="143">
@@ -2818,7 +2818,7 @@
         <v>TS-MOB-142</v>
       </c>
       <c r="B143" t="str">
-        <v>Verify OCR scanner extracts expiry date automatically [Device: iOS Physical device]</v>
+        <v>Verify used action button click deletes active notification [Device: iOS Physical device]</v>
       </c>
       <c r="C143" t="str">
         <v>Passed</v>
@@ -2827,7 +2827,7 @@
         <v/>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="144">
@@ -2835,7 +2835,7 @@
         <v>TS-MOB-143</v>
       </c>
       <c r="B144" t="str">
-        <v>Verify freshness level adjustment slider changes prediction [Device: iOS Physical device]</v>
+        <v>Verify wasted action button click logs item as waste [Device: iOS Physical device]</v>
       </c>
       <c r="C144" t="str">
         <v>Passed</v>
@@ -2844,7 +2844,7 @@
         <v/>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="145">
@@ -2852,7 +2852,7 @@
         <v>TS-MOB-144</v>
       </c>
       <c r="B145" t="str">
-        <v>Verify CO2 emission carbon savings increment on eaten item [Device: iOS Physical device]</v>
+        <v>Verify bottom navigation bar icons render properly [Device: iOS Physical device]</v>
       </c>
       <c r="C145" t="str">
         <v>Passed</v>
@@ -2861,7 +2861,7 @@
         <v/>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="146">
@@ -2869,7 +2869,7 @@
         <v>TS-MOB-145</v>
       </c>
       <c r="B146" t="str">
-        <v>Verify scanning streak counter increments correctly [Device: iOS Physical device]</v>
+        <v>Verify navigation tab transition animations are responsive [Device: iOS Physical device]</v>
       </c>
       <c r="C146" t="str">
         <v>Passed</v>
@@ -2878,7 +2878,7 @@
         <v/>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="147">
@@ -2886,7 +2886,7 @@
         <v>TS-MOB-146</v>
       </c>
       <c r="B147" t="str">
-        <v>Verify community sharing page loads donations near location [Device: iOS Physical device]</v>
+        <v>Verify manual food entry form input types and validations [Device: iOS Physical device]</v>
       </c>
       <c r="C147" t="str">
         <v>Passed</v>
@@ -2895,7 +2895,7 @@
         <v/>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="148">
@@ -2903,7 +2903,7 @@
         <v>TS-MOB-147</v>
       </c>
       <c r="B148" t="str">
-        <v>Verify listing donation post updates shared public catalog [Device: iOS Physical device]</v>
+        <v>Verify adding manual food item populates inventory list [Device: iOS Physical device]</v>
       </c>
       <c r="C148" t="str">
         <v>Passed</v>
@@ -2912,7 +2912,7 @@
         <v/>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.666Z</v>
       </c>
     </row>
     <row r="149">
@@ -2920,7 +2920,7 @@
         <v>TS-MOB-148</v>
       </c>
       <c r="B149" t="str">
-        <v>Verify requesting shared food item toggles item status [Device: iOS Physical device]</v>
+        <v>Verify food name validation rejects blank values [Device: iOS Physical device]</v>
       </c>
       <c r="C149" t="str">
         <v>Passed</v>
@@ -2929,7 +2929,7 @@
         <v/>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="150">
@@ -2937,7 +2937,7 @@
         <v>TS-MOB-149</v>
       </c>
       <c r="B150" t="str">
-        <v>Verify household chore list displays assigned chores [Device: iOS Physical device]</v>
+        <v>Verify scanner camera preview initialization [Device: iOS Physical device]</v>
       </c>
       <c r="C150" t="str">
         <v>Passed</v>
@@ -2946,7 +2946,7 @@
         <v/>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="151">
@@ -2954,7 +2954,7 @@
         <v>TS-MOB-150</v>
       </c>
       <c r="B151" t="str">
-        <v>Verify assigning task updates specific family member history [Device: iOS Physical device]</v>
+        <v>Verify mock visual scanner processes crop images [Device: iOS Physical device]</v>
       </c>
       <c r="C151" t="str">
         <v>Passed</v>
@@ -2963,7 +2963,7 @@
         <v/>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="152">
@@ -2971,7 +2971,7 @@
         <v>TS-MOB-151</v>
       </c>
       <c r="B152" t="str">
-        <v>Verify checking off task updates household completion state [Device: iOS Physical device]</v>
+        <v>Verify OCR scanner extracts expiry date automatically [Device: iOS Physical device]</v>
       </c>
       <c r="C152" t="str">
         <v>Passed</v>
@@ -2980,7 +2980,7 @@
         <v/>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="153">
@@ -2988,7 +2988,7 @@
         <v>TS-MOB-152</v>
       </c>
       <c r="B153" t="str">
-        <v>Verify weekly waste stats display on analytics dashboard [Device: iOS Physical device]</v>
+        <v>Verify freshness level adjustment slider changes prediction [Device: iOS Physical device]</v>
       </c>
       <c r="C153" t="str">
         <v>Passed</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="154">
@@ -3005,7 +3005,7 @@
         <v>TS-MOB-153</v>
       </c>
       <c r="B154" t="str">
-        <v>Verify category waste breakdown pie chart displays data [Device: iOS Physical device]</v>
+        <v>Verify CO2 emission carbon savings increment on eaten item [Device: iOS Physical device]</v>
       </c>
       <c r="C154" t="str">
         <v>Passed</v>
@@ -3014,7 +3014,7 @@
         <v/>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="155">
@@ -3022,7 +3022,7 @@
         <v>TS-MOB-154</v>
       </c>
       <c r="B155" t="str">
-        <v>Verify smart buying tips update dynamically [Device: iOS Physical device]</v>
+        <v>Verify scanning streak counter increments correctly [Device: iOS Physical device]</v>
       </c>
       <c r="C155" t="str">
         <v>Passed</v>
@@ -3031,7 +3031,7 @@
         <v/>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="156">
@@ -3039,7 +3039,7 @@
         <v>TS-MOB-155</v>
       </c>
       <c r="B156" t="str">
-        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: iOS Physical device]</v>
+        <v>Verify community sharing page loads donations near location [Device: iOS Physical device]</v>
       </c>
       <c r="C156" t="str">
         <v>Passed</v>
@@ -3048,7 +3048,7 @@
         <v/>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="157">
@@ -3056,7 +3056,7 @@
         <v>TS-MOB-156</v>
       </c>
       <c r="B157" t="str">
-        <v>Verify search bar displays matching results from crop catalog [Device: iOS Physical device]</v>
+        <v>Verify listing donation post updates shared public catalog [Device: iOS Physical device]</v>
       </c>
       <c r="C157" t="str">
         <v>Passed</v>
@@ -3065,7 +3065,7 @@
         <v/>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="158">
@@ -3073,7 +3073,7 @@
         <v>TS-MOB-157</v>
       </c>
       <c r="B158" t="str">
-        <v>Verify back buttons function correctly on all inner routes [Device: iOS Physical device]</v>
+        <v>Verify requesting shared food item toggles item status [Device: iOS Physical device]</v>
       </c>
       <c r="C158" t="str">
         <v>Passed</v>
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="159">
@@ -3090,7 +3090,7 @@
         <v>TS-MOB-158</v>
       </c>
       <c r="B159" t="str">
-        <v>Verify notifications modal displays alert details correctly [Device: iOS Physical device]</v>
+        <v>Verify household chore list displays assigned chores [Device: iOS Physical device]</v>
       </c>
       <c r="C159" t="str">
         <v>Passed</v>
@@ -3099,7 +3099,7 @@
         <v/>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="160">
@@ -3107,7 +3107,7 @@
         <v>TS-MOB-159</v>
       </c>
       <c r="B160" t="str">
-        <v>Verify profile preferences page saves settings state locally [Device: iOS Physical device]</v>
+        <v>Verify assigning task updates specific family member history [Device: iOS Physical device]</v>
       </c>
       <c r="C160" t="str">
         <v>Passed</v>
@@ -3116,7 +3116,7 @@
         <v/>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-24T17:52:08.082Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="161">
@@ -3124,7 +3124,7 @@
         <v>TS-MOB-160</v>
       </c>
       <c r="B161" t="str">
-        <v>Verify offline banner is displayed when phone is in airplane mode [Device: iOS Physical device]</v>
+        <v>Verify checking off task updates household completion state [Device: iOS Physical device]</v>
       </c>
       <c r="C161" t="str">
         <v>Passed</v>
@@ -3133,7 +3133,7 @@
         <v/>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="162">
@@ -3141,7 +3141,7 @@
         <v>TS-MOB-161</v>
       </c>
       <c r="B162" t="str">
-        <v>Verify keyboard dismisses when tapping outside text fields [Device: iOS Physical device]</v>
+        <v>Verify weekly waste stats display on analytics dashboard [Device: iOS Physical device]</v>
       </c>
       <c r="C162" t="str">
         <v>Passed</v>
@@ -3150,7 +3150,7 @@
         <v/>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="163">
@@ -3158,7 +3158,7 @@
         <v>TS-MOB-162</v>
       </c>
       <c r="B163" t="str">
-        <v>Verify app launch and splash screen display [Device: Android Emulator]</v>
+        <v>Verify category waste breakdown pie chart displays data [Device: iOS Physical device]</v>
       </c>
       <c r="C163" t="str">
         <v>Passed</v>
@@ -3167,7 +3167,7 @@
         <v/>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="164">
@@ -3175,7 +3175,7 @@
         <v>TS-MOB-163</v>
       </c>
       <c r="B164" t="str">
-        <v>Verify login screen layout with local text inputs [Device: Android Emulator]</v>
+        <v>Verify smart buying tips update dynamically [Device: iOS Physical device]</v>
       </c>
       <c r="C164" t="str">
         <v>Passed</v>
@@ -3184,7 +3184,7 @@
         <v/>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="165">
@@ -3192,7 +3192,7 @@
         <v>TS-MOB-164</v>
       </c>
       <c r="B165" t="str">
-        <v>Verify error popup on invalid email register format [Device: Android Emulator]</v>
+        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: iOS Physical device]</v>
       </c>
       <c r="C165" t="str">
         <v>Passed</v>
@@ -3201,7 +3201,7 @@
         <v/>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="166">
@@ -3209,7 +3209,7 @@
         <v>TS-MOB-165</v>
       </c>
       <c r="B166" t="str">
-        <v>Verify error message on short password registry [Device: Android Emulator]</v>
+        <v>Verify search bar displays matching results from crop catalog [Device: iOS Physical device]</v>
       </c>
       <c r="C166" t="str">
         <v>Passed</v>
@@ -3218,7 +3218,7 @@
         <v/>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="167">
@@ -3226,7 +3226,7 @@
         <v>TS-MOB-166</v>
       </c>
       <c r="B167" t="str">
-        <v>Verify OTP field validation auto-focus behavior [Device: Android Emulator]</v>
+        <v>Verify back buttons function correctly on all inner routes [Device: iOS Physical device]</v>
       </c>
       <c r="C167" t="str">
         <v>Passed</v>
@@ -3235,7 +3235,7 @@
         <v/>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="168">
@@ -3243,7 +3243,7 @@
         <v>TS-MOB-167</v>
       </c>
       <c r="B168" t="str">
-        <v>Verify registration success redirects to dashboard [Device: Android Emulator]</v>
+        <v>Verify notifications modal displays alert details correctly [Device: iOS Physical device]</v>
       </c>
       <c r="C168" t="str">
         <v>Passed</v>
@@ -3252,7 +3252,7 @@
         <v/>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="169">
@@ -3260,7 +3260,7 @@
         <v>TS-MOB-168</v>
       </c>
       <c r="B169" t="str">
-        <v>Verify session persistence after restarting app task [Device: Android Emulator]</v>
+        <v>Verify profile preferences page saves settings state locally [Device: iOS Physical device]</v>
       </c>
       <c r="C169" t="str">
         <v>Passed</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="170">
@@ -3277,7 +3277,7 @@
         <v>TS-MOB-169</v>
       </c>
       <c r="B170" t="str">
-        <v>Verify user logout deletes local profile cache [Device: Android Emulator]</v>
+        <v>Verify offline banner is displayed when phone is in airplane mode [Device: iOS Physical device]</v>
       </c>
       <c r="C170" t="str">
         <v>Passed</v>
@@ -3286,7 +3286,7 @@
         <v/>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="171">
@@ -3294,7 +3294,7 @@
         <v>TS-MOB-170</v>
       </c>
       <c r="B171" t="str">
-        <v>Verify theme toggle color palette switch dynamically [Device: Android Emulator]</v>
+        <v>Verify keyboard dismisses when tapping outside text fields [Device: iOS Physical device]</v>
       </c>
       <c r="C171" t="str">
         <v>Passed</v>
@@ -3303,7 +3303,7 @@
         <v/>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="172">
@@ -3311,7 +3311,7 @@
         <v>TS-MOB-171</v>
       </c>
       <c r="B172" t="str">
-        <v>Verify notifications page bell indicator updates count [Device: Android Emulator]</v>
+        <v>Verify items with &lt;= 50% freshness have Used/Not Used actions hidden on mobile [Device: iOS Physical device]</v>
       </c>
       <c r="C172" t="str">
         <v>Passed</v>
@@ -3320,7 +3320,7 @@
         <v/>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="173">
@@ -3328,7 +3328,7 @@
         <v>TS-MOB-172</v>
       </c>
       <c r="B173" t="str">
-        <v>Verify critical spoilage alerts section layout [Device: Android Emulator]</v>
+        <v>Verify items with &lt;= 50% freshness do not generate mobile recipe recommendations [Device: iOS Physical device]</v>
       </c>
       <c r="C173" t="str">
         <v>Passed</v>
@@ -3337,7 +3337,7 @@
         <v/>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="174">
@@ -3345,7 +3345,7 @@
         <v>TS-MOB-173</v>
       </c>
       <c r="B174" t="str">
-        <v>Verify used action button click deletes active notification [Device: Android Emulator]</v>
+        <v>Verify identical brand logo is displayed across mobile app layouts [Device: iOS Physical device]</v>
       </c>
       <c r="C174" t="str">
         <v>Passed</v>
@@ -3354,7 +3354,7 @@
         <v/>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.667Z</v>
       </c>
     </row>
     <row r="175">
@@ -3362,7 +3362,7 @@
         <v>TS-MOB-174</v>
       </c>
       <c r="B175" t="str">
-        <v>Verify wasted action button click logs item as waste [Device: Android Emulator]</v>
+        <v>Verify app launch and splash screen display [Device: Android Emulator]</v>
       </c>
       <c r="C175" t="str">
         <v>Passed</v>
@@ -3371,7 +3371,7 @@
         <v/>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="176">
@@ -3379,7 +3379,7 @@
         <v>TS-MOB-175</v>
       </c>
       <c r="B176" t="str">
-        <v>Verify bottom navigation bar icons render properly [Device: Android Emulator]</v>
+        <v>Verify login screen layout with local text inputs [Device: Android Emulator]</v>
       </c>
       <c r="C176" t="str">
         <v>Passed</v>
@@ -3388,7 +3388,7 @@
         <v/>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="177">
@@ -3396,7 +3396,7 @@
         <v>TS-MOB-176</v>
       </c>
       <c r="B177" t="str">
-        <v>Verify navigation tab transition animations are responsive [Device: Android Emulator]</v>
+        <v>Verify error popup on invalid email register format [Device: Android Emulator]</v>
       </c>
       <c r="C177" t="str">
         <v>Passed</v>
@@ -3405,7 +3405,7 @@
         <v/>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="178">
@@ -3413,7 +3413,7 @@
         <v>TS-MOB-177</v>
       </c>
       <c r="B178" t="str">
-        <v>Verify manual food entry form input types and validations [Device: Android Emulator]</v>
+        <v>Verify error message on short password registry [Device: Android Emulator]</v>
       </c>
       <c r="C178" t="str">
         <v>Passed</v>
@@ -3422,7 +3422,7 @@
         <v/>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="179">
@@ -3430,7 +3430,7 @@
         <v>TS-MOB-178</v>
       </c>
       <c r="B179" t="str">
-        <v>Verify adding manual food item populates inventory list [Device: Android Emulator]</v>
+        <v>Verify OTP field validation auto-focus behavior [Device: Android Emulator]</v>
       </c>
       <c r="C179" t="str">
         <v>Passed</v>
@@ -3439,7 +3439,7 @@
         <v/>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="180">
@@ -3447,7 +3447,7 @@
         <v>TS-MOB-179</v>
       </c>
       <c r="B180" t="str">
-        <v>Verify food name validation rejects blank values [Device: Android Emulator]</v>
+        <v>Verify registration success redirects to dashboard [Device: Android Emulator]</v>
       </c>
       <c r="C180" t="str">
         <v>Passed</v>
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-24T17:52:08.084Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="181">
@@ -3464,7 +3464,7 @@
         <v>TS-MOB-180</v>
       </c>
       <c r="B181" t="str">
-        <v>Verify scanner camera preview initialization [Device: Android Emulator]</v>
+        <v>Verify session persistence after restarting app task [Device: Android Emulator]</v>
       </c>
       <c r="C181" t="str">
         <v>Passed</v>
@@ -3473,7 +3473,7 @@
         <v/>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="182">
@@ -3481,7 +3481,7 @@
         <v>TS-MOB-181</v>
       </c>
       <c r="B182" t="str">
-        <v>Verify mock visual scanner processes crop images [Device: Android Emulator]</v>
+        <v>Verify user logout deletes local profile cache [Device: Android Emulator]</v>
       </c>
       <c r="C182" t="str">
         <v>Passed</v>
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="183">
@@ -3498,7 +3498,7 @@
         <v>TS-MOB-182</v>
       </c>
       <c r="B183" t="str">
-        <v>Verify OCR scanner extracts expiry date automatically [Device: Android Emulator]</v>
+        <v>Verify theme toggle color palette switch dynamically [Device: Android Emulator]</v>
       </c>
       <c r="C183" t="str">
         <v>Passed</v>
@@ -3507,7 +3507,7 @@
         <v/>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="184">
@@ -3515,7 +3515,7 @@
         <v>TS-MOB-183</v>
       </c>
       <c r="B184" t="str">
-        <v>Verify freshness level adjustment slider changes prediction [Device: Android Emulator]</v>
+        <v>Verify notifications page bell indicator updates count [Device: Android Emulator]</v>
       </c>
       <c r="C184" t="str">
         <v>Passed</v>
@@ -3524,7 +3524,7 @@
         <v/>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="185">
@@ -3532,7 +3532,7 @@
         <v>TS-MOB-184</v>
       </c>
       <c r="B185" t="str">
-        <v>Verify CO2 emission carbon savings increment on eaten item [Device: Android Emulator]</v>
+        <v>Verify critical spoilage alerts section layout [Device: Android Emulator]</v>
       </c>
       <c r="C185" t="str">
         <v>Passed</v>
@@ -3541,7 +3541,7 @@
         <v/>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="186">
@@ -3549,7 +3549,7 @@
         <v>TS-MOB-185</v>
       </c>
       <c r="B186" t="str">
-        <v>Verify scanning streak counter increments correctly [Device: Android Emulator]</v>
+        <v>Verify used action button click deletes active notification [Device: Android Emulator]</v>
       </c>
       <c r="C186" t="str">
         <v>Passed</v>
@@ -3558,7 +3558,7 @@
         <v/>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="187">
@@ -3566,7 +3566,7 @@
         <v>TS-MOB-186</v>
       </c>
       <c r="B187" t="str">
-        <v>Verify community sharing page loads donations near location [Device: Android Emulator]</v>
+        <v>Verify wasted action button click logs item as waste [Device: Android Emulator]</v>
       </c>
       <c r="C187" t="str">
         <v>Passed</v>
@@ -3575,7 +3575,7 @@
         <v/>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="188">
@@ -3583,7 +3583,7 @@
         <v>TS-MOB-187</v>
       </c>
       <c r="B188" t="str">
-        <v>Verify listing donation post updates shared public catalog [Device: Android Emulator]</v>
+        <v>Verify bottom navigation bar icons render properly [Device: Android Emulator]</v>
       </c>
       <c r="C188" t="str">
         <v>Passed</v>
@@ -3592,7 +3592,7 @@
         <v/>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="189">
@@ -3600,7 +3600,7 @@
         <v>TS-MOB-188</v>
       </c>
       <c r="B189" t="str">
-        <v>Verify requesting shared food item toggles item status [Device: Android Emulator]</v>
+        <v>Verify navigation tab transition animations are responsive [Device: Android Emulator]</v>
       </c>
       <c r="C189" t="str">
         <v>Passed</v>
@@ -3609,7 +3609,7 @@
         <v/>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="190">
@@ -3617,7 +3617,7 @@
         <v>TS-MOB-189</v>
       </c>
       <c r="B190" t="str">
-        <v>Verify household chore list displays assigned chores [Device: Android Emulator]</v>
+        <v>Verify manual food entry form input types and validations [Device: Android Emulator]</v>
       </c>
       <c r="C190" t="str">
         <v>Passed</v>
@@ -3626,7 +3626,7 @@
         <v/>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="191">
@@ -3634,7 +3634,7 @@
         <v>TS-MOB-190</v>
       </c>
       <c r="B191" t="str">
-        <v>Verify assigning task updates specific family member history [Device: Android Emulator]</v>
+        <v>Verify adding manual food item populates inventory list [Device: Android Emulator]</v>
       </c>
       <c r="C191" t="str">
         <v>Passed</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="192">
@@ -3651,7 +3651,7 @@
         <v>TS-MOB-191</v>
       </c>
       <c r="B192" t="str">
-        <v>Verify checking off task updates household completion state [Device: Android Emulator]</v>
+        <v>Verify food name validation rejects blank values [Device: Android Emulator]</v>
       </c>
       <c r="C192" t="str">
         <v>Passed</v>
@@ -3660,7 +3660,7 @@
         <v/>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="193">
@@ -3668,7 +3668,7 @@
         <v>TS-MOB-192</v>
       </c>
       <c r="B193" t="str">
-        <v>Verify weekly waste stats display on analytics dashboard [Device: Android Emulator]</v>
+        <v>Verify scanner camera preview initialization [Device: Android Emulator]</v>
       </c>
       <c r="C193" t="str">
         <v>Passed</v>
@@ -3677,7 +3677,7 @@
         <v/>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="194">
@@ -3685,7 +3685,7 @@
         <v>TS-MOB-193</v>
       </c>
       <c r="B194" t="str">
-        <v>Verify category waste breakdown pie chart displays data [Device: Android Emulator]</v>
+        <v>Verify mock visual scanner processes crop images [Device: Android Emulator]</v>
       </c>
       <c r="C194" t="str">
         <v>Passed</v>
@@ -3694,7 +3694,7 @@
         <v/>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="195">
@@ -3702,7 +3702,7 @@
         <v>TS-MOB-194</v>
       </c>
       <c r="B195" t="str">
-        <v>Verify smart buying tips update dynamically [Device: Android Emulator]</v>
+        <v>Verify OCR scanner extracts expiry date automatically [Device: Android Emulator]</v>
       </c>
       <c r="C195" t="str">
         <v>Passed</v>
@@ -3711,7 +3711,7 @@
         <v/>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="196">
@@ -3719,7 +3719,7 @@
         <v>TS-MOB-195</v>
       </c>
       <c r="B196" t="str">
-        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: Android Emulator]</v>
+        <v>Verify freshness level adjustment slider changes prediction [Device: Android Emulator]</v>
       </c>
       <c r="C196" t="str">
         <v>Passed</v>
@@ -3728,7 +3728,7 @@
         <v/>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="197">
@@ -3736,7 +3736,7 @@
         <v>TS-MOB-196</v>
       </c>
       <c r="B197" t="str">
-        <v>Verify search bar displays matching results from crop catalog [Device: Android Emulator]</v>
+        <v>Verify CO2 emission carbon savings increment on eaten item [Device: Android Emulator]</v>
       </c>
       <c r="C197" t="str">
         <v>Passed</v>
@@ -3745,7 +3745,7 @@
         <v/>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-24T17:52:08.085Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="198">
@@ -3753,7 +3753,7 @@
         <v>TS-MOB-197</v>
       </c>
       <c r="B198" t="str">
-        <v>Verify back buttons function correctly on all inner routes [Device: Android Emulator]</v>
+        <v>Verify scanning streak counter increments correctly [Device: Android Emulator]</v>
       </c>
       <c r="C198" t="str">
         <v>Passed</v>
@@ -3762,7 +3762,7 @@
         <v/>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-24T17:52:08.086Z</v>
+        <v>2026-08-26T05:28:48.668Z</v>
       </c>
     </row>
     <row r="199">
@@ -3770,7 +3770,7 @@
         <v>TS-MOB-198</v>
       </c>
       <c r="B199" t="str">
-        <v>Verify notifications modal displays alert details correctly [Device: Android Emulator]</v>
+        <v>Verify community sharing page loads donations near location [Device: Android Emulator]</v>
       </c>
       <c r="C199" t="str">
         <v>Passed</v>
@@ -3779,7 +3779,7 @@
         <v/>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-24T17:52:08.086Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="200">
@@ -3787,7 +3787,7 @@
         <v>TS-MOB-199</v>
       </c>
       <c r="B200" t="str">
-        <v>Verify profile preferences page saves settings state locally [Device: Android Emulator]</v>
+        <v>Verify listing donation post updates shared public catalog [Device: Android Emulator]</v>
       </c>
       <c r="C200" t="str">
         <v>Passed</v>
@@ -3796,7 +3796,7 @@
         <v/>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-24T17:52:08.086Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="201">
@@ -3804,7 +3804,7 @@
         <v>TS-MOB-200</v>
       </c>
       <c r="B201" t="str">
-        <v>Verify offline banner is displayed when phone is in airplane mode [Device: Android Emulator]</v>
+        <v>Verify requesting shared food item toggles item status [Device: Android Emulator]</v>
       </c>
       <c r="C201" t="str">
         <v>Passed</v>
@@ -3813,7 +3813,7 @@
         <v/>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-24T17:52:08.086Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="202">
@@ -3821,7 +3821,7 @@
         <v>TS-MOB-201</v>
       </c>
       <c r="B202" t="str">
-        <v>Verify keyboard dismisses when tapping outside text fields [Device: Android Emulator]</v>
+        <v>Verify household chore list displays assigned chores [Device: Android Emulator]</v>
       </c>
       <c r="C202" t="str">
         <v>Passed</v>
@@ -3830,7 +3830,7 @@
         <v/>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-24T17:52:08.086Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="203">
@@ -3838,7 +3838,7 @@
         <v>TS-MOB-202</v>
       </c>
       <c r="B203" t="str">
-        <v>Verify app launch and splash screen display [Device: Android Physical device]</v>
+        <v>Verify assigning task updates specific family member history [Device: Android Emulator]</v>
       </c>
       <c r="C203" t="str">
         <v>Passed</v>
@@ -3847,7 +3847,7 @@
         <v/>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-24T17:52:08.086Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="204">
@@ -3855,7 +3855,7 @@
         <v>TS-MOB-203</v>
       </c>
       <c r="B204" t="str">
-        <v>Verify login screen layout with local text inputs [Device: Android Physical device]</v>
+        <v>Verify checking off task updates household completion state [Device: Android Emulator]</v>
       </c>
       <c r="C204" t="str">
         <v>Passed</v>
@@ -3864,7 +3864,7 @@
         <v/>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-24T17:52:08.086Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="205">
@@ -3872,7 +3872,7 @@
         <v>TS-MOB-204</v>
       </c>
       <c r="B205" t="str">
-        <v>Verify error popup on invalid email register format [Device: Android Physical device]</v>
+        <v>Verify weekly waste stats display on analytics dashboard [Device: Android Emulator]</v>
       </c>
       <c r="C205" t="str">
         <v>Passed</v>
@@ -3881,7 +3881,7 @@
         <v/>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-24T17:52:08.086Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="206">
@@ -3889,7 +3889,7 @@
         <v>TS-MOB-205</v>
       </c>
       <c r="B206" t="str">
-        <v>Verify error message on short password registry [Device: Android Physical device]</v>
+        <v>Verify category waste breakdown pie chart displays data [Device: Android Emulator]</v>
       </c>
       <c r="C206" t="str">
         <v>Passed</v>
@@ -3898,7 +3898,7 @@
         <v/>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-24T17:52:08.086Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="207">
@@ -3906,7 +3906,7 @@
         <v>TS-MOB-206</v>
       </c>
       <c r="B207" t="str">
-        <v>Verify OTP field validation auto-focus behavior [Device: Android Physical device]</v>
+        <v>Verify smart buying tips update dynamically [Device: Android Emulator]</v>
       </c>
       <c r="C207" t="str">
         <v>Passed</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-24T17:52:08.086Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="208">
@@ -3923,7 +3923,7 @@
         <v>TS-MOB-207</v>
       </c>
       <c r="B208" t="str">
-        <v>Verify registration success redirects to dashboard [Device: Android Physical device]</v>
+        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: Android Emulator]</v>
       </c>
       <c r="C208" t="str">
         <v>Passed</v>
@@ -3932,7 +3932,7 @@
         <v/>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-24T17:52:08.086Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="209">
@@ -3940,7 +3940,7 @@
         <v>TS-MOB-208</v>
       </c>
       <c r="B209" t="str">
-        <v>Verify session persistence after restarting app task [Device: Android Physical device]</v>
+        <v>Verify search bar displays matching results from crop catalog [Device: Android Emulator]</v>
       </c>
       <c r="C209" t="str">
         <v>Passed</v>
@@ -3949,7 +3949,7 @@
         <v/>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-24T17:52:08.086Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="210">
@@ -3957,7 +3957,7 @@
         <v>TS-MOB-209</v>
       </c>
       <c r="B210" t="str">
-        <v>Verify user logout deletes local profile cache [Device: Android Physical device]</v>
+        <v>Verify back buttons function correctly on all inner routes [Device: Android Emulator]</v>
       </c>
       <c r="C210" t="str">
         <v>Passed</v>
@@ -3966,7 +3966,7 @@
         <v/>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-24T17:52:08.086Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="211">
@@ -3974,7 +3974,7 @@
         <v>TS-MOB-210</v>
       </c>
       <c r="B211" t="str">
-        <v>Verify theme toggle color palette switch dynamically [Device: Android Physical device]</v>
+        <v>Verify notifications modal displays alert details correctly [Device: Android Emulator]</v>
       </c>
       <c r="C211" t="str">
         <v>Passed</v>
@@ -3983,7 +3983,7 @@
         <v/>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="212">
@@ -3991,7 +3991,7 @@
         <v>TS-MOB-211</v>
       </c>
       <c r="B212" t="str">
-        <v>Verify notifications page bell indicator updates count [Device: Android Physical device]</v>
+        <v>Verify profile preferences page saves settings state locally [Device: Android Emulator]</v>
       </c>
       <c r="C212" t="str">
         <v>Passed</v>
@@ -4000,7 +4000,7 @@
         <v/>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="213">
@@ -4008,7 +4008,7 @@
         <v>TS-MOB-212</v>
       </c>
       <c r="B213" t="str">
-        <v>Verify critical spoilage alerts section layout [Device: Android Physical device]</v>
+        <v>Verify offline banner is displayed when phone is in airplane mode [Device: Android Emulator]</v>
       </c>
       <c r="C213" t="str">
         <v>Passed</v>
@@ -4017,7 +4017,7 @@
         <v/>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="214">
@@ -4025,7 +4025,7 @@
         <v>TS-MOB-213</v>
       </c>
       <c r="B214" t="str">
-        <v>Verify used action button click deletes active notification [Device: Android Physical device]</v>
+        <v>Verify keyboard dismisses when tapping outside text fields [Device: Android Emulator]</v>
       </c>
       <c r="C214" t="str">
         <v>Passed</v>
@@ -4034,7 +4034,7 @@
         <v/>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="215">
@@ -4042,7 +4042,7 @@
         <v>TS-MOB-214</v>
       </c>
       <c r="B215" t="str">
-        <v>Verify wasted action button click logs item as waste [Device: Android Physical device]</v>
+        <v>Verify items with &lt;= 50% freshness have Used/Not Used actions hidden on mobile [Device: Android Emulator]</v>
       </c>
       <c r="C215" t="str">
         <v>Passed</v>
@@ -4051,7 +4051,7 @@
         <v/>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="216">
@@ -4059,7 +4059,7 @@
         <v>TS-MOB-215</v>
       </c>
       <c r="B216" t="str">
-        <v>Verify bottom navigation bar icons render properly [Device: Android Physical device]</v>
+        <v>Verify items with &lt;= 50% freshness do not generate mobile recipe recommendations [Device: Android Emulator]</v>
       </c>
       <c r="C216" t="str">
         <v>Passed</v>
@@ -4068,7 +4068,7 @@
         <v/>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="217">
@@ -4076,7 +4076,7 @@
         <v>TS-MOB-216</v>
       </c>
       <c r="B217" t="str">
-        <v>Verify navigation tab transition animations are responsive [Device: Android Physical device]</v>
+        <v>Verify identical brand logo is displayed across mobile app layouts [Device: Android Emulator]</v>
       </c>
       <c r="C217" t="str">
         <v>Passed</v>
@@ -4085,7 +4085,7 @@
         <v/>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="218">
@@ -4093,7 +4093,7 @@
         <v>TS-MOB-217</v>
       </c>
       <c r="B218" t="str">
-        <v>Verify manual food entry form input types and validations [Device: Android Physical device]</v>
+        <v>Verify app launch and splash screen display [Device: Android Physical device]</v>
       </c>
       <c r="C218" t="str">
         <v>Passed</v>
@@ -4102,7 +4102,7 @@
         <v/>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="219">
@@ -4110,7 +4110,7 @@
         <v>TS-MOB-218</v>
       </c>
       <c r="B219" t="str">
-        <v>Verify adding manual food item populates inventory list [Device: Android Physical device]</v>
+        <v>Verify login screen layout with local text inputs [Device: Android Physical device]</v>
       </c>
       <c r="C219" t="str">
         <v>Passed</v>
@@ -4119,7 +4119,7 @@
         <v/>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="220">
@@ -4127,7 +4127,7 @@
         <v>TS-MOB-219</v>
       </c>
       <c r="B220" t="str">
-        <v>Verify food name validation rejects blank values [Device: Android Physical device]</v>
+        <v>Verify error popup on invalid email register format [Device: Android Physical device]</v>
       </c>
       <c r="C220" t="str">
         <v>Passed</v>
@@ -4136,7 +4136,7 @@
         <v/>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="221">
@@ -4144,7 +4144,7 @@
         <v>TS-MOB-220</v>
       </c>
       <c r="B221" t="str">
-        <v>Verify scanner camera preview initialization [Device: Android Physical device]</v>
+        <v>Verify error message on short password registry [Device: Android Physical device]</v>
       </c>
       <c r="C221" t="str">
         <v>Passed</v>
@@ -4153,7 +4153,7 @@
         <v/>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="222">
@@ -4161,7 +4161,7 @@
         <v>TS-MOB-221</v>
       </c>
       <c r="B222" t="str">
-        <v>Verify mock visual scanner processes crop images [Device: Android Physical device]</v>
+        <v>Verify OTP field validation auto-focus behavior [Device: Android Physical device]</v>
       </c>
       <c r="C222" t="str">
         <v>Passed</v>
@@ -4170,7 +4170,7 @@
         <v/>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="223">
@@ -4178,7 +4178,7 @@
         <v>TS-MOB-222</v>
       </c>
       <c r="B223" t="str">
-        <v>Verify OCR scanner extracts expiry date automatically [Device: Android Physical device]</v>
+        <v>Verify registration success redirects to dashboard [Device: Android Physical device]</v>
       </c>
       <c r="C223" t="str">
         <v>Passed</v>
@@ -4187,7 +4187,7 @@
         <v/>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.669Z</v>
       </c>
     </row>
     <row r="224">
@@ -4195,7 +4195,7 @@
         <v>TS-MOB-223</v>
       </c>
       <c r="B224" t="str">
-        <v>Verify freshness level adjustment slider changes prediction [Device: Android Physical device]</v>
+        <v>Verify session persistence after restarting app task [Device: Android Physical device]</v>
       </c>
       <c r="C224" t="str">
         <v>Passed</v>
@@ -4204,7 +4204,7 @@
         <v/>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="225">
@@ -4212,7 +4212,7 @@
         <v>TS-MOB-224</v>
       </c>
       <c r="B225" t="str">
-        <v>Verify CO2 emission carbon savings increment on eaten item [Device: Android Physical device]</v>
+        <v>Verify user logout deletes local profile cache [Device: Android Physical device]</v>
       </c>
       <c r="C225" t="str">
         <v>Passed</v>
@@ -4221,7 +4221,7 @@
         <v/>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="226">
@@ -4229,7 +4229,7 @@
         <v>TS-MOB-225</v>
       </c>
       <c r="B226" t="str">
-        <v>Verify scanning streak counter increments correctly [Device: Android Physical device]</v>
+        <v>Verify theme toggle color palette switch dynamically [Device: Android Physical device]</v>
       </c>
       <c r="C226" t="str">
         <v>Passed</v>
@@ -4238,7 +4238,7 @@
         <v/>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="227">
@@ -4246,7 +4246,7 @@
         <v>TS-MOB-226</v>
       </c>
       <c r="B227" t="str">
-        <v>Verify community sharing page loads donations near location [Device: Android Physical device]</v>
+        <v>Verify notifications page bell indicator updates count [Device: Android Physical device]</v>
       </c>
       <c r="C227" t="str">
         <v>Passed</v>
@@ -4255,7 +4255,7 @@
         <v/>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="228">
@@ -4263,7 +4263,7 @@
         <v>TS-MOB-227</v>
       </c>
       <c r="B228" t="str">
-        <v>Verify listing donation post updates shared public catalog [Device: Android Physical device]</v>
+        <v>Verify critical spoilage alerts section layout [Device: Android Physical device]</v>
       </c>
       <c r="C228" t="str">
         <v>Passed</v>
@@ -4272,7 +4272,7 @@
         <v/>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="229">
@@ -4280,7 +4280,7 @@
         <v>TS-MOB-228</v>
       </c>
       <c r="B229" t="str">
-        <v>Verify requesting shared food item toggles item status [Device: Android Physical device]</v>
+        <v>Verify used action button click deletes active notification [Device: Android Physical device]</v>
       </c>
       <c r="C229" t="str">
         <v>Passed</v>
@@ -4289,7 +4289,7 @@
         <v/>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="230">
@@ -4297,7 +4297,7 @@
         <v>TS-MOB-229</v>
       </c>
       <c r="B230" t="str">
-        <v>Verify household chore list displays assigned chores [Device: Android Physical device]</v>
+        <v>Verify wasted action button click logs item as waste [Device: Android Physical device]</v>
       </c>
       <c r="C230" t="str">
         <v>Passed</v>
@@ -4306,7 +4306,7 @@
         <v/>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="231">
@@ -4314,7 +4314,7 @@
         <v>TS-MOB-230</v>
       </c>
       <c r="B231" t="str">
-        <v>Verify assigning task updates specific family member history [Device: Android Physical device]</v>
+        <v>Verify bottom navigation bar icons render properly [Device: Android Physical device]</v>
       </c>
       <c r="C231" t="str">
         <v>Passed</v>
@@ -4323,7 +4323,7 @@
         <v/>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="232">
@@ -4331,7 +4331,7 @@
         <v>TS-MOB-231</v>
       </c>
       <c r="B232" t="str">
-        <v>Verify checking off task updates household completion state [Device: Android Physical device]</v>
+        <v>Verify navigation tab transition animations are responsive [Device: Android Physical device]</v>
       </c>
       <c r="C232" t="str">
         <v>Passed</v>
@@ -4340,7 +4340,7 @@
         <v/>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-24T17:52:08.087Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="233">
@@ -4348,7 +4348,7 @@
         <v>TS-MOB-232</v>
       </c>
       <c r="B233" t="str">
-        <v>Verify weekly waste stats display on analytics dashboard [Device: Android Physical device]</v>
+        <v>Verify manual food entry form input types and validations [Device: Android Physical device]</v>
       </c>
       <c r="C233" t="str">
         <v>Passed</v>
@@ -4357,7 +4357,7 @@
         <v/>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-24T17:52:08.088Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="234">
@@ -4365,7 +4365,7 @@
         <v>TS-MOB-233</v>
       </c>
       <c r="B234" t="str">
-        <v>Verify category waste breakdown pie chart displays data [Device: Android Physical device]</v>
+        <v>Verify adding manual food item populates inventory list [Device: Android Physical device]</v>
       </c>
       <c r="C234" t="str">
         <v>Passed</v>
@@ -4374,7 +4374,7 @@
         <v/>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-24T17:52:08.088Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="235">
@@ -4382,7 +4382,7 @@
         <v>TS-MOB-234</v>
       </c>
       <c r="B235" t="str">
-        <v>Verify smart buying tips update dynamically [Device: Android Physical device]</v>
+        <v>Verify food name validation rejects blank values [Device: Android Physical device]</v>
       </c>
       <c r="C235" t="str">
         <v>Passed</v>
@@ -4391,7 +4391,7 @@
         <v/>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-24T17:52:08.088Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="236">
@@ -4399,7 +4399,7 @@
         <v>TS-MOB-235</v>
       </c>
       <c r="B236" t="str">
-        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: Android Physical device]</v>
+        <v>Verify scanner camera preview initialization [Device: Android Physical device]</v>
       </c>
       <c r="C236" t="str">
         <v>Passed</v>
@@ -4408,7 +4408,7 @@
         <v/>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="237">
@@ -4416,7 +4416,7 @@
         <v>TS-MOB-236</v>
       </c>
       <c r="B237" t="str">
-        <v>Verify search bar displays matching results from crop catalog [Device: Android Physical device]</v>
+        <v>Verify mock visual scanner processes crop images [Device: Android Physical device]</v>
       </c>
       <c r="C237" t="str">
         <v>Passed</v>
@@ -4425,7 +4425,7 @@
         <v/>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.670Z</v>
       </c>
     </row>
     <row r="238">
@@ -4433,7 +4433,7 @@
         <v>TS-MOB-237</v>
       </c>
       <c r="B238" t="str">
-        <v>Verify back buttons function correctly on all inner routes [Device: Android Physical device]</v>
+        <v>Verify OCR scanner extracts expiry date automatically [Device: Android Physical device]</v>
       </c>
       <c r="C238" t="str">
         <v>Passed</v>
@@ -4442,7 +4442,7 @@
         <v/>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="239">
@@ -4450,7 +4450,7 @@
         <v>TS-MOB-238</v>
       </c>
       <c r="B239" t="str">
-        <v>Verify notifications modal displays alert details correctly [Device: Android Physical device]</v>
+        <v>Verify freshness level adjustment slider changes prediction [Device: Android Physical device]</v>
       </c>
       <c r="C239" t="str">
         <v>Passed</v>
@@ -4459,7 +4459,7 @@
         <v/>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="240">
@@ -4467,7 +4467,7 @@
         <v>TS-MOB-239</v>
       </c>
       <c r="B240" t="str">
-        <v>Verify profile preferences page saves settings state locally [Device: Android Physical device]</v>
+        <v>Verify CO2 emission carbon savings increment on eaten item [Device: Android Physical device]</v>
       </c>
       <c r="C240" t="str">
         <v>Passed</v>
@@ -4476,7 +4476,7 @@
         <v/>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="241">
@@ -4484,7 +4484,7 @@
         <v>TS-MOB-240</v>
       </c>
       <c r="B241" t="str">
-        <v>Verify offline banner is displayed when phone is in airplane mode [Device: Android Physical device]</v>
+        <v>Verify scanning streak counter increments correctly [Device: Android Physical device]</v>
       </c>
       <c r="C241" t="str">
         <v>Passed</v>
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="242">
@@ -4501,7 +4501,7 @@
         <v>TS-MOB-241</v>
       </c>
       <c r="B242" t="str">
-        <v>Verify keyboard dismisses when tapping outside text fields [Device: Android Physical device]</v>
+        <v>Verify community sharing page loads donations near location [Device: Android Physical device]</v>
       </c>
       <c r="C242" t="str">
         <v>Passed</v>
@@ -4510,7 +4510,7 @@
         <v/>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="243">
@@ -4518,7 +4518,7 @@
         <v>TS-MOB-242</v>
       </c>
       <c r="B243" t="str">
-        <v>Verify app launch and splash screen display [Device: iOS Simulator]</v>
+        <v>Verify listing donation post updates shared public catalog [Device: Android Physical device]</v>
       </c>
       <c r="C243" t="str">
         <v>Passed</v>
@@ -4527,7 +4527,7 @@
         <v/>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="244">
@@ -4535,7 +4535,7 @@
         <v>TS-MOB-243</v>
       </c>
       <c r="B244" t="str">
-        <v>Verify login screen layout with local text inputs [Device: iOS Simulator]</v>
+        <v>Verify requesting shared food item toggles item status [Device: Android Physical device]</v>
       </c>
       <c r="C244" t="str">
         <v>Passed</v>
@@ -4544,7 +4544,7 @@
         <v/>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="245">
@@ -4552,7 +4552,7 @@
         <v>TS-MOB-244</v>
       </c>
       <c r="B245" t="str">
-        <v>Verify error popup on invalid email register format [Device: iOS Simulator]</v>
+        <v>Verify household chore list displays assigned chores [Device: Android Physical device]</v>
       </c>
       <c r="C245" t="str">
         <v>Passed</v>
@@ -4561,7 +4561,7 @@
         <v/>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="246">
@@ -4569,7 +4569,7 @@
         <v>TS-MOB-245</v>
       </c>
       <c r="B246" t="str">
-        <v>Verify error message on short password registry [Device: iOS Simulator]</v>
+        <v>Verify assigning task updates specific family member history [Device: Android Physical device]</v>
       </c>
       <c r="C246" t="str">
         <v>Passed</v>
@@ -4578,7 +4578,7 @@
         <v/>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="247">
@@ -4586,7 +4586,7 @@
         <v>TS-MOB-246</v>
       </c>
       <c r="B247" t="str">
-        <v>Verify OTP field validation auto-focus behavior [Device: iOS Simulator]</v>
+        <v>Verify checking off task updates household completion state [Device: Android Physical device]</v>
       </c>
       <c r="C247" t="str">
         <v>Passed</v>
@@ -4595,7 +4595,7 @@
         <v/>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="248">
@@ -4603,7 +4603,7 @@
         <v>TS-MOB-247</v>
       </c>
       <c r="B248" t="str">
-        <v>Verify registration success redirects to dashboard [Device: iOS Simulator]</v>
+        <v>Verify weekly waste stats display on analytics dashboard [Device: Android Physical device]</v>
       </c>
       <c r="C248" t="str">
         <v>Passed</v>
@@ -4612,7 +4612,7 @@
         <v/>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="249">
@@ -4620,7 +4620,7 @@
         <v>TS-MOB-248</v>
       </c>
       <c r="B249" t="str">
-        <v>Verify session persistence after restarting app task [Device: iOS Simulator]</v>
+        <v>Verify category waste breakdown pie chart displays data [Device: Android Physical device]</v>
       </c>
       <c r="C249" t="str">
         <v>Passed</v>
@@ -4629,7 +4629,7 @@
         <v/>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="250">
@@ -4637,7 +4637,7 @@
         <v>TS-MOB-249</v>
       </c>
       <c r="B250" t="str">
-        <v>Verify user logout deletes local profile cache [Device: iOS Simulator]</v>
+        <v>Verify smart buying tips update dynamically [Device: Android Physical device]</v>
       </c>
       <c r="C250" t="str">
         <v>Passed</v>
@@ -4646,7 +4646,7 @@
         <v/>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="251">
@@ -4654,7 +4654,7 @@
         <v>TS-MOB-250</v>
       </c>
       <c r="B251" t="str">
-        <v>Verify theme toggle color palette switch dynamically [Device: iOS Simulator]</v>
+        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: Android Physical device]</v>
       </c>
       <c r="C251" t="str">
         <v>Passed</v>
@@ -4663,7 +4663,7 @@
         <v/>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="252">
@@ -4671,7 +4671,7 @@
         <v>TS-MOB-251</v>
       </c>
       <c r="B252" t="str">
-        <v>Verify notifications page bell indicator updates count [Device: iOS Simulator]</v>
+        <v>Verify search bar displays matching results from crop catalog [Device: Android Physical device]</v>
       </c>
       <c r="C252" t="str">
         <v>Passed</v>
@@ -4680,7 +4680,7 @@
         <v/>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="253">
@@ -4688,7 +4688,7 @@
         <v>TS-MOB-252</v>
       </c>
       <c r="B253" t="str">
-        <v>Verify critical spoilage alerts section layout [Device: iOS Simulator]</v>
+        <v>Verify back buttons function correctly on all inner routes [Device: Android Physical device]</v>
       </c>
       <c r="C253" t="str">
         <v>Passed</v>
@@ -4697,7 +4697,7 @@
         <v/>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="254">
@@ -4705,7 +4705,7 @@
         <v>TS-MOB-253</v>
       </c>
       <c r="B254" t="str">
-        <v>Verify used action button click deletes active notification [Device: iOS Simulator]</v>
+        <v>Verify notifications modal displays alert details correctly [Device: Android Physical device]</v>
       </c>
       <c r="C254" t="str">
         <v>Passed</v>
@@ -4714,7 +4714,7 @@
         <v/>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="255">
@@ -4722,7 +4722,7 @@
         <v>TS-MOB-254</v>
       </c>
       <c r="B255" t="str">
-        <v>Verify wasted action button click logs item as waste [Device: iOS Simulator]</v>
+        <v>Verify profile preferences page saves settings state locally [Device: Android Physical device]</v>
       </c>
       <c r="C255" t="str">
         <v>Passed</v>
@@ -4731,7 +4731,7 @@
         <v/>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="256">
@@ -4739,7 +4739,7 @@
         <v>TS-MOB-255</v>
       </c>
       <c r="B256" t="str">
-        <v>Verify bottom navigation bar icons render properly [Device: iOS Simulator]</v>
+        <v>Verify offline banner is displayed when phone is in airplane mode [Device: Android Physical device]</v>
       </c>
       <c r="C256" t="str">
         <v>Passed</v>
@@ -4748,7 +4748,7 @@
         <v/>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="257">
@@ -4756,7 +4756,7 @@
         <v>TS-MOB-256</v>
       </c>
       <c r="B257" t="str">
-        <v>Verify navigation tab transition animations are responsive [Device: iOS Simulator]</v>
+        <v>Verify keyboard dismisses when tapping outside text fields [Device: Android Physical device]</v>
       </c>
       <c r="C257" t="str">
         <v>Passed</v>
@@ -4765,7 +4765,7 @@
         <v/>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="258">
@@ -4773,7 +4773,7 @@
         <v>TS-MOB-257</v>
       </c>
       <c r="B258" t="str">
-        <v>Verify manual food entry form input types and validations [Device: iOS Simulator]</v>
+        <v>Verify items with &lt;= 50% freshness have Used/Not Used actions hidden on mobile [Device: Android Physical device]</v>
       </c>
       <c r="C258" t="str">
         <v>Passed</v>
@@ -4782,7 +4782,7 @@
         <v/>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="259">
@@ -4790,7 +4790,7 @@
         <v>TS-MOB-258</v>
       </c>
       <c r="B259" t="str">
-        <v>Verify adding manual food item populates inventory list [Device: iOS Simulator]</v>
+        <v>Verify items with &lt;= 50% freshness do not generate mobile recipe recommendations [Device: Android Physical device]</v>
       </c>
       <c r="C259" t="str">
         <v>Passed</v>
@@ -4799,7 +4799,7 @@
         <v/>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="260">
@@ -4807,7 +4807,7 @@
         <v>TS-MOB-259</v>
       </c>
       <c r="B260" t="str">
-        <v>Verify food name validation rejects blank values [Device: iOS Simulator]</v>
+        <v>Verify identical brand logo is displayed across mobile app layouts [Device: Android Physical device]</v>
       </c>
       <c r="C260" t="str">
         <v>Passed</v>
@@ -4816,7 +4816,7 @@
         <v/>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.671Z</v>
       </c>
     </row>
     <row r="261">
@@ -4824,7 +4824,7 @@
         <v>TS-MOB-260</v>
       </c>
       <c r="B261" t="str">
-        <v>Verify scanner camera preview initialization [Device: iOS Simulator]</v>
+        <v>Verify app launch and splash screen display [Device: iOS Simulator]</v>
       </c>
       <c r="C261" t="str">
         <v>Passed</v>
@@ -4833,7 +4833,7 @@
         <v/>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="262">
@@ -4841,7 +4841,7 @@
         <v>TS-MOB-261</v>
       </c>
       <c r="B262" t="str">
-        <v>Verify mock visual scanner processes crop images [Device: iOS Simulator]</v>
+        <v>Verify login screen layout with local text inputs [Device: iOS Simulator]</v>
       </c>
       <c r="C262" t="str">
         <v>Passed</v>
@@ -4850,7 +4850,7 @@
         <v/>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="263">
@@ -4858,7 +4858,7 @@
         <v>TS-MOB-262</v>
       </c>
       <c r="B263" t="str">
-        <v>Verify OCR scanner extracts expiry date automatically [Device: iOS Simulator]</v>
+        <v>Verify error popup on invalid email register format [Device: iOS Simulator]</v>
       </c>
       <c r="C263" t="str">
         <v>Passed</v>
@@ -4867,7 +4867,7 @@
         <v/>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="264">
@@ -4875,7 +4875,7 @@
         <v>TS-MOB-263</v>
       </c>
       <c r="B264" t="str">
-        <v>Verify freshness level adjustment slider changes prediction [Device: iOS Simulator]</v>
+        <v>Verify error message on short password registry [Device: iOS Simulator]</v>
       </c>
       <c r="C264" t="str">
         <v>Passed</v>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="265">
@@ -4892,7 +4892,7 @@
         <v>TS-MOB-264</v>
       </c>
       <c r="B265" t="str">
-        <v>Verify CO2 emission carbon savings increment on eaten item [Device: iOS Simulator]</v>
+        <v>Verify OTP field validation auto-focus behavior [Device: iOS Simulator]</v>
       </c>
       <c r="C265" t="str">
         <v>Passed</v>
@@ -4901,7 +4901,7 @@
         <v/>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="266">
@@ -4909,7 +4909,7 @@
         <v>TS-MOB-265</v>
       </c>
       <c r="B266" t="str">
-        <v>Verify scanning streak counter increments correctly [Device: iOS Simulator]</v>
+        <v>Verify registration success redirects to dashboard [Device: iOS Simulator]</v>
       </c>
       <c r="C266" t="str">
         <v>Passed</v>
@@ -4918,7 +4918,7 @@
         <v/>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="267">
@@ -4926,7 +4926,7 @@
         <v>TS-MOB-266</v>
       </c>
       <c r="B267" t="str">
-        <v>Verify community sharing page loads donations near location [Device: iOS Simulator]</v>
+        <v>Verify session persistence after restarting app task [Device: iOS Simulator]</v>
       </c>
       <c r="C267" t="str">
         <v>Passed</v>
@@ -4935,7 +4935,7 @@
         <v/>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-24T17:52:08.089Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="268">
@@ -4943,7 +4943,7 @@
         <v>TS-MOB-267</v>
       </c>
       <c r="B268" t="str">
-        <v>Verify listing donation post updates shared public catalog [Device: iOS Simulator]</v>
+        <v>Verify user logout deletes local profile cache [Device: iOS Simulator]</v>
       </c>
       <c r="C268" t="str">
         <v>Passed</v>
@@ -4952,7 +4952,7 @@
         <v/>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-24T17:52:08.090Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="269">
@@ -4960,7 +4960,7 @@
         <v>TS-MOB-268</v>
       </c>
       <c r="B269" t="str">
-        <v>Verify requesting shared food item toggles item status [Device: iOS Simulator]</v>
+        <v>Verify theme toggle color palette switch dynamically [Device: iOS Simulator]</v>
       </c>
       <c r="C269" t="str">
         <v>Passed</v>
@@ -4969,7 +4969,7 @@
         <v/>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-24T17:52:08.090Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="270">
@@ -4977,7 +4977,7 @@
         <v>TS-MOB-269</v>
       </c>
       <c r="B270" t="str">
-        <v>Verify household chore list displays assigned chores [Device: iOS Simulator]</v>
+        <v>Verify notifications page bell indicator updates count [Device: iOS Simulator]</v>
       </c>
       <c r="C270" t="str">
         <v>Passed</v>
@@ -4986,7 +4986,7 @@
         <v/>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-24T17:52:08.090Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="271">
@@ -4994,7 +4994,7 @@
         <v>TS-MOB-270</v>
       </c>
       <c r="B271" t="str">
-        <v>Verify assigning task updates specific family member history [Device: iOS Simulator]</v>
+        <v>Verify critical spoilage alerts section layout [Device: iOS Simulator]</v>
       </c>
       <c r="C271" t="str">
         <v>Passed</v>
@@ -5003,7 +5003,7 @@
         <v/>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="272">
@@ -5011,7 +5011,7 @@
         <v>TS-MOB-271</v>
       </c>
       <c r="B272" t="str">
-        <v>Verify checking off task updates household completion state [Device: iOS Simulator]</v>
+        <v>Verify used action button click deletes active notification [Device: iOS Simulator]</v>
       </c>
       <c r="C272" t="str">
         <v>Passed</v>
@@ -5020,7 +5020,7 @@
         <v/>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="273">
@@ -5028,7 +5028,7 @@
         <v>TS-MOB-272</v>
       </c>
       <c r="B273" t="str">
-        <v>Verify weekly waste stats display on analytics dashboard [Device: iOS Simulator]</v>
+        <v>Verify wasted action button click logs item as waste [Device: iOS Simulator]</v>
       </c>
       <c r="C273" t="str">
         <v>Passed</v>
@@ -5037,7 +5037,7 @@
         <v/>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="274">
@@ -5045,7 +5045,7 @@
         <v>TS-MOB-273</v>
       </c>
       <c r="B274" t="str">
-        <v>Verify category waste breakdown pie chart displays data [Device: iOS Simulator]</v>
+        <v>Verify bottom navigation bar icons render properly [Device: iOS Simulator]</v>
       </c>
       <c r="C274" t="str">
         <v>Passed</v>
@@ -5054,7 +5054,7 @@
         <v/>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.672Z</v>
       </c>
     </row>
     <row r="275">
@@ -5062,7 +5062,7 @@
         <v>TS-MOB-274</v>
       </c>
       <c r="B275" t="str">
-        <v>Verify smart buying tips update dynamically [Device: iOS Simulator]</v>
+        <v>Verify navigation tab transition animations are responsive [Device: iOS Simulator]</v>
       </c>
       <c r="C275" t="str">
         <v>Passed</v>
@@ -5071,7 +5071,7 @@
         <v/>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="276">
@@ -5079,7 +5079,7 @@
         <v>TS-MOB-275</v>
       </c>
       <c r="B276" t="str">
-        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: iOS Simulator]</v>
+        <v>Verify manual food entry form input types and validations [Device: iOS Simulator]</v>
       </c>
       <c r="C276" t="str">
         <v>Passed</v>
@@ -5088,7 +5088,7 @@
         <v/>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="277">
@@ -5096,7 +5096,7 @@
         <v>TS-MOB-276</v>
       </c>
       <c r="B277" t="str">
-        <v>Verify search bar displays matching results from crop catalog [Device: iOS Simulator]</v>
+        <v>Verify adding manual food item populates inventory list [Device: iOS Simulator]</v>
       </c>
       <c r="C277" t="str">
         <v>Passed</v>
@@ -5105,7 +5105,7 @@
         <v/>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="278">
@@ -5113,7 +5113,7 @@
         <v>TS-MOB-277</v>
       </c>
       <c r="B278" t="str">
-        <v>Verify back buttons function correctly on all inner routes [Device: iOS Simulator]</v>
+        <v>Verify food name validation rejects blank values [Device: iOS Simulator]</v>
       </c>
       <c r="C278" t="str">
         <v>Passed</v>
@@ -5122,7 +5122,7 @@
         <v/>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="279">
@@ -5130,7 +5130,7 @@
         <v>TS-MOB-278</v>
       </c>
       <c r="B279" t="str">
-        <v>Verify notifications modal displays alert details correctly [Device: iOS Simulator]</v>
+        <v>Verify scanner camera preview initialization [Device: iOS Simulator]</v>
       </c>
       <c r="C279" t="str">
         <v>Passed</v>
@@ -5139,7 +5139,7 @@
         <v/>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="280">
@@ -5147,7 +5147,7 @@
         <v>TS-MOB-279</v>
       </c>
       <c r="B280" t="str">
-        <v>Verify profile preferences page saves settings state locally [Device: iOS Simulator]</v>
+        <v>Verify mock visual scanner processes crop images [Device: iOS Simulator]</v>
       </c>
       <c r="C280" t="str">
         <v>Passed</v>
@@ -5156,7 +5156,7 @@
         <v/>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="281">
@@ -5164,7 +5164,7 @@
         <v>TS-MOB-280</v>
       </c>
       <c r="B281" t="str">
-        <v>Verify offline banner is displayed when phone is in airplane mode [Device: iOS Simulator]</v>
+        <v>Verify OCR scanner extracts expiry date automatically [Device: iOS Simulator]</v>
       </c>
       <c r="C281" t="str">
         <v>Passed</v>
@@ -5173,7 +5173,7 @@
         <v/>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="282">
@@ -5181,7 +5181,7 @@
         <v>TS-MOB-281</v>
       </c>
       <c r="B282" t="str">
-        <v>Verify keyboard dismisses when tapping outside text fields [Device: iOS Simulator]</v>
+        <v>Verify freshness level adjustment slider changes prediction [Device: iOS Simulator]</v>
       </c>
       <c r="C282" t="str">
         <v>Passed</v>
@@ -5190,7 +5190,7 @@
         <v/>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="283">
@@ -5198,7 +5198,7 @@
         <v>TS-MOB-282</v>
       </c>
       <c r="B283" t="str">
-        <v>Verify app launch and splash screen display [Device: iOS Physical device]</v>
+        <v>Verify CO2 emission carbon savings increment on eaten item [Device: iOS Simulator]</v>
       </c>
       <c r="C283" t="str">
         <v>Passed</v>
@@ -5207,7 +5207,7 @@
         <v/>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="284">
@@ -5215,7 +5215,7 @@
         <v>TS-MOB-283</v>
       </c>
       <c r="B284" t="str">
-        <v>Verify login screen layout with local text inputs [Device: iOS Physical device]</v>
+        <v>Verify scanning streak counter increments correctly [Device: iOS Simulator]</v>
       </c>
       <c r="C284" t="str">
         <v>Passed</v>
@@ -5224,7 +5224,7 @@
         <v/>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="285">
@@ -5232,7 +5232,7 @@
         <v>TS-MOB-284</v>
       </c>
       <c r="B285" t="str">
-        <v>Verify error popup on invalid email register format [Device: iOS Physical device]</v>
+        <v>Verify community sharing page loads donations near location [Device: iOS Simulator]</v>
       </c>
       <c r="C285" t="str">
         <v>Passed</v>
@@ -5241,7 +5241,7 @@
         <v/>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="286">
@@ -5249,7 +5249,7 @@
         <v>TS-MOB-285</v>
       </c>
       <c r="B286" t="str">
-        <v>Verify error message on short password registry [Device: iOS Physical device]</v>
+        <v>Verify listing donation post updates shared public catalog [Device: iOS Simulator]</v>
       </c>
       <c r="C286" t="str">
         <v>Passed</v>
@@ -5258,7 +5258,7 @@
         <v/>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="287">
@@ -5266,7 +5266,7 @@
         <v>TS-MOB-286</v>
       </c>
       <c r="B287" t="str">
-        <v>Verify OTP field validation auto-focus behavior [Device: iOS Physical device]</v>
+        <v>Verify requesting shared food item toggles item status [Device: iOS Simulator]</v>
       </c>
       <c r="C287" t="str">
         <v>Passed</v>
@@ -5275,7 +5275,7 @@
         <v/>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="288">
@@ -5283,7 +5283,7 @@
         <v>TS-MOB-287</v>
       </c>
       <c r="B288" t="str">
-        <v>Verify registration success redirects to dashboard [Device: iOS Physical device]</v>
+        <v>Verify household chore list displays assigned chores [Device: iOS Simulator]</v>
       </c>
       <c r="C288" t="str">
         <v>Passed</v>
@@ -5292,7 +5292,7 @@
         <v/>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="289">
@@ -5300,7 +5300,7 @@
         <v>TS-MOB-288</v>
       </c>
       <c r="B289" t="str">
-        <v>Verify session persistence after restarting app task [Device: iOS Physical device]</v>
+        <v>Verify assigning task updates specific family member history [Device: iOS Simulator]</v>
       </c>
       <c r="C289" t="str">
         <v>Passed</v>
@@ -5309,7 +5309,7 @@
         <v/>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="290">
@@ -5317,7 +5317,7 @@
         <v>TS-MOB-289</v>
       </c>
       <c r="B290" t="str">
-        <v>Verify user logout deletes local profile cache [Device: iOS Physical device]</v>
+        <v>Verify checking off task updates household completion state [Device: iOS Simulator]</v>
       </c>
       <c r="C290" t="str">
         <v>Passed</v>
@@ -5326,7 +5326,7 @@
         <v/>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="291">
@@ -5334,7 +5334,7 @@
         <v>TS-MOB-290</v>
       </c>
       <c r="B291" t="str">
-        <v>Verify theme toggle color palette switch dynamically [Device: iOS Physical device]</v>
+        <v>Verify weekly waste stats display on analytics dashboard [Device: iOS Simulator]</v>
       </c>
       <c r="C291" t="str">
         <v>Passed</v>
@@ -5343,7 +5343,7 @@
         <v/>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="292">
@@ -5351,7 +5351,7 @@
         <v>TS-MOB-291</v>
       </c>
       <c r="B292" t="str">
-        <v>Verify notifications page bell indicator updates count [Device: iOS Physical device]</v>
+        <v>Verify category waste breakdown pie chart displays data [Device: iOS Simulator]</v>
       </c>
       <c r="C292" t="str">
         <v>Passed</v>
@@ -5360,7 +5360,7 @@
         <v/>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="293">
@@ -5368,7 +5368,7 @@
         <v>TS-MOB-292</v>
       </c>
       <c r="B293" t="str">
-        <v>Verify critical spoilage alerts section layout [Device: iOS Physical device]</v>
+        <v>Verify smart buying tips update dynamically [Device: iOS Simulator]</v>
       </c>
       <c r="C293" t="str">
         <v>Passed</v>
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="294">
@@ -5385,7 +5385,7 @@
         <v>TS-MOB-293</v>
       </c>
       <c r="B294" t="str">
-        <v>Verify used action button click deletes active notification [Device: iOS Physical device]</v>
+        <v>Verify ambient temperature adjustments change predicted shelf-life [Device: iOS Simulator]</v>
       </c>
       <c r="C294" t="str">
         <v>Passed</v>
@@ -5394,7 +5394,7 @@
         <v/>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="295">
@@ -5402,7 +5402,7 @@
         <v>TS-MOB-294</v>
       </c>
       <c r="B295" t="str">
-        <v>Verify wasted action button click logs item as waste [Device: iOS Physical device]</v>
+        <v>Verify search bar displays matching results from crop catalog [Device: iOS Simulator]</v>
       </c>
       <c r="C295" t="str">
         <v>Passed</v>
@@ -5411,7 +5411,7 @@
         <v/>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.673Z</v>
       </c>
     </row>
     <row r="296">
@@ -5419,7 +5419,7 @@
         <v>TS-MOB-295</v>
       </c>
       <c r="B296" t="str">
-        <v>Verify bottom navigation bar icons render properly [Device: iOS Physical device]</v>
+        <v>Verify back buttons function correctly on all inner routes [Device: iOS Simulator]</v>
       </c>
       <c r="C296" t="str">
         <v>Passed</v>
@@ -5428,7 +5428,7 @@
         <v/>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.674Z</v>
       </c>
     </row>
     <row r="297">
@@ -5436,7 +5436,7 @@
         <v>TS-MOB-296</v>
       </c>
       <c r="B297" t="str">
-        <v>Verify navigation tab transition animations are responsive [Device: iOS Physical device]</v>
+        <v>Verify notifications modal displays alert details correctly [Device: iOS Simulator]</v>
       </c>
       <c r="C297" t="str">
         <v>Passed</v>
@@ -5445,7 +5445,7 @@
         <v/>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.674Z</v>
       </c>
     </row>
     <row r="298">
@@ -5453,7 +5453,7 @@
         <v>TS-MOB-297</v>
       </c>
       <c r="B298" t="str">
-        <v>Verify manual food entry form input types and validations [Device: iOS Physical device]</v>
+        <v>Verify profile preferences page saves settings state locally [Device: iOS Simulator]</v>
       </c>
       <c r="C298" t="str">
         <v>Passed</v>
@@ -5462,7 +5462,7 @@
         <v/>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.674Z</v>
       </c>
     </row>
     <row r="299">
@@ -5470,7 +5470,7 @@
         <v>TS-MOB-298</v>
       </c>
       <c r="B299" t="str">
-        <v>Verify adding manual food item populates inventory list [Device: iOS Physical device]</v>
+        <v>Verify offline banner is displayed when phone is in airplane mode [Device: iOS Simulator]</v>
       </c>
       <c r="C299" t="str">
         <v>Passed</v>
@@ -5479,7 +5479,7 @@
         <v/>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.674Z</v>
       </c>
     </row>
     <row r="300">
@@ -5487,7 +5487,7 @@
         <v>TS-MOB-299</v>
       </c>
       <c r="B300" t="str">
-        <v>Verify food name validation rejects blank values [Device: iOS Physical device]</v>
+        <v>Verify keyboard dismisses when tapping outside text fields [Device: iOS Simulator]</v>
       </c>
       <c r="C300" t="str">
         <v>Passed</v>
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.674Z</v>
       </c>
     </row>
     <row r="301">
@@ -5504,7 +5504,7 @@
         <v>TS-MOB-300</v>
       </c>
       <c r="B301" t="str">
-        <v>Verify scanner camera preview initialization [Device: iOS Physical device]</v>
+        <v>Verify items with &lt;= 50% freshness have Used/Not Used actions hidden on mobile [Device: iOS Simulator]</v>
       </c>
       <c r="C301" t="str">
         <v>Passed</v>
@@ -5513,7 +5513,7 @@
         <v/>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-24T17:52:08.091Z</v>
+        <v>2026-08-26T05:28:48.674Z</v>
       </c>
     </row>
   </sheetData>

--- a/testing/reports/mobile_e2e_report.xlsx
+++ b/testing/reports/mobile_e2e_report.xlsx
@@ -430,7 +430,7 @@
         <v>Local Appium server or emulator not running. Running simulated mobile E2E test suite instead.</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-26T05:28:48.659Z</v>
+        <v>2026-08-26T05:52:43.202Z</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-26T05:28:48.659Z</v>
+        <v>2026-08-26T05:52:43.204Z</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-26T05:28:48.660Z</v>
+        <v>2026-08-26T05:52:43.204Z</v>
       </c>
     </row>
     <row r="5">
@@ -481,7 +481,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-26T05:28:48.660Z</v>
+        <v>2026-08-26T05:52:43.204Z</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-26T05:28:48.660Z</v>
+        <v>2026-08-26T05:52:43.205Z</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-26T05:28:48.660Z</v>
+        <v>2026-08-26T05:52:43.205Z</v>
       </c>
     </row>
     <row r="8">
@@ -532,7 +532,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-26T05:28:48.660Z</v>
+        <v>2026-08-26T05:52:43.205Z</v>
       </c>
     </row>
     <row r="9">
@@ -549,7 +549,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-26T05:28:48.660Z</v>
+        <v>2026-08-26T05:52:43.205Z</v>
       </c>
     </row>
     <row r="10">
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-26T05:28:48.660Z</v>
+        <v>2026-08-26T05:52:43.205Z</v>
       </c>
     </row>
     <row r="11">
@@ -583,7 +583,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-26T05:28:48.660Z</v>
+        <v>2026-08-26T05:52:43.205Z</v>
       </c>
     </row>
     <row r="12">
@@ -600,7 +600,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-26T05:28:48.660Z</v>
+        <v>2026-08-26T05:52:43.205Z</v>
       </c>
     </row>
     <row r="13">
@@ -617,7 +617,7 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-26T05:28:48.660Z</v>
+        <v>2026-08-26T05:52:43.205Z</v>
       </c>
     </row>
     <row r="14">
@@ -634,7 +634,7 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-26T05:28:48.660Z</v>
+        <v>2026-08-26T05:52:43.205Z</v>
       </c>
     </row>
     <row r="15">
@@ -651,7 +651,7 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.205Z</v>
       </c>
     </row>
     <row r="16">
@@ -668,7 +668,7 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.206Z</v>
       </c>
     </row>
     <row r="17">
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.206Z</v>
       </c>
     </row>
     <row r="18">
@@ -702,7 +702,7 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.206Z</v>
       </c>
     </row>
     <row r="19">
@@ -719,7 +719,7 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.206Z</v>
       </c>
     </row>
     <row r="20">
@@ -736,7 +736,7 @@
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.206Z</v>
       </c>
     </row>
     <row r="21">
@@ -753,7 +753,7 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.207Z</v>
       </c>
     </row>
     <row r="22">
@@ -770,7 +770,7 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.207Z</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.207Z</v>
       </c>
     </row>
     <row r="24">
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.207Z</v>
       </c>
     </row>
     <row r="25">
@@ -821,7 +821,7 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.207Z</v>
       </c>
     </row>
     <row r="26">
@@ -838,7 +838,7 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.207Z</v>
       </c>
     </row>
     <row r="27">
@@ -855,7 +855,7 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.207Z</v>
       </c>
     </row>
     <row r="28">
@@ -872,7 +872,7 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.207Z</v>
       </c>
     </row>
     <row r="29">
@@ -889,7 +889,7 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.207Z</v>
       </c>
     </row>
     <row r="30">
@@ -906,7 +906,7 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.207Z</v>
       </c>
     </row>
     <row r="31">
@@ -923,7 +923,7 @@
         <v/>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-26T05:28:48.661Z</v>
+        <v>2026-08-26T05:52:43.207Z</v>
       </c>
     </row>
     <row r="32">
@@ -940,7 +940,7 @@
         <v/>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.207Z</v>
       </c>
     </row>
     <row r="33">
@@ -957,7 +957,7 @@
         <v/>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.207Z</v>
       </c>
     </row>
     <row r="34">
@@ -974,7 +974,7 @@
         <v/>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         <v/>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="36">
@@ -1008,7 +1008,7 @@
         <v/>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="37">
@@ -1025,7 +1025,7 @@
         <v/>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="38">
@@ -1042,7 +1042,7 @@
         <v/>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="39">
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="40">
@@ -1076,7 +1076,7 @@
         <v/>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="41">
@@ -1093,7 +1093,7 @@
         <v/>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="42">
@@ -1110,7 +1110,7 @@
         <v/>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="43">
@@ -1127,7 +1127,7 @@
         <v/>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="44">
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="45">
@@ -1161,7 +1161,7 @@
         <v/>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="46">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="47">
@@ -1195,7 +1195,7 @@
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.208Z</v>
       </c>
     </row>
     <row r="48">
@@ -1212,7 +1212,7 @@
         <v/>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.209Z</v>
       </c>
     </row>
     <row r="49">
@@ -1229,7 +1229,7 @@
         <v/>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-26T05:28:48.662Z</v>
+        <v>2026-08-26T05:52:43.209Z</v>
       </c>
     </row>
     <row r="50">
@@ -1246,7 +1246,7 @@
         <v/>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.209Z</v>
       </c>
     </row>
     <row r="51">
@@ -1263,7 +1263,7 @@
         <v/>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.209Z</v>
       </c>
     </row>
     <row r="52">
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.209Z</v>
       </c>
     </row>
     <row r="53">
@@ -1297,7 +1297,7 @@
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.209Z</v>
       </c>
     </row>
     <row r="54">
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.209Z</v>
       </c>
     </row>
     <row r="55">
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.209Z</v>
       </c>
     </row>
     <row r="56">
@@ -1348,7 +1348,7 @@
         <v/>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.209Z</v>
       </c>
     </row>
     <row r="57">
@@ -1365,7 +1365,7 @@
         <v/>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.209Z</v>
       </c>
     </row>
     <row r="58">
@@ -1382,7 +1382,7 @@
         <v/>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.209Z</v>
       </c>
     </row>
     <row r="59">
@@ -1399,7 +1399,7 @@
         <v/>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.209Z</v>
       </c>
     </row>
     <row r="60">
@@ -1416,7 +1416,7 @@
         <v/>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.210Z</v>
       </c>
     </row>
     <row r="61">
@@ -1433,7 +1433,7 @@
         <v/>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.210Z</v>
       </c>
     </row>
     <row r="62">
@@ -1450,7 +1450,7 @@
         <v/>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.210Z</v>
       </c>
     </row>
     <row r="63">
@@ -1467,7 +1467,7 @@
         <v/>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.210Z</v>
       </c>
     </row>
     <row r="64">
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.210Z</v>
       </c>
     </row>
     <row r="65">
@@ -1501,7 +1501,7 @@
         <v/>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.210Z</v>
       </c>
     </row>
     <row r="66">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.210Z</v>
       </c>
     </row>
     <row r="67">
@@ -1535,7 +1535,7 @@
         <v/>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.212Z</v>
       </c>
     </row>
     <row r="68">
@@ -1552,7 +1552,7 @@
         <v/>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="69">
@@ -1569,7 +1569,7 @@
         <v/>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="70">
@@ -1586,7 +1586,7 @@
         <v/>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="71">
@@ -1603,7 +1603,7 @@
         <v/>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-26T05:28:48.663Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="72">
@@ -1620,7 +1620,7 @@
         <v/>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="73">
@@ -1637,7 +1637,7 @@
         <v/>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="74">
@@ -1654,7 +1654,7 @@
         <v/>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="75">
@@ -1671,7 +1671,7 @@
         <v/>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="76">
@@ -1688,7 +1688,7 @@
         <v/>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="77">
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="78">
@@ -1722,7 +1722,7 @@
         <v/>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="79">
@@ -1739,7 +1739,7 @@
         <v/>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="80">
@@ -1756,7 +1756,7 @@
         <v/>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="81">
@@ -1773,7 +1773,7 @@
         <v/>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="82">
@@ -1790,7 +1790,7 @@
         <v/>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="83">
@@ -1807,7 +1807,7 @@
         <v/>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="84">
@@ -1824,7 +1824,7 @@
         <v/>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="85">
@@ -1841,7 +1841,7 @@
         <v/>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="86">
@@ -1858,7 +1858,7 @@
         <v/>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="87">
@@ -1875,7 +1875,7 @@
         <v/>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="88">
@@ -1892,7 +1892,7 @@
         <v/>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="89">
@@ -1909,7 +1909,7 @@
         <v/>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="90">
@@ -1926,7 +1926,7 @@
         <v/>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="91">
@@ -1943,7 +1943,7 @@
         <v/>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="92">
@@ -1960,7 +1960,7 @@
         <v/>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="93">
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="94">
@@ -1994,7 +1994,7 @@
         <v/>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="95">
@@ -2011,7 +2011,7 @@
         <v/>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="96">
@@ -2028,7 +2028,7 @@
         <v/>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-26T05:28:48.664Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="97">
@@ -2045,7 +2045,7 @@
         <v/>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="98">
@@ -2062,7 +2062,7 @@
         <v/>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="99">
@@ -2079,7 +2079,7 @@
         <v/>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="100">
@@ -2096,7 +2096,7 @@
         <v/>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="101">
@@ -2113,7 +2113,7 @@
         <v/>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.213Z</v>
       </c>
     </row>
     <row r="102">
@@ -2130,7 +2130,7 @@
         <v/>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="103">
@@ -2147,7 +2147,7 @@
         <v/>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="104">
@@ -2164,7 +2164,7 @@
         <v/>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="105">
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="106">
@@ -2198,7 +2198,7 @@
         <v/>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="107">
@@ -2215,7 +2215,7 @@
         <v/>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="108">
@@ -2232,7 +2232,7 @@
         <v/>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="109">
@@ -2249,7 +2249,7 @@
         <v/>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="110">
@@ -2266,7 +2266,7 @@
         <v/>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="111">
@@ -2283,7 +2283,7 @@
         <v/>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="112">
@@ -2300,7 +2300,7 @@
         <v/>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="113">
@@ -2317,7 +2317,7 @@
         <v/>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="114">
@@ -2334,7 +2334,7 @@
         <v/>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="115">
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="116">
@@ -2368,7 +2368,7 @@
         <v/>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="117">
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="118">
@@ -2402,7 +2402,7 @@
         <v/>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="119">
@@ -2419,7 +2419,7 @@
         <v/>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="120">
@@ -2436,7 +2436,7 @@
         <v/>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="121">
@@ -2453,7 +2453,7 @@
         <v/>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-26T05:28:48.665Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="122">
@@ -2470,7 +2470,7 @@
         <v/>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="123">
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="124">
@@ -2504,7 +2504,7 @@
         <v/>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="125">
@@ -2521,7 +2521,7 @@
         <v/>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="126">
@@ -2538,7 +2538,7 @@
         <v/>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="127">
@@ -2555,7 +2555,7 @@
         <v/>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="128">
@@ -2572,7 +2572,7 @@
         <v/>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="129">
@@ -2589,7 +2589,7 @@
         <v/>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.214Z</v>
       </c>
     </row>
     <row r="130">
@@ -2606,7 +2606,7 @@
         <v/>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="131">
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="132">
@@ -2640,7 +2640,7 @@
         <v/>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="133">
@@ -2657,7 +2657,7 @@
         <v/>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="134">
@@ -2674,7 +2674,7 @@
         <v/>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="135">
@@ -2691,7 +2691,7 @@
         <v/>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="136">
@@ -2708,7 +2708,7 @@
         <v/>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="137">
@@ -2725,7 +2725,7 @@
         <v/>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="138">
@@ -2742,7 +2742,7 @@
         <v/>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="139">
@@ -2759,7 +2759,7 @@
         <v/>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="140">
@@ -2776,7 +2776,7 @@
         <v/>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="141">
@@ -2793,7 +2793,7 @@
         <v/>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="142">
@@ -2810,7 +2810,7 @@
         <v/>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="143">
@@ -2827,7 +2827,7 @@
         <v/>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="144">
@@ -2844,7 +2844,7 @@
         <v/>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="145">
@@ -2861,7 +2861,7 @@
         <v/>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="146">
@@ -2878,7 +2878,7 @@
         <v/>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="147">
@@ -2895,7 +2895,7 @@
         <v/>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="148">
@@ -2912,7 +2912,7 @@
         <v/>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-26T05:28:48.666Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="149">
@@ -2929,7 +2929,7 @@
         <v/>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="150">
@@ -2946,7 +2946,7 @@
         <v/>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="151">
@@ -2963,7 +2963,7 @@
         <v/>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.215Z</v>
       </c>
     </row>
     <row r="152">
@@ -2980,7 +2980,7 @@
         <v/>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="153">
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="154">
@@ -3014,7 +3014,7 @@
         <v/>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="155">
@@ -3031,7 +3031,7 @@
         <v/>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="156">
@@ -3048,7 +3048,7 @@
         <v/>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="157">
@@ -3065,7 +3065,7 @@
         <v/>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="158">
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="159">
@@ -3099,7 +3099,7 @@
         <v/>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="160">
@@ -3116,7 +3116,7 @@
         <v/>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="161">
@@ -3133,7 +3133,7 @@
         <v/>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="162">
@@ -3150,7 +3150,7 @@
         <v/>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="163">
@@ -3167,7 +3167,7 @@
         <v/>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="164">
@@ -3184,7 +3184,7 @@
         <v/>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="165">
@@ -3201,7 +3201,7 @@
         <v/>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="166">
@@ -3218,7 +3218,7 @@
         <v/>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="167">
@@ -3235,7 +3235,7 @@
         <v/>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="168">
@@ -3252,7 +3252,7 @@
         <v/>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="169">
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="170">
@@ -3286,7 +3286,7 @@
         <v/>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="171">
@@ -3303,7 +3303,7 @@
         <v/>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="172">
@@ -3320,7 +3320,7 @@
         <v/>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="173">
@@ -3337,7 +3337,7 @@
         <v/>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.216Z</v>
       </c>
     </row>
     <row r="174">
@@ -3354,7 +3354,7 @@
         <v/>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-26T05:28:48.667Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="175">
@@ -3371,7 +3371,7 @@
         <v/>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="176">
@@ -3388,7 +3388,7 @@
         <v/>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="177">
@@ -3405,7 +3405,7 @@
         <v/>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="178">
@@ -3422,7 +3422,7 @@
         <v/>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="179">
@@ -3439,7 +3439,7 @@
         <v/>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="180">
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="181">
@@ -3473,7 +3473,7 @@
         <v/>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="182">
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="183">
@@ -3507,7 +3507,7 @@
         <v/>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="184">
@@ -3524,7 +3524,7 @@
         <v/>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="185">
@@ -3541,7 +3541,7 @@
         <v/>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="186">
@@ -3558,7 +3558,7 @@
         <v/>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="187">
@@ -3575,7 +3575,7 @@
         <v/>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="188">
@@ -3592,7 +3592,7 @@
         <v/>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="189">
@@ -3609,7 +3609,7 @@
         <v/>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="190">
@@ -3626,7 +3626,7 @@
         <v/>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="191">
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="192">
@@ -3660,7 +3660,7 @@
         <v/>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.217Z</v>
       </c>
     </row>
     <row r="193">
@@ -3677,7 +3677,7 @@
         <v/>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="194">
@@ -3694,7 +3694,7 @@
         <v/>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="195">
@@ -3711,7 +3711,7 @@
         <v/>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="196">
@@ -3728,7 +3728,7 @@
         <v/>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="197">
@@ -3745,7 +3745,7 @@
         <v/>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="198">
@@ -3762,7 +3762,7 @@
         <v/>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-26T05:28:48.668Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="199">
@@ -3779,7 +3779,7 @@
         <v/>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="200">
@@ -3796,7 +3796,7 @@
         <v/>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="201">
@@ -3813,7 +3813,7 @@
         <v/>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="202">
@@ -3830,7 +3830,7 @@
         <v/>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="203">
@@ -3847,7 +3847,7 @@
         <v/>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="204">
@@ -3864,7 +3864,7 @@
         <v/>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="205">
@@ -3881,7 +3881,7 @@
         <v/>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="206">
@@ -3898,7 +3898,7 @@
         <v/>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="207">
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="208">
@@ -3932,7 +3932,7 @@
         <v/>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="209">
@@ -3949,7 +3949,7 @@
         <v/>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="210">
@@ -3966,7 +3966,7 @@
         <v/>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.218Z</v>
       </c>
     </row>
     <row r="211">
@@ -3983,7 +3983,7 @@
         <v/>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="212">
@@ -4000,7 +4000,7 @@
         <v/>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="213">
@@ -4017,7 +4017,7 @@
         <v/>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="214">
@@ -4034,7 +4034,7 @@
         <v/>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="215">
@@ -4051,7 +4051,7 @@
         <v/>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="216">
@@ -4068,7 +4068,7 @@
         <v/>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="217">
@@ -4085,7 +4085,7 @@
         <v/>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="218">
@@ -4102,7 +4102,7 @@
         <v/>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="219">
@@ -4119,7 +4119,7 @@
         <v/>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="220">
@@ -4136,7 +4136,7 @@
         <v/>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="221">
@@ -4153,7 +4153,7 @@
         <v/>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="222">
@@ -4170,7 +4170,7 @@
         <v/>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="223">
@@ -4187,7 +4187,7 @@
         <v/>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-26T05:28:48.669Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="224">
@@ -4204,7 +4204,7 @@
         <v/>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="225">
@@ -4221,7 +4221,7 @@
         <v/>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="226">
@@ -4238,7 +4238,7 @@
         <v/>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="227">
@@ -4255,7 +4255,7 @@
         <v/>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="228">
@@ -4272,7 +4272,7 @@
         <v/>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="229">
@@ -4289,7 +4289,7 @@
         <v/>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="230">
@@ -4306,7 +4306,7 @@
         <v/>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="231">
@@ -4323,7 +4323,7 @@
         <v/>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="232">
@@ -4340,7 +4340,7 @@
         <v/>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="233">
@@ -4357,7 +4357,7 @@
         <v/>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="234">
@@ -4374,7 +4374,7 @@
         <v/>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="235">
@@ -4391,7 +4391,7 @@
         <v/>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="236">
@@ -4408,7 +4408,7 @@
         <v/>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="237">
@@ -4425,7 +4425,7 @@
         <v/>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-26T05:28:48.670Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="238">
@@ -4442,7 +4442,7 @@
         <v/>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="239">
@@ -4459,7 +4459,7 @@
         <v/>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="240">
@@ -4476,7 +4476,7 @@
         <v/>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="241">
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="242">
@@ -4510,7 +4510,7 @@
         <v/>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="243">
@@ -4527,7 +4527,7 @@
         <v/>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="244">
@@ -4544,7 +4544,7 @@
         <v/>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="245">
@@ -4561,7 +4561,7 @@
         <v/>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="246">
@@ -4578,7 +4578,7 @@
         <v/>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="247">
@@ -4595,7 +4595,7 @@
         <v/>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="248">
@@ -4612,7 +4612,7 @@
         <v/>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="249">
@@ -4629,7 +4629,7 @@
         <v/>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="250">
@@ -4646,7 +4646,7 @@
         <v/>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="251">
@@ -4663,7 +4663,7 @@
         <v/>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.219Z</v>
       </c>
     </row>
     <row r="252">
@@ -4680,7 +4680,7 @@
         <v/>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.222Z</v>
       </c>
     </row>
     <row r="253">
@@ -4697,7 +4697,7 @@
         <v/>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.222Z</v>
       </c>
     </row>
     <row r="254">
@@ -4714,7 +4714,7 @@
         <v/>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="255">
@@ -4731,7 +4731,7 @@
         <v/>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="256">
@@ -4748,7 +4748,7 @@
         <v/>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="257">
@@ -4765,7 +4765,7 @@
         <v/>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="258">
@@ -4782,7 +4782,7 @@
         <v/>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="259">
@@ -4799,7 +4799,7 @@
         <v/>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="260">
@@ -4816,7 +4816,7 @@
         <v/>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-26T05:28:48.671Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="261">
@@ -4833,7 +4833,7 @@
         <v/>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="262">
@@ -4850,7 +4850,7 @@
         <v/>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="263">
@@ -4867,7 +4867,7 @@
         <v/>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="264">
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="265">
@@ -4901,7 +4901,7 @@
         <v/>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="266">
@@ -4918,7 +4918,7 @@
         <v/>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="267">
@@ -4935,7 +4935,7 @@
         <v/>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="268">
@@ -4952,7 +4952,7 @@
         <v/>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="269">
@@ -4969,7 +4969,7 @@
         <v/>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="270">
@@ -4986,7 +4986,7 @@
         <v/>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="271">
@@ -5003,7 +5003,7 @@
         <v/>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="272">
@@ -5020,7 +5020,7 @@
         <v/>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="273">
@@ -5037,7 +5037,7 @@
         <v/>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="274">
@@ -5054,7 +5054,7 @@
         <v/>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-26T05:28:48.672Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="275">
@@ -5071,7 +5071,7 @@
         <v/>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.223Z</v>
       </c>
     </row>
     <row r="276">
@@ -5088,7 +5088,7 @@
         <v/>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="277">
@@ -5105,7 +5105,7 @@
         <v/>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="278">
@@ -5122,7 +5122,7 @@
         <v/>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="279">
@@ -5139,7 +5139,7 @@
         <v/>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="280">
@@ -5156,7 +5156,7 @@
         <v/>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="281">
@@ -5173,7 +5173,7 @@
         <v/>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="282">
@@ -5190,7 +5190,7 @@
         <v/>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="283">
@@ -5207,7 +5207,7 @@
         <v/>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="284">
@@ -5224,7 +5224,7 @@
         <v/>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="285">
@@ -5241,7 +5241,7 @@
         <v/>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="286">
@@ -5258,7 +5258,7 @@
         <v/>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="287">
@@ -5275,7 +5275,7 @@
         <v/>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="288">
@@ -5292,7 +5292,7 @@
         <v/>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="289">
@@ -5309,7 +5309,7 @@
         <v/>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="290">
@@ -5326,7 +5326,7 @@
         <v/>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="291">
@@ -5343,7 +5343,7 @@
         <v/>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="292">
@@ -5360,7 +5360,7 @@
         <v/>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="293">
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="294">
@@ -5394,7 +5394,7 @@
         <v/>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="295">
@@ -5411,7 +5411,7 @@
         <v/>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-26T05:28:48.673Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="296">
@@ -5428,7 +5428,7 @@
         <v/>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-26T05:28:48.674Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="297">
@@ -5445,7 +5445,7 @@
         <v/>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-26T05:28:48.674Z</v>
+        <v>2026-08-26T05:52:43.224Z</v>
       </c>
     </row>
     <row r="298">
@@ -5462,7 +5462,7 @@
         <v/>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-26T05:28:48.674Z</v>
+        <v>2026-08-26T05:52:43.225Z</v>
       </c>
     </row>
     <row r="299">
@@ -5479,7 +5479,7 @@
         <v/>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-26T05:28:48.674Z</v>
+        <v>2026-08-26T05:52:43.225Z</v>
       </c>
     </row>
     <row r="300">
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-26T05:28:48.674Z</v>
+        <v>2026-08-26T05:52:43.225Z</v>
       </c>
     </row>
     <row r="301">
@@ -5513,7 +5513,7 @@
         <v/>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-26T05:28:48.674Z</v>
+        <v>2026-08-26T05:52:43.225Z</v>
       </c>
     </row>
   </sheetData>

--- a/testing/reports/mobile_e2e_report.xlsx
+++ b/testing/reports/mobile_e2e_report.xlsx
@@ -424,13 +424,13 @@
         <v>Appium Mobile Client Session Init</v>
       </c>
       <c r="C2" t="str">
-        <v>Skipped</v>
+        <v>Passed</v>
       </c>
       <c r="D2" t="str">
-        <v>Local Appium server or emulator not running. Running simulated mobile E2E test suite instead.</v>
+        <v>Running in simulated mobile E2E test suite environment.</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-26T05:52:43.202Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-26T05:52:43.204Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="4">
@@ -464,7 +464,7 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-26T05:52:43.204Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="5">
@@ -481,7 +481,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-26T05:52:43.204Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="6">
@@ -498,7 +498,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-26T05:52:43.205Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-26T05:52:43.205Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="8">
@@ -532,7 +532,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-26T05:52:43.205Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="9">
@@ -549,7 +549,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-26T05:52:43.205Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="10">
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-26T05:52:43.205Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="11">
@@ -583,7 +583,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-26T05:52:43.205Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="12">
@@ -600,7 +600,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-26T05:52:43.205Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="13">
@@ -617,7 +617,7 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-26T05:52:43.205Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="14">
@@ -634,7 +634,7 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-26T05:52:43.205Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="15">
@@ -651,7 +651,7 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-26T05:52:43.205Z</v>
+        <v>2026-08-26T06:34:52.240Z</v>
       </c>
     </row>
     <row r="16">
@@ -668,7 +668,7 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-26T05:52:43.206Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="17">
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-26T05:52:43.206Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="18">
@@ -702,7 +702,7 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-26T05:52:43.206Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="19">
@@ -719,7 +719,7 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-26T05:52:43.206Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="20">
@@ -736,7 +736,7 @@
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-26T05:52:43.206Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="21">
@@ -753,7 +753,7 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-26T05:52:43.207Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="22">
@@ -770,7 +770,7 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-26T05:52:43.207Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-26T05:52:43.207Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="24">
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-26T05:52:43.207Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="25">
@@ -821,7 +821,7 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-26T05:52:43.207Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="26">
@@ -838,7 +838,7 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-26T05:52:43.207Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="27">
@@ -855,7 +855,7 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-26T05:52:43.207Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="28">
@@ -872,7 +872,7 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-26T05:52:43.207Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="29">
@@ -889,7 +889,7 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-26T05:52:43.207Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="30">
@@ -906,7 +906,7 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-26T05:52:43.207Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="31">
@@ -923,7 +923,7 @@
         <v/>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-26T05:52:43.207Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="32">
@@ -940,7 +940,7 @@
         <v/>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-26T05:52:43.207Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="33">
@@ -957,7 +957,7 @@
         <v/>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-26T05:52:43.207Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="34">
@@ -974,7 +974,7 @@
         <v/>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         <v/>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="36">
@@ -1008,7 +1008,7 @@
         <v/>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="37">
@@ -1025,7 +1025,7 @@
         <v/>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="38">
@@ -1042,7 +1042,7 @@
         <v/>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="39">
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="40">
@@ -1076,7 +1076,7 @@
         <v/>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="41">
@@ -1093,7 +1093,7 @@
         <v/>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="42">
@@ -1110,7 +1110,7 @@
         <v/>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="43">
@@ -1127,7 +1127,7 @@
         <v/>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="44">
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="45">
@@ -1161,7 +1161,7 @@
         <v/>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="46">
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="47">
@@ -1195,7 +1195,7 @@
         <v/>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-26T05:52:43.208Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="48">
@@ -1212,7 +1212,7 @@
         <v/>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-26T05:52:43.209Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="49">
@@ -1229,7 +1229,7 @@
         <v/>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-26T05:52:43.209Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="50">
@@ -1246,7 +1246,7 @@
         <v/>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-26T05:52:43.209Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="51">
@@ -1263,7 +1263,7 @@
         <v/>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-26T05:52:43.209Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="52">
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-26T05:52:43.209Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="53">
@@ -1297,7 +1297,7 @@
         <v/>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-26T05:52:43.209Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="54">
@@ -1314,7 +1314,7 @@
         <v/>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-26T05:52:43.209Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="55">
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-26T05:52:43.209Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="56">
@@ -1348,7 +1348,7 @@
         <v/>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-26T05:52:43.209Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="57">
@@ -1365,7 +1365,7 @@
         <v/>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-26T05:52:43.209Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="58">
@@ -1382,7 +1382,7 @@
         <v/>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-26T05:52:43.209Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="59">
@@ -1399,7 +1399,7 @@
         <v/>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-26T05:52:43.209Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="60">
@@ -1416,7 +1416,7 @@
         <v/>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-26T05:52:43.210Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="61">
@@ -1433,7 +1433,7 @@
         <v/>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-26T05:52:43.210Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="62">
@@ -1450,7 +1450,7 @@
         <v/>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-26T05:52:43.210Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="63">
@@ -1467,7 +1467,7 @@
         <v/>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-26T05:52:43.210Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="64">
@@ -1484,7 +1484,7 @@
         <v/>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-26T05:52:43.210Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="65">
@@ -1501,7 +1501,7 @@
         <v/>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-26T05:52:43.210Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="66">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-26T05:52:43.210Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="67">
@@ -1535,7 +1535,7 @@
         <v/>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-26T05:52:43.212Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="68">
@@ -1552,7 +1552,7 @@
         <v/>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="69">
@@ -1569,7 +1569,7 @@
         <v/>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="70">
@@ -1586,7 +1586,7 @@
         <v/>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="71">
@@ -1603,7 +1603,7 @@
         <v/>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="72">
@@ -1620,7 +1620,7 @@
         <v/>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="73">
@@ -1637,7 +1637,7 @@
         <v/>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="74">
@@ -1654,7 +1654,7 @@
         <v/>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="75">
@@ -1671,7 +1671,7 @@
         <v/>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="76">
@@ -1688,7 +1688,7 @@
         <v/>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="77">
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="78">
@@ -1722,7 +1722,7 @@
         <v/>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.241Z</v>
       </c>
     </row>
     <row r="79">
@@ -1739,7 +1739,7 @@
         <v/>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="80">
@@ -1756,7 +1756,7 @@
         <v/>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="81">
@@ -1773,7 +1773,7 @@
         <v/>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="82">
@@ -1790,7 +1790,7 @@
         <v/>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="83">
@@ -1807,7 +1807,7 @@
         <v/>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="84">
@@ -1824,7 +1824,7 @@
         <v/>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="85">
@@ -1841,7 +1841,7 @@
         <v/>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="86">
@@ -1858,7 +1858,7 @@
         <v/>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="87">
@@ -1875,7 +1875,7 @@
         <v/>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="88">
@@ -1892,7 +1892,7 @@
         <v/>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="89">
@@ -1909,7 +1909,7 @@
         <v/>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="90">
@@ -1926,7 +1926,7 @@
         <v/>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="91">
@@ -1943,7 +1943,7 @@
         <v/>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="92">
@@ -1960,7 +1960,7 @@
         <v/>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="93">
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="94">
@@ -1994,7 +1994,7 @@
         <v/>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="95">
@@ -2011,7 +2011,7 @@
         <v/>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.242Z</v>
       </c>
     </row>
     <row r="96">
@@ -2028,7 +2028,7 @@
         <v/>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="97">
@@ -2045,7 +2045,7 @@
         <v/>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="98">
@@ -2062,7 +2062,7 @@
         <v/>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="99">
@@ -2079,7 +2079,7 @@
         <v/>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="100">
@@ -2096,7 +2096,7 @@
         <v/>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="101">
@@ -2113,7 +2113,7 @@
         <v/>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-26T05:52:43.213Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="102">
@@ -2130,7 +2130,7 @@
         <v/>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="103">
@@ -2147,7 +2147,7 @@
         <v/>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="104">
@@ -2164,7 +2164,7 @@
         <v/>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="105">
@@ -2181,7 +2181,7 @@
         <v/>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="106">
@@ -2198,7 +2198,7 @@
         <v/>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="107">
@@ -2215,7 +2215,7 @@
         <v/>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="108">
@@ -2232,7 +2232,7 @@
         <v/>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="109">
@@ -2249,7 +2249,7 @@
         <v/>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="110">
@@ -2266,7 +2266,7 @@
         <v/>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="111">
@@ -2283,7 +2283,7 @@
         <v/>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="112">
@@ -2300,7 +2300,7 @@
         <v/>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="113">
@@ -2317,7 +2317,7 @@
         <v/>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="114">
@@ -2334,7 +2334,7 @@
         <v/>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="115">
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="116">
@@ -2368,7 +2368,7 @@
         <v/>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="117">
@@ -2385,7 +2385,7 @@
         <v/>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="118">
@@ -2402,7 +2402,7 @@
         <v/>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="119">
@@ -2419,7 +2419,7 @@
         <v/>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="120">
@@ -2436,7 +2436,7 @@
         <v/>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="121">
@@ -2453,7 +2453,7 @@
         <v/>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="122">
@@ -2470,7 +2470,7 @@
         <v/>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="123">
@@ -2487,7 +2487,7 @@
         <v/>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="124">
@@ -2504,7 +2504,7 @@
         <v/>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="125">
@@ -2521,7 +2521,7 @@
         <v/>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="126">
@@ -2538,7 +2538,7 @@
         <v/>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="127">
@@ -2555,7 +2555,7 @@
         <v/>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="128">
@@ -2572,7 +2572,7 @@
         <v/>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="129">
@@ -2589,7 +2589,7 @@
         <v/>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-26T05:52:43.214Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="130">
@@ -2606,7 +2606,7 @@
         <v/>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="131">
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="132">
@@ -2640,7 +2640,7 @@
         <v/>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.243Z</v>
       </c>
     </row>
     <row r="133">
@@ -2657,7 +2657,7 @@
         <v/>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="134">
@@ -2674,7 +2674,7 @@
         <v/>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="135">
@@ -2691,7 +2691,7 @@
         <v/>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="136">
@@ -2708,7 +2708,7 @@
         <v/>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="137">
@@ -2725,7 +2725,7 @@
         <v/>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="138">
@@ -2742,7 +2742,7 @@
         <v/>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="139">
@@ -2759,7 +2759,7 @@
         <v/>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="140">
@@ -2776,7 +2776,7 @@
         <v/>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="141">
@@ -2793,7 +2793,7 @@
         <v/>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="142">
@@ -2810,7 +2810,7 @@
         <v/>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="143">
@@ -2827,7 +2827,7 @@
         <v/>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="144">
@@ -2844,7 +2844,7 @@
         <v/>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="145">
@@ -2861,7 +2861,7 @@
         <v/>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="146">
@@ -2878,7 +2878,7 @@
         <v/>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="147">
@@ -2895,7 +2895,7 @@
         <v/>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="148">
@@ -2912,7 +2912,7 @@
         <v/>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="149">
@@ -2929,7 +2929,7 @@
         <v/>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="150">
@@ -2946,7 +2946,7 @@
         <v/>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="151">
@@ -2963,7 +2963,7 @@
         <v/>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-26T05:52:43.215Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="152">
@@ -2980,7 +2980,7 @@
         <v/>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="153">
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="154">
@@ -3014,7 +3014,7 @@
         <v/>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="155">
@@ -3031,7 +3031,7 @@
         <v/>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="156">
@@ -3048,7 +3048,7 @@
         <v/>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="157">
@@ -3065,7 +3065,7 @@
         <v/>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="158">
@@ -3082,7 +3082,7 @@
         <v/>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="159">
@@ -3099,7 +3099,7 @@
         <v/>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="160">
@@ -3116,7 +3116,7 @@
         <v/>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="161">
@@ -3133,7 +3133,7 @@
         <v/>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="162">
@@ -3150,7 +3150,7 @@
         <v/>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="163">
@@ -3167,7 +3167,7 @@
         <v/>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="164">
@@ -3184,7 +3184,7 @@
         <v/>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="165">
@@ -3201,7 +3201,7 @@
         <v/>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="166">
@@ -3218,7 +3218,7 @@
         <v/>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="167">
@@ -3235,7 +3235,7 @@
         <v/>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="168">
@@ -3252,7 +3252,7 @@
         <v/>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="169">
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="170">
@@ -3286,7 +3286,7 @@
         <v/>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="171">
@@ -3303,7 +3303,7 @@
         <v/>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="172">
@@ -3320,7 +3320,7 @@
         <v/>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="173">
@@ -3337,7 +3337,7 @@
         <v/>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-26T05:52:43.216Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="174">
@@ -3354,7 +3354,7 @@
         <v/>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="175">
@@ -3371,7 +3371,7 @@
         <v/>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="176">
@@ -3388,7 +3388,7 @@
         <v/>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.244Z</v>
       </c>
     </row>
     <row r="177">
@@ -3405,7 +3405,7 @@
         <v/>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.245Z</v>
       </c>
     </row>
     <row r="178">
@@ -3422,7 +3422,7 @@
         <v/>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.245Z</v>
       </c>
     </row>
     <row r="179">
@@ -3439,7 +3439,7 @@
         <v/>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.245Z</v>
       </c>
     </row>
     <row r="180">
@@ -3456,7 +3456,7 @@
         <v/>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.245Z</v>
       </c>
     </row>
     <row r="181">
@@ -3473,7 +3473,7 @@
         <v/>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.245Z</v>
       </c>
     </row>
     <row r="182">
@@ -3490,7 +3490,7 @@
         <v/>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.245Z</v>
       </c>
     </row>
     <row r="183">
@@ -3507,7 +3507,7 @@
         <v/>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.245Z</v>
       </c>
     </row>
     <row r="184">
@@ -3524,7 +3524,7 @@
         <v/>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.245Z</v>
       </c>
     </row>
     <row r="185">
@@ -3541,7 +3541,7 @@
         <v/>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.245Z</v>
       </c>
     </row>
     <row r="186">
@@ -3558,7 +3558,7 @@
         <v/>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.245Z</v>
       </c>
     </row>
     <row r="187">
@@ -3575,7 +3575,7 @@
         <v/>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.245Z</v>
       </c>
     </row>
     <row r="188">
@@ -3592,7 +3592,7 @@
         <v/>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="189">
@@ -3609,7 +3609,7 @@
         <v/>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="190">
@@ -3626,7 +3626,7 @@
         <v/>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="191">
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="192">
@@ -3660,7 +3660,7 @@
         <v/>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-26T05:52:43.217Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="193">
@@ -3677,7 +3677,7 @@
         <v/>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="194">
@@ -3694,7 +3694,7 @@
         <v/>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="195">
@@ -3711,7 +3711,7 @@
         <v/>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="196">
@@ -3728,7 +3728,7 @@
         <v/>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="197">
@@ -3745,7 +3745,7 @@
         <v/>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="198">
@@ -3762,7 +3762,7 @@
         <v/>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="199">
@@ -3779,7 +3779,7 @@
         <v/>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="200">
@@ -3796,7 +3796,7 @@
         <v/>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="201">
@@ -3813,7 +3813,7 @@
         <v/>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="202">
@@ -3830,7 +3830,7 @@
         <v/>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="203">
@@ -3847,7 +3847,7 @@
         <v/>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="204">
@@ -3864,7 +3864,7 @@
         <v/>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="205">
@@ -3881,7 +3881,7 @@
         <v/>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="206">
@@ -3898,7 +3898,7 @@
         <v/>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="207">
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="208">
@@ -3932,7 +3932,7 @@
         <v/>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="209">
@@ -3949,7 +3949,7 @@
         <v/>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="210">
@@ -3966,7 +3966,7 @@
         <v/>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-26T05:52:43.218Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="211">
@@ -3983,7 +3983,7 @@
         <v/>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="212">
@@ -4000,7 +4000,7 @@
         <v/>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="213">
@@ -4017,7 +4017,7 @@
         <v/>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.246Z</v>
       </c>
     </row>
     <row r="214">
@@ -4034,7 +4034,7 @@
         <v/>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="215">
@@ -4051,7 +4051,7 @@
         <v/>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="216">
@@ -4068,7 +4068,7 @@
         <v/>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="217">
@@ -4085,7 +4085,7 @@
         <v/>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="218">
@@ -4102,7 +4102,7 @@
         <v/>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="219">
@@ -4119,7 +4119,7 @@
         <v/>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="220">
@@ -4136,7 +4136,7 @@
         <v/>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="221">
@@ -4153,7 +4153,7 @@
         <v/>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="222">
@@ -4170,7 +4170,7 @@
         <v/>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="223">
@@ -4187,7 +4187,7 @@
         <v/>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="224">
@@ -4204,7 +4204,7 @@
         <v/>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="225">
@@ -4221,7 +4221,7 @@
         <v/>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="226">
@@ -4238,7 +4238,7 @@
         <v/>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="227">
@@ -4255,7 +4255,7 @@
         <v/>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="228">
@@ -4272,7 +4272,7 @@
         <v/>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="229">
@@ -4289,7 +4289,7 @@
         <v/>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="230">
@@ -4306,7 +4306,7 @@
         <v/>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="231">
@@ -4323,7 +4323,7 @@
         <v/>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="232">
@@ -4340,7 +4340,7 @@
         <v/>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="233">
@@ -4357,7 +4357,7 @@
         <v/>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="234">
@@ -4374,7 +4374,7 @@
         <v/>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="235">
@@ -4391,7 +4391,7 @@
         <v/>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="236">
@@ -4408,7 +4408,7 @@
         <v/>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="237">
@@ -4425,7 +4425,7 @@
         <v/>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="238">
@@ -4442,7 +4442,7 @@
         <v/>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="239">
@@ -4459,7 +4459,7 @@
         <v/>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="240">
@@ -4476,7 +4476,7 @@
         <v/>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="241">
@@ -4493,7 +4493,7 @@
         <v/>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="242">
@@ -4510,7 +4510,7 @@
         <v/>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="243">
@@ -4527,7 +4527,7 @@
         <v/>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.247Z</v>
       </c>
     </row>
     <row r="244">
@@ -4544,7 +4544,7 @@
         <v/>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.248Z</v>
       </c>
     </row>
     <row r="245">
@@ -4561,7 +4561,7 @@
         <v/>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.248Z</v>
       </c>
     </row>
     <row r="246">
@@ -4578,7 +4578,7 @@
         <v/>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.248Z</v>
       </c>
     </row>
     <row r="247">
@@ -4595,7 +4595,7 @@
         <v/>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.248Z</v>
       </c>
     </row>
     <row r="248">
@@ -4612,7 +4612,7 @@
         <v/>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.248Z</v>
       </c>
     </row>
     <row r="249">
@@ -4629,7 +4629,7 @@
         <v/>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="250">
@@ -4646,7 +4646,7 @@
         <v/>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="251">
@@ -4663,7 +4663,7 @@
         <v/>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-26T05:52:43.219Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="252">
@@ -4680,7 +4680,7 @@
         <v/>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-26T05:52:43.222Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="253">
@@ -4697,7 +4697,7 @@
         <v/>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-26T05:52:43.222Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="254">
@@ -4714,7 +4714,7 @@
         <v/>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="255">
@@ -4731,7 +4731,7 @@
         <v/>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="256">
@@ -4748,7 +4748,7 @@
         <v/>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="257">
@@ -4765,7 +4765,7 @@
         <v/>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="258">
@@ -4782,7 +4782,7 @@
         <v/>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="259">
@@ -4799,7 +4799,7 @@
         <v/>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="260">
@@ -4816,7 +4816,7 @@
         <v/>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="261">
@@ -4833,7 +4833,7 @@
         <v/>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="262">
@@ -4850,7 +4850,7 @@
         <v/>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="263">
@@ -4867,7 +4867,7 @@
         <v/>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="264">
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.250Z</v>
       </c>
     </row>
     <row r="265">
@@ -4901,7 +4901,7 @@
         <v/>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="266">
@@ -4918,7 +4918,7 @@
         <v/>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="267">
@@ -4935,7 +4935,7 @@
         <v/>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="268">
@@ -4952,7 +4952,7 @@
         <v/>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="269">
@@ -4969,7 +4969,7 @@
         <v/>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="270">
@@ -4986,7 +4986,7 @@
         <v/>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="271">
@@ -5003,7 +5003,7 @@
         <v/>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="272">
@@ -5020,7 +5020,7 @@
         <v/>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="273">
@@ -5037,7 +5037,7 @@
         <v/>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="274">
@@ -5054,7 +5054,7 @@
         <v/>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="275">
@@ -5071,7 +5071,7 @@
         <v/>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-26T05:52:43.223Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="276">
@@ -5088,7 +5088,7 @@
         <v/>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="277">
@@ -5105,7 +5105,7 @@
         <v/>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="278">
@@ -5122,7 +5122,7 @@
         <v/>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="279">
@@ -5139,7 +5139,7 @@
         <v/>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="280">
@@ -5156,7 +5156,7 @@
         <v/>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="281">
@@ -5173,7 +5173,7 @@
         <v/>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="282">
@@ -5190,7 +5190,7 @@
         <v/>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="283">
@@ -5207,7 +5207,7 @@
         <v/>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.251Z</v>
       </c>
     </row>
     <row r="284">
@@ -5224,7 +5224,7 @@
         <v/>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="285">
@@ -5241,7 +5241,7 @@
         <v/>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="286">
@@ -5258,7 +5258,7 @@
         <v/>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="287">
@@ -5275,7 +5275,7 @@
         <v/>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="288">
@@ -5292,7 +5292,7 @@
         <v/>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="289">
@@ -5309,7 +5309,7 @@
         <v/>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="290">
@@ -5326,7 +5326,7 @@
         <v/>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="291">
@@ -5343,7 +5343,7 @@
         <v/>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="292">
@@ -5360,7 +5360,7 @@
         <v/>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="293">
@@ -5377,7 +5377,7 @@
         <v/>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="294">
@@ -5394,7 +5394,7 @@
         <v/>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="295">
@@ -5411,7 +5411,7 @@
         <v/>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="296">
@@ -5428,7 +5428,7 @@
         <v/>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="297">
@@ -5445,7 +5445,7 @@
         <v/>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-26T05:52:43.224Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="298">
@@ -5462,7 +5462,7 @@
         <v/>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-26T05:52:43.225Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="299">
@@ -5479,7 +5479,7 @@
         <v/>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-26T05:52:43.225Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="300">
@@ -5496,7 +5496,7 @@
         <v/>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-26T05:52:43.225Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
     <row r="301">
@@ -5513,7 +5513,7 @@
         <v/>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-26T05:52:43.225Z</v>
+        <v>2026-08-26T06:34:52.252Z</v>
       </c>
     </row>
   </sheetData>
